--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\tests\testthat\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99C8CE6-5582-425D-B354-537A017633DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2686426E-7F9E-4404-AE29-61B6EB8DD53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
   <sheets>
     <sheet name="dt_meta" sheetId="1" r:id="rId1"/>
+    <sheet name="dt_var_naming" sheetId="2" r:id="rId2"/>
+    <sheet name="naming_lookup" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="231">
   <si>
     <t>name_dt</t>
   </si>
@@ -272,9 +274,6 @@
     <t>NDVI_649IN_5_1_1</t>
   </si>
   <si>
-    <t>NDVI</t>
-  </si>
-  <si>
     <t>Photosynthetic photon flux density incoming @649 nm</t>
   </si>
   <si>
@@ -299,9 +298,6 @@
     <t>LWS_4_1_1</t>
   </si>
   <si>
-    <t>LEAF_WET</t>
-  </si>
-  <si>
     <t>Leaf Wetness</t>
   </si>
   <si>
@@ -402,6 +398,401 @@
   </si>
   <si>
     <t>UK-WHM</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t>range_min</t>
+  </si>
+  <si>
+    <t>range_max</t>
+  </si>
+  <si>
+    <t>standard_name_icos</t>
+  </si>
+  <si>
+    <t>long_name_icos</t>
+  </si>
+  <si>
+    <t>units_icos</t>
+  </si>
+  <si>
+    <t>standard_name_cf</t>
+  </si>
+  <si>
+    <t>long_name_cf</t>
+  </si>
+  <si>
+    <t>units_cf</t>
+  </si>
+  <si>
+    <t>standard_name_era5</t>
+  </si>
+  <si>
+    <t>long_name_era5</t>
+  </si>
+  <si>
+    <t>units_era5</t>
+  </si>
+  <si>
+    <t>surface_snow_thickness</t>
+  </si>
+  <si>
+    <t>Surface snow refers to the snow on the solid ground or on surface ice cover, but excludes, for example, falling snowflakes and snow on plants. "Thickness" means the vertical extent of a layer. Unless indicated in the cell_methods attribute, a quantity is assumed to apply to the whole area of each horizontal grid box. Previously, the qualifier where_type was used to specify that the quantity applies only to the part of the grid box of the named type. Names containing the where_type qualifier are deprecated and newly created data should use the cell_methods attribute to indicate the horizontal area to which the quantity applies.</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>_x000D_
+This parameter is the depth of snow from the snow-covered area of a grid box._x000D_
+_x000D_
+Its units are metres of water equivalent, so it is the depth the water would have if the snow melted and was spread evenly over the whole grid box. The ECMWF Integrated Forecast System represents snow as a single additional layer over the uppermost soil level. The snow may cover all or part of the grid box._x000D_
+_x000D_
+See further information. [NOTE: See 228141 for the equivalent parameter in "kg m-2"]</t>
+  </si>
+  <si>
+    <t>m of water equivalent</t>
+  </si>
+  <si>
+    <t>timestamp in POSIX format</t>
+  </si>
+  <si>
+    <t>W m^2</t>
+  </si>
+  <si>
+    <t>downward_heat_flux_at_ground_level_in_soil</t>
+  </si>
+  <si>
+    <t>ground_level means the land surface (beneath the snow and surface water, if any). 'Downward' indicates a vector component which is positive when directed downward (negative upward). In accordance with common usage in geophysical disciplines, 'flux' implies per unit area, called 'flux density' in physics.</t>
+  </si>
+  <si>
+    <t>W / m^2</t>
+  </si>
+  <si>
+    <t>Incoming Longwave radiation (in the range from 4 to 50 micron)</t>
+  </si>
+  <si>
+    <t>surface_downwelling_longwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>The surface called "surface" means the lower boundary of the atmosphere. Downwelling radiation is radiation from above. It does not mean "net downward". The sign convention is that "upwelling" is positive upwards and "downwelling" is positive downwards. The term "longwave" means longwave radiation. When thought of as being incident on a surface, a radiative flux is sometimes called "irradiance". In addition, it is identical with the quantity measured by a cosine-collector light-meter and sometimes called "vector irradiance". In accordance with common usage in geophysical disciplines, "flux" implies per unit area, called "flux density" in physics.</t>
+  </si>
+  <si>
+    <t>strd</t>
+  </si>
+  <si>
+    <t>This parameter is the amount of thermal (also known as longwave or terrestrial) radiation emitted by the atmosphere and clouds that reaches a horizontal plane at the surface of the Earth._x000D_
+_x000D_
+The surface of the Earth emits thermal radiation, some of which is absorbed by the atmosphere and clouds. The atmosphere and clouds likewise emit thermal radiation in all directions, some of which reaches the surface (represented by this parameter). See further documentation._x000D_
+_x000D_
+This parameter is accumulated over a particular time period which depends on the data extracted. The units are joules per square metre (J m-2). To convert to watts per square metre (W m-2), the accumulated values should be divided by the accumulation period expressed in seconds. The ECMWF convention for vertical fluxes is positive downwards.</t>
+  </si>
+  <si>
+    <t>J m-2</t>
+  </si>
+  <si>
+    <t>Outgoing Longwave radiation (in the range from 4 to 50 micron)</t>
+  </si>
+  <si>
+    <t>surface_upwelling_longwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>The surface called "surface" means the lower boundary of the atmosphere. The term "longwave" means longwave radiation. Upwelling radiation is radiation from below. It does not mean "net upward". The sign convention is that "upwelling" is positive upwards and "downwelling" is positive downwards. When thought of as being incident on a surface, a radiative flux is sometimes called "irradiance". In addition, it is identical with the quantity measured by a cosine-collector light-meter and sometimes called "vector irradiance". In accordance with common usage in geophysical disciplines, "flux" implies per unit area, called "flux density" in physics.</t>
+  </si>
+  <si>
+    <t>LWS</t>
+  </si>
+  <si>
+    <t>Leaf wetness</t>
+  </si>
+  <si>
+    <t>NDVI_649IN</t>
+  </si>
+  <si>
+    <t>micromol / m^2 / s</t>
+  </si>
+  <si>
+    <t>Normalized Difference Vegetation Index</t>
+  </si>
+  <si>
+    <t>NDVI_649OUT</t>
+  </si>
+  <si>
+    <t>NDVI_797IN</t>
+  </si>
+  <si>
+    <t>NDVI_797OUT</t>
+  </si>
+  <si>
+    <t>tp</t>
+  </si>
+  <si>
+    <t>_x000D_
+This parameter is the accumulated liquid and frozen water, comprising rain and snow, that falls to the Earth's surface. It is the sum of large-scale precipitation and convective precipitation. Large-scale precipitation is generated by the cloud scheme in the ECMWF Integrated Forecasting System (IFS). The cloud scheme represents the formation and dissipation of clouds and large-scale precipitation due to changes in atmospheric quantities (such as pressure, temperature and moisture) predicted directly by the IFS at spatial scales of the grid box or larger. Convective precipitation is generated by the convection scheme in the IFS, which represents convection at spatial scales smaller than the grid box. See further information. This parameter does not include fog, dew or the precipitation that evaporates in the atmosphere before it lands at the surface of the Earth._x000D_
+_x000D_
+This parameter is the total amount of water accumulated over a particular time period which depends on the data extracted. The units of this parameter are depth in metres of water equivalent. It is the depth the water would have if it were spread evenly over the grid box._x000D_
+_x000D_
+Care should be taken when comparing model parameters with observations, because observations are often local to a particular point in space and time, rather than representing averages over a model grid box. [NOTE: See 228228 for the equivalent parameter in "kg m-2"]</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>This parameter is the pressure (force per unit area) of the atmosphere on the surface of land, sea and in-land water._x000D_
+_x000D_
+It is a measure of the weight of all the air in a column vertically above the area of the Earth's surface represented at a fixed point._x000D_
+_x000D_
+Surface pressure is often used in combination with temperature to calculate air density._x000D_
+_x000D_
+The strong variation of pressure with altitude makes it difficult to see the low and high pressure systems over mountainous areas, so mean sea level pressure, rather than surface pressure, is normally used for this purpose._x000D_
+_x000D_
+The units of this parameter are Pascals (Pa). Surface pressure is often measured in hPa and sometimes is presented in the old units of millibars, mb (1 hPa = 1 mb= 100 Pa).</t>
+  </si>
+  <si>
+    <t>Pa</t>
+  </si>
+  <si>
+    <t>Diffuse incoming PPFD (400-700 nm)</t>
+  </si>
+  <si>
+    <t>surface_diffuse_downwelling_photosynthetic_radiative_flux_in_air</t>
+  </si>
+  <si>
+    <t>The surface called "surface" means the lower boundary of the atmosphere. Downwelling radiation is radiation from above. It does not mean "net downward". The sign convention is that "upwelling" is positive upwards and "downwelling" is positive downwards. "Photosynthetic" radiation is the part of the spectrum which is used in photosynthesis e.g. 400-700 nm. "Diffuse" radiation is radiation that has been scattered by gas molecules in the atmosphere and by particles such as cloud droplets and aerosols. The range of wavelengths could be specified precisely by the bounds of a coordinate of radiation_wavelength. When thought of as being incident on a surface, a radiative flux is sometimes called "irradiance". In addition, it is identical with the quantity measured by a cosine-collector light-meter and sometimes called "vector irradiance". In accordance with common usage in geophysical disciplines, "flux" implies per unit area, called "flux density" in physics.</t>
+  </si>
+  <si>
+    <t>Photosynthetic Photon Flux Density (400-700 nm)</t>
+  </si>
+  <si>
+    <t>Reflected PPFD (400-700 nm)</t>
+  </si>
+  <si>
+    <t>surface_upwelling_photosynthetic_photon_flux_in_air</t>
+  </si>
+  <si>
+    <t>The surface called "surface" means the lower boundary of the atmosphere. Upwelling radiation is radiation from below. It does not mean "net upward". The sign convention is that "upwelling" is positive upwards and "downwelling" is positive downwards. "Photosynthetic" radiation is the part of the spectrum which is used in photosynthesis e.g. 400-700 nm. The range of wavelengths could be specified precisely by the bounds of a coordinate of radiation_wavelength. A photon flux is specified in terms of numbers of photons expressed in moles. In accordance with common usage in geophysical disciplines, "flux" implies per unit area, called "flux density" in physics.</t>
+  </si>
+  <si>
+    <t>mol m-2 s-1</t>
+  </si>
+  <si>
+    <t>ssrd</t>
+  </si>
+  <si>
+    <t>This parameter is the amount of solar radiation (also known as shortwave radiation) that reaches a horizontal plane at the surface of the Earth. This parameter comprises both direct and diffuse solar radiation._x000D_
+_x000D_
+Radiation from the Sun (solar, or shortwave, radiation) is partly reflected back to space by clouds and particles in the atmosphere (aerosols) and some of it is absorbed. The rest is incident on the Earth's surface (represented by this parameter). See further documentation._x000D_
+_x000D_
+To a reasonably good approximation, this parameter is the model equivalent of what would be measured by a pyranometer (an instrument used for measuring solar radiation) at the surface. However, care should be taken when comparing model parameters with observations, because observations are often local to a particular point in space and time, rather than representing averages over a model grid box._x000D_
+_x000D_
+This parameter is accumulated over a particular time period which depends on the data extracted. The units are joules per square metre (J m-2). To convert to watts per square metre (W m-2), the accumulated values should be divided by the accumulation period expressed in seconds. The ECMWF convention for vertical fluxes is positive downwards.</t>
+  </si>
+  <si>
+    <t>percent</t>
+  </si>
+  <si>
+    <t>rh</t>
+  </si>
+  <si>
+    <t>_x000D_
+This parameter is the water vapour pressure as a percentage of the value at which the air becomes saturated (the point at which water vapour begins to condense into liquid water or deposition into ice)._x000D_
+_x000D_
+For temperatures over 0degree_C (273.15 K) it is calculated for saturation over water. At temperatures below -23degree_C it is calculated for saturation over ice. Between -23degree_C and 0degree_C this parameter is calculated by interpolating between the ice and water values using a quadratic function.</t>
+  </si>
+  <si>
+    <t>Net radiation (including SW and LW components)</t>
+  </si>
+  <si>
+    <t>This parameter is the amount of solar radiation (also known as shortwave radiation) that reaches a horizontal plane at the surface of the Earth (both direct and diffuse) minus the amount reflected by the Earth's surface (which is governed by the albedo)._x000D_
+_x000D_
+Radiation from the Sun (solar, or shortwave, radiation) is partly reflected back to space by clouds and particles in the atmosphere (aerosols) and some of it is absorbed. The remainder is incident on the Earth's surface, where some of it is reflected. See further documentation._x000D_
+_x000D_
+This parameter is accumulated over a particular time period which depends on the data extracted. The units are joules per square metre (J m-2). To convert to watts per square metre (W m-2), the accumulated values should be divided by the accumulation period expressed in seconds. The ECMWF convention for vertical fluxes is positive downwards.</t>
+  </si>
+  <si>
+    <t>Incoming Shortwave radiation (in the range from 0.3 to 4.5 micron)</t>
+  </si>
+  <si>
+    <t>surface_downwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>The surface called "surface" means the lower boundary of the atmosphere. Downwelling radiation is radiation from above. It does not mean "net downward". The sign convention is that "upwelling" is positive upwards and "downwelling" is positive downwards. The term "shortwave" means shortwave radiation. Surface downwelling shortwave is the sum of direct and diffuse solar radiation incident on the surface, and is sometimes called "global radiation". When thought of as being incident on a surface, a radiative flux is sometimes called "irradiance". In addition, it is identical with the quantity measured by a cosine-collector light-meter and sometimes called "vector irradiance". In accordance with common usage in geophysical disciplines, "flux" implies per unit area, called "flux density" in physics.</t>
+  </si>
+  <si>
+    <t>Outgoing Shortwave radiation (in the range from 0.3 to 4.5 micron)</t>
+  </si>
+  <si>
+    <t>surface_upwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>The surface called "surface" means the lower boundary of the atmosphere. The term "shortwave" means shortwave radiation. Upwelling radiation is radiation from below. It does not mean "net upward". The sign convention is that "upwelling" is positive upwards and "downwelling" is positive downwards. When thought of as being incident on a surface, a radiative flux is sometimes called "irradiance". In addition, it is identical with the quantity measured by a cosine-collector light-meter and sometimes called "vector irradiance". In accordance with common usage in geophysical disciplines, "flux" implies per unit area, called "flux density" in physics.</t>
+  </si>
+  <si>
+    <t>volume_fraction_of_condensed_water_in_soil</t>
+  </si>
+  <si>
+    <t>"Volume fraction" is used in the construction "volume_fraction_of_X_in_Y", where X is a material constituent of Y. It is evaluated as the volume of X divided by the volume of Y (including X). It may be expressed as a fraction, a percentage, or any other dimensionless representation of a fraction. The phrase "condensed_water" means liquid and ice.</t>
+  </si>
+  <si>
+    <t>swvl1</t>
+  </si>
+  <si>
+    <t>This parameter is the volume of water in soil layer 1 (0 - 7cm, the surface is at 0cm)._x000D_
+_x000D_
+The ECMWF Integrated Forecasting System model has a four-layer representation of soil:_x000D_
+Layer 1: 0 - 7cm_x000D_
+Layer 2: 7 - 28cm_x000D_
+Layer 3: 28 - 100cm_x000D_
+Layer 4: 100 - 289cm_x000D_
+_x000D_
+The volumetric soil water is associated with the soil texture (or classification), soil depth, and the underlying groundwater level.</t>
+  </si>
+  <si>
+    <t>m3 m-3</t>
+  </si>
+  <si>
+    <t>degree_C</t>
+  </si>
+  <si>
+    <t>_x000D_
+This parameter is the temperature of air at 2m above the surface of land, sea or in-land waters._x000D_
+_x000D_
+2m temperature is calculated by interpolating between the lowest model level and the Earth's surface, taking account of the atmospheric conditions. See further information ._x000D_
+_x000D_
+This parameter has units of kelvin (K). Temperature measured in kelvin can be converted to degrees Celsius (degree_C) by subtracting 273.15._x000D_
+_x000D_
+Please note that the encodings listed here for s2s &amp; uerra (which includes encodings for carra/cerra) include entries for Mean 2 metre temperature. The specific encoding for Mean 2 metre temperature can be found in 228004.</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>soil_temperature</t>
+  </si>
+  <si>
+    <t>Soil temperature is the bulk temperature of the soil, not the surface (skin) temperature. "Soil" means the near-surface layer where plants sink their roots. For subsurface temperatures that extend beneath the soil layer or in areas where there is no surface soil layer, the standard name temperature_in_ground should be used. It is strongly recommended that a variable with this standard name should have a units_metadata attribute, with one of the values "on-scale" or "difference", whichever is appropriate for the data, because it is essential to know whether the temperature is on-scale (meaning relative to the origin of the scale indicated by the units) or refers to temperature differences (implying that the origin of the temperature scale is irrelevant), in order to convert the units correctly (cf. https://cfconventions.org/cf-conventions/cf-conventions.html#temperature-units).</t>
+  </si>
+  <si>
+    <t>stl1</t>
+  </si>
+  <si>
+    <t>This parameter is the temperature of the soil at level 1 (in the middle of layer 1)._x000D_
+_x000D_
+The ECMWF Integrated Forecasting System (IFS) has a four-layer representation of soil, where the surface is at 0cm:_x000D_
+_x000D_
+Layer 1: 0 - 7cm_x000D_
+Layer 2: 7 - 28cm_x000D_
+Layer 3: 28 - 100cm_x000D_
+Layer 4: 100 - 289cm_x000D_
+_x000D_
+Soil temperature is set at the middle of each layer, and heat transfer is calculated at the interfaces between them. It is assumed that there is no heat transfer out of the bottom of the lowest layer._x000D_
+_x000D_
+This parameter has units of Kelvin (K). Temperature measured in Kelvin can be converted to degrees Celsius (degree_C) by subtracting 273.15.</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>This parameter is the horizontal speed of the wind, or movement of air, at a height of ten metres above the surface of the Earth. The units of this parameter are metres per second._x000D_
+_x000D_
+Care should be taken when comparing this parameter with observations, because wind observations vary on small space and time scales and are affected by the local terrain, vegetation and buildings that are represented only on average in the ECMWF Integrated Forecasting System._x000D_
+_x000D_
+The eastward and northward components of the horizontal wind at 10m are also available as parameters.</t>
+  </si>
+  <si>
+    <t>water_table_depth</t>
+  </si>
+  <si>
+    <t>Depth is the vertical distance below the surface. The water table is the surface below which the soil is saturated with water such that all pore spaces are filled.</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>icos_name</t>
+  </si>
+  <si>
+    <t>icos_units</t>
+  </si>
+  <si>
+    <t>era5_name</t>
+  </si>
+  <si>
+    <t>mainmet_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil temperature </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air pressure  </t>
+  </si>
+  <si>
+    <t>ssru</t>
+  </si>
+  <si>
+    <t>stru</t>
+  </si>
+  <si>
+    <t>fdif</t>
+  </si>
+  <si>
+    <t>ws</t>
+  </si>
+  <si>
+    <t>WS_6_1_1</t>
+  </si>
+  <si>
+    <t>wd</t>
+  </si>
+  <si>
+    <t>WD_6_1_1</t>
+  </si>
+  <si>
+    <t>rn</t>
+  </si>
+  <si>
+    <t>RN_5_1_1</t>
+  </si>
+  <si>
+    <t>SWC_4_1_1</t>
+  </si>
+  <si>
+    <t>SWC_4_2_1</t>
+  </si>
+  <si>
+    <t>SWC_4_3_1</t>
+  </si>
+  <si>
+    <t>SWC_4_4_1</t>
+  </si>
+  <si>
+    <t>t2m</t>
+  </si>
+  <si>
+    <t>TA_4_1_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relative  humidity  </t>
+  </si>
+  <si>
+    <t>RH_4_1_1</t>
+  </si>
+  <si>
+    <t>era5_units</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>μmol / m^2 / s</t>
+  </si>
+  <si>
+    <t>m / s</t>
+  </si>
+  <si>
+    <t>mm</t>
   </si>
 </sst>
 </file>
@@ -885,10 +1276,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1266,17 +1663,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B621CE1-A4D4-4502-917D-92507EE2F7EE}">
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:T104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
     <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1291,10 +1690,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -1329,22 +1728,28 @@
       <c r="R1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" t="s">
@@ -1380,10 +1785,17 @@
       <c r="R2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T2" t="str">
+        <f>VLOOKUP(C2,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -1398,7 +1810,7 @@
         <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H3" s="1">
         <v>46023</v>
@@ -1433,13 +1845,21 @@
       <c r="R3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3" t="str">
+        <f>VLOOKUP(C3,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>sd</v>
+      </c>
+      <c r="T3" t="str">
+        <f>VLOOKUP(C3,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>cm</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
         <v>62</v>
@@ -1451,7 +1871,7 @@
         <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H4" s="1">
         <v>46023</v>
@@ -1486,10 +1906,18 @@
       <c r="R4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4" t="str">
+        <f>VLOOKUP(C4,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>sd</v>
+      </c>
+      <c r="T4" t="str">
+        <f>VLOOKUP(C4,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>cm</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -1498,13 +1926,13 @@
         <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -1539,10 +1967,18 @@
       <c r="R5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5" t="str">
+        <f>VLOOKUP(C5,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>time</v>
+      </c>
+      <c r="T5" t="str">
+        <f>VLOOKUP(C5,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1557,7 +1993,7 @@
         <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H6" s="1">
         <v>46023</v>
@@ -1592,10 +2028,18 @@
       <c r="R6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S6" t="str">
+        <f>VLOOKUP(C6,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T6" t="str">
+        <f>VLOOKUP(C6,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -1610,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H7" s="1">
         <v>46023</v>
@@ -1645,10 +2089,18 @@
       <c r="R7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S7" t="str">
+        <f>VLOOKUP(C7,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T7" t="str">
+        <f>VLOOKUP(C7,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -1663,7 +2115,7 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H8" s="1">
         <v>46023</v>
@@ -1698,10 +2150,18 @@
       <c r="R8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S8" t="str">
+        <f>VLOOKUP(C8,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T8" t="str">
+        <f>VLOOKUP(C8,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -1716,7 +2176,7 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H9" s="1">
         <v>46023</v>
@@ -1751,13 +2211,21 @@
       <c r="R9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S9" t="str">
+        <f>VLOOKUP(C9,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>strd</v>
+      </c>
+      <c r="T9" t="str">
+        <f>VLOOKUP(C9,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -1769,7 +2237,7 @@
         <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H10" s="1">
         <v>46023</v>
@@ -1804,10 +2272,18 @@
       <c r="R10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S10" t="str">
+        <f>VLOOKUP(C10,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>strd</v>
+      </c>
+      <c r="T10" t="str">
+        <f>VLOOKUP(C10,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1822,7 +2298,7 @@
         <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H11" s="1">
         <v>46023</v>
@@ -1857,13 +2333,21 @@
       <c r="R11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S11" t="str">
+        <f>VLOOKUP(C11,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stru</v>
+      </c>
+      <c r="T11" t="str">
+        <f>VLOOKUP(C11,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
@@ -1875,7 +2359,7 @@
         <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H12" s="1">
         <v>46023</v>
@@ -1910,25 +2394,33 @@
       <c r="R12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S12" t="str">
+        <f>VLOOKUP(C12,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stru</v>
+      </c>
+      <c r="T12" t="str">
+        <f>VLOOKUP(C12,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>88</v>
       </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" t="s">
-        <v>90</v>
-      </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H13" s="1">
         <v>46023</v>
@@ -1963,25 +2455,33 @@
       <c r="R13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S13" t="str">
+        <f>VLOOKUP(C13,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="T13">
+        <f>VLOOKUP(C13,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
         <v>88</v>
       </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>90</v>
-      </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H14" s="1">
         <v>46023</v>
@@ -2016,25 +2516,33 @@
       <c r="R14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S14" t="str">
+        <f>VLOOKUP(C14,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="T14">
+        <f>VLOOKUP(C14,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
         <v>78</v>
       </c>
       <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
         <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>80</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H15" s="1">
         <v>46023</v>
@@ -2069,25 +2577,33 @@
       <c r="R15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S15" t="str">
+        <f>VLOOKUP(C15,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T15" t="str">
+        <f>VLOOKUP(C15,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
         <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H16" s="1">
         <v>46023</v>
@@ -2122,25 +2638,33 @@
       <c r="R16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S16" t="str">
+        <f>VLOOKUP(C16,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+      <c r="T16" t="str">
+        <f>VLOOKUP(C16,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
         <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H17" s="1">
         <v>46023</v>
@@ -2175,25 +2699,33 @@
       <c r="R17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S17" t="str">
+        <f>VLOOKUP(C17,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T17" t="str">
+        <f>VLOOKUP(C17,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
         <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" t="s">
-        <v>86</v>
       </c>
       <c r="E18" t="s">
         <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H18" s="1">
         <v>46023</v>
@@ -2228,10 +2760,18 @@
       <c r="R18" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S18" t="str">
+        <f>VLOOKUP(C18,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+      <c r="T18" t="str">
+        <f>VLOOKUP(C18,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
         <v>52</v>
@@ -2246,7 +2786,7 @@
         <v>55</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H19" s="1">
         <v>46023</v>
@@ -2281,13 +2821,21 @@
       <c r="R19" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S19" t="str">
+        <f>VLOOKUP(C19,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>tp</v>
+      </c>
+      <c r="T19" t="str">
+        <f>VLOOKUP(C19,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>mm</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
         <v>53</v>
@@ -2299,7 +2847,7 @@
         <v>55</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H20" s="1">
         <v>46023</v>
@@ -2334,10 +2882,18 @@
       <c r="R20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S20" t="str">
+        <f>VLOOKUP(C20,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>tp</v>
+      </c>
+      <c r="T20" t="str">
+        <f>VLOOKUP(C20,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>mm</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
@@ -2352,7 +2908,7 @@
         <v>35</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
         <v>46023</v>
@@ -2387,10 +2943,18 @@
       <c r="R21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S21" t="str">
+        <f>VLOOKUP(C21,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>sp</v>
+      </c>
+      <c r="T21" t="str">
+        <f>VLOOKUP(C21,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>kPa</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
@@ -2405,7 +2969,7 @@
         <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H22" s="1">
         <v>46023</v>
@@ -2440,13 +3004,21 @@
       <c r="R22" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S22" t="str">
+        <f>VLOOKUP(C22,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>fdif</v>
+      </c>
+      <c r="T22" t="str">
+        <f>VLOOKUP(C22,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
@@ -2458,7 +3030,7 @@
         <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H23" s="1">
         <v>46023</v>
@@ -2493,10 +3065,18 @@
       <c r="R23" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S23" t="str">
+        <f>VLOOKUP(C23,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>fdif</v>
+      </c>
+      <c r="T23" t="str">
+        <f>VLOOKUP(C23,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>44</v>
@@ -2511,7 +3091,7 @@
         <v>47</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H24" s="1">
         <v>46023</v>
@@ -2546,13 +3126,21 @@
       <c r="R24" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S24" t="str">
+        <f>VLOOKUP(C24,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T24" t="str">
+        <f>VLOOKUP(C24,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
         <v>45</v>
@@ -2564,7 +3152,7 @@
         <v>47</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H25" s="1">
         <v>46023</v>
@@ -2599,13 +3187,21 @@
       <c r="R25" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S25" t="str">
+        <f>VLOOKUP(C25,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T25" t="str">
+        <f>VLOOKUP(C25,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
         <v>45</v>
@@ -2617,7 +3213,7 @@
         <v>47</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H26" s="1">
         <v>46023</v>
@@ -2652,10 +3248,18 @@
       <c r="R26" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S26" t="str">
+        <f>VLOOKUP(C26,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T26" t="str">
+        <f>VLOOKUP(C26,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
@@ -2670,7 +3274,7 @@
         <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H27" s="1">
         <v>46023</v>
@@ -2705,13 +3309,21 @@
       <c r="R27" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S27" t="str">
+        <f>VLOOKUP(C27,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+      <c r="T27" t="str">
+        <f>VLOOKUP(C27,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
@@ -2723,7 +3335,7 @@
         <v>47</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H28" s="1">
         <v>46023</v>
@@ -2758,14 +3370,25 @@
       <c r="R28" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S28" t="str">
+        <f>VLOOKUP(C28,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+      <c r="T28" t="str">
+        <f>VLOOKUP(C28,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B29" t="s">
         <v>76</v>
       </c>
+      <c r="C29" t="s">
+        <v>121</v>
+      </c>
       <c r="D29" t="s">
         <v>77</v>
       </c>
@@ -2773,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H29" s="1">
         <v>46023</v>
@@ -2808,10 +3431,18 @@
       <c r="R29" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S29" t="str">
+        <f>VLOOKUP(C29,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T29" t="str">
+        <f>VLOOKUP(C29,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="str">
         <f t="shared" ref="B30:B33" si="0">C30&amp;"_"&amp;J30&amp;"_"&amp;K30&amp;"_"&amp;L30</f>
@@ -2827,7 +3458,7 @@
         <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H30" s="1">
         <v>46023</v>
@@ -2862,10 +3493,18 @@
       <c r="R30" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S30" t="str">
+        <f>VLOOKUP(C30,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="T30" t="str">
+        <f>VLOOKUP(C30,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B31" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2881,7 +3520,7 @@
         <v>24</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H31" s="1">
         <v>46023</v>
@@ -2916,10 +3555,18 @@
       <c r="R31" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S31" t="str">
+        <f>VLOOKUP(C31,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="T31" t="str">
+        <f>VLOOKUP(C31,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2935,7 +3582,7 @@
         <v>24</v>
       </c>
       <c r="F32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H32" s="1">
         <v>46023</v>
@@ -2970,17 +3617,25 @@
       <c r="R32" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S32" t="str">
+        <f>VLOOKUP(C32,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="T32" t="str">
+        <f>VLOOKUP(C32,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>RN_5_1_1</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
         <v>65</v>
@@ -2989,7 +3644,7 @@
         <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H33" s="1">
         <v>46023</v>
@@ -3024,10 +3679,18 @@
       <c r="R33" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S33" t="str">
+        <f>VLOOKUP(C33,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rn</v>
+      </c>
+      <c r="T33" t="str">
+        <f>VLOOKUP(C33,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
         <v>36</v>
@@ -3042,7 +3705,7 @@
         <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H34" s="1">
         <v>46023</v>
@@ -3077,10 +3740,18 @@
       <c r="R34" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S34" t="str">
+        <f>VLOOKUP(C34,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T34" t="str">
+        <f>VLOOKUP(C34,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B35" s="2" t="str">
         <f t="shared" ref="B35:B36" si="1">C35&amp;"_"&amp;J35&amp;"_"&amp;K35&amp;"_"&amp;L35</f>
@@ -3096,7 +3767,7 @@
         <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H35" s="1">
         <v>46023</v>
@@ -3131,10 +3802,18 @@
       <c r="R35" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S35" t="str">
+        <f>VLOOKUP(C35,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T35" t="str">
+        <f>VLOOKUP(C35,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B36" s="2" t="str">
         <f t="shared" si="1"/>
@@ -3150,7 +3829,7 @@
         <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H36" s="1">
         <v>46023</v>
@@ -3185,10 +3864,18 @@
       <c r="R36" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S36" t="str">
+        <f>VLOOKUP(C36,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T36" t="str">
+        <f>VLOOKUP(C36,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
@@ -3203,7 +3890,7 @@
         <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H37" s="1">
         <v>46023</v>
@@ -3238,13 +3925,21 @@
       <c r="R37" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S37" t="str">
+        <f>VLOOKUP(C37,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+      <c r="T37" t="str">
+        <f>VLOOKUP(C37,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
         <v>38</v>
@@ -3256,7 +3951,7 @@
         <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H38" s="1">
         <v>46023</v>
@@ -3291,10 +3986,18 @@
       <c r="R38" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S38" t="str">
+        <f>VLOOKUP(C38,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+      <c r="T38" t="str">
+        <f>VLOOKUP(C38,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
@@ -3309,7 +4012,7 @@
         <v>24</v>
       </c>
       <c r="F39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H39" s="1">
         <v>46023</v>
@@ -3344,10 +4047,18 @@
       <c r="R39" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S39" t="str">
+        <f>VLOOKUP(C39,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T39" t="str">
+        <f>VLOOKUP(C39,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B40" s="2" t="str">
         <f t="shared" ref="B40:B51" si="2">C40&amp;"_"&amp;J40&amp;"_"&amp;K40&amp;"_"&amp;L40</f>
@@ -3363,7 +4074,7 @@
         <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H40" s="1">
         <v>46023</v>
@@ -3398,10 +4109,18 @@
       <c r="R40" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S40" t="str">
+        <f>VLOOKUP(C40,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T40" t="str">
+        <f>VLOOKUP(C40,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B41" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3417,7 +4136,7 @@
         <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H41" s="1">
         <v>46023</v>
@@ -3452,10 +4171,18 @@
       <c r="R41" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S41" t="str">
+        <f>VLOOKUP(C41,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T41" t="str">
+        <f>VLOOKUP(C41,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B42" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3471,7 +4198,7 @@
         <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H42" s="1">
         <v>46023</v>
@@ -3506,10 +4233,18 @@
       <c r="R42" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S42" t="str">
+        <f>VLOOKUP(C42,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T42" t="str">
+        <f>VLOOKUP(C42,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B43" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3525,7 +4260,7 @@
         <v>24</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H43" s="1">
         <v>46023</v>
@@ -3560,10 +4295,18 @@
       <c r="R43" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S43" t="str">
+        <f>VLOOKUP(C43,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T43" t="str">
+        <f>VLOOKUP(C43,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B44" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3579,7 +4322,7 @@
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H44" s="1">
         <v>46023</v>
@@ -3614,10 +4357,18 @@
       <c r="R44" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S44" t="str">
+        <f>VLOOKUP(C44,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="T44" t="str">
+        <f>VLOOKUP(C44,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B45" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3633,7 +4384,7 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H45" s="1">
         <v>46023</v>
@@ -3668,10 +4419,18 @@
       <c r="R45" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S45" t="str">
+        <f>VLOOKUP(C45,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="T45" t="str">
+        <f>VLOOKUP(C45,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B46" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3687,7 +4446,7 @@
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H46" s="1">
         <v>46023</v>
@@ -3722,25 +4481,33 @@
       <c r="R46" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S46" t="str">
+        <f>VLOOKUP(C46,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="T46" t="str">
+        <f>VLOOKUP(C46,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" t="s">
+        <v>97</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="F47" t="s">
-        <v>99</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -3775,10 +4542,18 @@
       <c r="R47" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S47" t="str">
+        <f>VLOOKUP(C47,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>time</v>
+      </c>
+      <c r="T47" t="str">
+        <f>VLOOKUP(C47,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>NA</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B48" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3794,7 +4569,7 @@
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H48" s="1">
         <v>46023</v>
@@ -3829,10 +4604,18 @@
       <c r="R48" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S48" t="str">
+        <f>VLOOKUP(C48,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>wd</v>
+      </c>
+      <c r="T48" t="str">
+        <f>VLOOKUP(C48,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B49" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3848,7 +4631,7 @@
         <v>58</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H49" s="1">
         <v>46023</v>
@@ -3883,10 +4666,18 @@
       <c r="R49" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S49" t="str">
+        <f>VLOOKUP(C49,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ws</v>
+      </c>
+      <c r="T49" t="str">
+        <f>VLOOKUP(C49,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m / s</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B50" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3902,7 +4693,7 @@
         <v>61</v>
       </c>
       <c r="F50" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H50" s="1">
         <v>46023</v>
@@ -3937,10 +4728,18 @@
       <c r="R50" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S50" t="str">
+        <f>VLOOKUP(C50,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>wd</v>
+      </c>
+      <c r="T50" t="str">
+        <f>VLOOKUP(C50,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B51" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3956,7 +4755,7 @@
         <v>58</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H51" s="1">
         <v>46023</v>
@@ -3991,10 +4790,18 @@
       <c r="R51" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S51" t="str">
+        <f>VLOOKUP(C51,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ws</v>
+      </c>
+      <c r="T51" t="str">
+        <f>VLOOKUP(C51,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m / s</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B52" t="s">
         <v>28</v>
@@ -4009,7 +4816,7 @@
         <v>30</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H52" s="1">
         <v>46023</v>
@@ -4044,10 +4851,18 @@
       <c r="R52" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S52" t="str">
+        <f>VLOOKUP(C52,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T52" t="str">
+        <f>VLOOKUP(C52,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
         <v>31</v>
@@ -4062,7 +4877,7 @@
         <v>30</v>
       </c>
       <c r="F53" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H53" s="1">
         <v>46023</v>
@@ -4097,10 +4912,18 @@
       <c r="R53" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S53" t="str">
+        <f>VLOOKUP(C53,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T53" t="str">
+        <f>VLOOKUP(C53,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -4115,7 +4938,7 @@
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H54" s="1">
         <v>46023</v>
@@ -4150,10 +4973,18 @@
       <c r="R54" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S54" t="str">
+        <f>VLOOKUP(C54,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T54" t="str">
+        <f>VLOOKUP(C54,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
         <v>66</v>
@@ -4168,7 +4999,7 @@
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H55" s="1">
         <v>46023</v>
@@ -4203,10 +5034,18 @@
       <c r="R55" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S55" t="str">
+        <f>VLOOKUP(C55,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T55" t="str">
+        <f>VLOOKUP(C55,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
@@ -4221,7 +5060,7 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H56" s="1">
         <v>46023</v>
@@ -4256,10 +5095,18 @@
       <c r="R56" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S56" t="str">
+        <f>VLOOKUP(C56,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T56" t="str">
+        <f>VLOOKUP(C56,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B57" t="s">
         <v>68</v>
@@ -4274,7 +5121,7 @@
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H57" s="1">
         <v>46023</v>
@@ -4309,10 +5156,18 @@
       <c r="R57" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S57" t="str">
+        <f>VLOOKUP(C57,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T57" t="str">
+        <f>VLOOKUP(C57,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
         <v>69</v>
@@ -4327,7 +5182,7 @@
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H58" s="1">
         <v>46023</v>
@@ -4362,10 +5217,18 @@
       <c r="R58" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S58" t="str">
+        <f>VLOOKUP(C58,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T58" t="str">
+        <f>VLOOKUP(C58,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B59" s="2" t="str">
         <f>C59&amp;"_"&amp;J59&amp;"_"&amp;K59&amp;"_"&amp;L59</f>
@@ -4381,7 +5244,7 @@
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H59" s="1">
         <v>46023</v>
@@ -4416,10 +5279,18 @@
       <c r="R59" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S59" t="str">
+        <f>VLOOKUP(C59,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T59" t="str">
+        <f>VLOOKUP(C59,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B60" s="2" t="str">
         <f t="shared" ref="B60:B63" si="3">C60&amp;"_"&amp;J60&amp;"_"&amp;K60&amp;"_"&amp;L60</f>
@@ -4435,7 +5306,7 @@
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H60" s="1">
         <v>46023</v>
@@ -4470,10 +5341,18 @@
       <c r="R60" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S60" t="str">
+        <f>VLOOKUP(C60,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T60" t="str">
+        <f>VLOOKUP(C60,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B61" s="2" t="str">
         <f t="shared" si="3"/>
@@ -4489,7 +5368,7 @@
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H61" s="1">
         <v>46023</v>
@@ -4524,10 +5403,18 @@
       <c r="R61" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S61" t="str">
+        <f>VLOOKUP(C61,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T61" t="str">
+        <f>VLOOKUP(C61,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B62" s="2" t="str">
         <f t="shared" ref="B62" si="4">C62&amp;"_"&amp;J62&amp;"_"&amp;K62&amp;"_"&amp;L62</f>
@@ -4543,7 +5430,7 @@
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H62" s="1">
         <v>46023</v>
@@ -4578,10 +5465,18 @@
       <c r="R62" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S62" t="str">
+        <f>VLOOKUP(C62,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T62" t="str">
+        <f>VLOOKUP(C62,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B63" s="2" t="str">
         <f t="shared" si="3"/>
@@ -4597,7 +5492,7 @@
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H63" s="1">
         <v>46023</v>
@@ -4632,10 +5527,18 @@
       <c r="R63" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S63" t="str">
+        <f>VLOOKUP(C63,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T63" t="str">
+        <f>VLOOKUP(C63,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B64" s="2" t="str">
         <f>C64&amp;"_"&amp;J64&amp;"_"&amp;K64&amp;"_"&amp;L64</f>
@@ -4651,7 +5554,7 @@
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H64" s="1">
         <v>46023</v>
@@ -4686,10 +5589,18 @@
       <c r="R64" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S64" t="str">
+        <f>VLOOKUP(C64,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T64" t="str">
+        <f>VLOOKUP(C64,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B65" s="2" t="str">
         <f t="shared" ref="B65:B67" si="5">C65&amp;"_"&amp;J65&amp;"_"&amp;K65&amp;"_"&amp;L65</f>
@@ -4705,7 +5616,7 @@
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H65" s="1">
         <v>46023</v>
@@ -4740,10 +5651,18 @@
       <c r="R65" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S65" t="str">
+        <f>VLOOKUP(C65,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T65" t="str">
+        <f>VLOOKUP(C65,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="str">
         <f t="shared" si="5"/>
@@ -4759,7 +5678,7 @@
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H66" s="1">
         <v>46023</v>
@@ -4794,10 +5713,18 @@
       <c r="R66" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S66" t="str">
+        <f>VLOOKUP(C66,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T66" t="str">
+        <f>VLOOKUP(C66,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B67" s="2" t="str">
         <f t="shared" si="5"/>
@@ -4813,7 +5740,7 @@
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H67" s="1">
         <v>46023</v>
@@ -4848,10 +5775,18 @@
       <c r="R67" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S67" t="str">
+        <f>VLOOKUP(C67,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T67" t="str">
+        <f>VLOOKUP(C67,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B68" s="2" t="str">
         <f t="shared" ref="B68:B69" si="6">C68&amp;"_"&amp;J68&amp;"_"&amp;K68&amp;"_"&amp;L68</f>
@@ -4867,7 +5802,7 @@
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H68" s="1">
         <v>46023</v>
@@ -4902,10 +5837,18 @@
       <c r="R68" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S68" t="str">
+        <f>VLOOKUP(C68,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T68" t="str">
+        <f>VLOOKUP(C68,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B69" s="2" t="str">
         <f t="shared" si="6"/>
@@ -4921,7 +5864,7 @@
         <v>27</v>
       </c>
       <c r="F69" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H69" s="1">
         <v>46023</v>
@@ -4956,10 +5899,18 @@
       <c r="R69" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S69" t="str">
+        <f>VLOOKUP(C69,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T69" t="str">
+        <f>VLOOKUP(C69,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B70" s="2" t="str">
         <f t="shared" ref="B70:B75" si="7">C70&amp;"_"&amp;J70&amp;"_"&amp;K70&amp;"_"&amp;L70</f>
@@ -4975,7 +5926,7 @@
         <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H70" s="1">
         <v>46023</v>
@@ -5010,10 +5961,18 @@
       <c r="R70" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S70" t="str">
+        <f>VLOOKUP(C70,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T70" t="str">
+        <f>VLOOKUP(C70,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B71" s="2" t="str">
         <f t="shared" si="7"/>
@@ -5029,7 +5988,7 @@
         <v>27</v>
       </c>
       <c r="F71" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H71" s="1">
         <v>46023</v>
@@ -5064,10 +6023,18 @@
       <c r="R71" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S71" t="str">
+        <f>VLOOKUP(C71,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T71" t="str">
+        <f>VLOOKUP(C71,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B72" s="2" t="str">
         <f t="shared" ref="B72:B74" si="8">C72&amp;"_"&amp;J72&amp;"_"&amp;K72&amp;"_"&amp;L72</f>
@@ -5083,7 +6050,7 @@
         <v>27</v>
       </c>
       <c r="F72" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H72" s="1">
         <v>46023</v>
@@ -5118,10 +6085,18 @@
       <c r="R72" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S72" t="str">
+        <f>VLOOKUP(C72,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T72" t="str">
+        <f>VLOOKUP(C72,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B73" s="2" t="str">
         <f t="shared" si="8"/>
@@ -5137,7 +6112,7 @@
         <v>30</v>
       </c>
       <c r="F73" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H73" s="1">
         <v>46023</v>
@@ -5172,10 +6147,18 @@
       <c r="R73" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S73" t="str">
+        <f>VLOOKUP(C73,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T73" t="str">
+        <f>VLOOKUP(C73,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B74" s="2" t="str">
         <f t="shared" si="8"/>
@@ -5191,7 +6174,7 @@
         <v>30</v>
       </c>
       <c r="F74" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H74" s="1">
         <v>46023</v>
@@ -5226,10 +6209,18 @@
       <c r="R74" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S74" t="str">
+        <f>VLOOKUP(C74,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T74" t="str">
+        <f>VLOOKUP(C74,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B75" s="2" t="str">
         <f t="shared" si="7"/>
@@ -5245,7 +6236,7 @@
         <v>30</v>
       </c>
       <c r="F75" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H75" s="1">
         <v>46023</v>
@@ -5280,10 +6271,18 @@
       <c r="R75" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S75" t="str">
+        <f>VLOOKUP(C75,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T75" t="str">
+        <f>VLOOKUP(C75,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B76" s="2" t="str">
         <f t="shared" ref="B76:B77" si="9">C76&amp;"_"&amp;J76&amp;"_"&amp;K76&amp;"_"&amp;L76</f>
@@ -5299,7 +6298,7 @@
         <v>30</v>
       </c>
       <c r="F76" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H76" s="1">
         <v>46023</v>
@@ -5334,10 +6333,18 @@
       <c r="R76" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S76" t="str">
+        <f>VLOOKUP(C76,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T76" t="str">
+        <f>VLOOKUP(C76,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>m</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B77" s="2" t="str">
         <f t="shared" si="9"/>
@@ -5353,7 +6360,7 @@
         <v>24</v>
       </c>
       <c r="F77" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H77" s="1">
         <v>46023</v>
@@ -5388,10 +6395,18 @@
       <c r="R77" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S77" t="str">
+        <f>VLOOKUP(C77,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T77" t="str">
+        <f>VLOOKUP(C77,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B78" s="2" t="str">
         <f t="shared" ref="B78:B84" si="10">C78&amp;"_"&amp;J78&amp;"_"&amp;K78&amp;"_"&amp;L78</f>
@@ -5407,7 +6422,7 @@
         <v>24</v>
       </c>
       <c r="F78" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H78" s="1">
         <v>46023</v>
@@ -5442,10 +6457,18 @@
       <c r="R78" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S78" t="str">
+        <f>VLOOKUP(C78,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T78" t="str">
+        <f>VLOOKUP(C78,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B79" s="2" t="str">
         <f t="shared" si="10"/>
@@ -5461,7 +6484,7 @@
         <v>24</v>
       </c>
       <c r="F79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H79" s="1">
         <v>46023</v>
@@ -5496,10 +6519,18 @@
       <c r="R79" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S79" t="str">
+        <f>VLOOKUP(C79,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T79" t="str">
+        <f>VLOOKUP(C79,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B80" s="2" t="str">
         <f t="shared" si="10"/>
@@ -5515,7 +6546,7 @@
         <v>24</v>
       </c>
       <c r="F80" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H80" s="1">
         <v>46023</v>
@@ -5550,10 +6581,18 @@
       <c r="R80" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S80" t="str">
+        <f>VLOOKUP(C80,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T80" t="str">
+        <f>VLOOKUP(C80,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B81" s="2" t="str">
         <f t="shared" si="10"/>
@@ -5569,7 +6608,7 @@
         <v>24</v>
       </c>
       <c r="F81" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H81" s="1">
         <v>46023</v>
@@ -5604,10 +6643,18 @@
       <c r="R81" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S81" t="str">
+        <f>VLOOKUP(C81,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T81" t="str">
+        <f>VLOOKUP(C81,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B82" s="2" t="str">
         <f t="shared" si="10"/>
@@ -5623,7 +6670,7 @@
         <v>24</v>
       </c>
       <c r="F82" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H82" s="1">
         <v>46023</v>
@@ -5658,10 +6705,18 @@
       <c r="R82" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S82" t="str">
+        <f>VLOOKUP(C82,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T82" t="str">
+        <f>VLOOKUP(C82,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B83" s="2" t="str">
         <f t="shared" si="10"/>
@@ -5677,7 +6732,7 @@
         <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H83" s="1">
         <v>46023</v>
@@ -5712,10 +6767,18 @@
       <c r="R83" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S83" t="str">
+        <f>VLOOKUP(C83,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T83" t="str">
+        <f>VLOOKUP(C83,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B84" s="2" t="str">
         <f t="shared" si="10"/>
@@ -5731,7 +6794,7 @@
         <v>24</v>
       </c>
       <c r="F84" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H84" s="1">
         <v>46023</v>
@@ -5766,10 +6829,18 @@
       <c r="R84" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S84" t="str">
+        <f>VLOOKUP(C84,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T84" t="str">
+        <f>VLOOKUP(C84,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B85" s="2" t="str">
         <f>C85&amp;"_"&amp;J85&amp;"_"&amp;K85&amp;"_"&amp;L85</f>
@@ -5785,7 +6856,7 @@
         <v>19</v>
       </c>
       <c r="F85" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H85" s="1">
         <v>46023</v>
@@ -5820,10 +6891,18 @@
       <c r="R85" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S85" t="str">
+        <f>VLOOKUP(C85,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T85" t="str">
+        <f>VLOOKUP(C85,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B86" s="2" t="str">
         <f t="shared" ref="B86:B89" si="11">C86&amp;"_"&amp;J86&amp;"_"&amp;K86&amp;"_"&amp;L86</f>
@@ -5839,7 +6918,7 @@
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H86" s="1">
         <v>46023</v>
@@ -5874,10 +6953,18 @@
       <c r="R86" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S86" t="str">
+        <f>VLOOKUP(C86,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T86" t="str">
+        <f>VLOOKUP(C86,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B87" s="2" t="str">
         <f t="shared" si="11"/>
@@ -5893,7 +6980,7 @@
         <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H87" s="1">
         <v>46023</v>
@@ -5928,10 +7015,18 @@
       <c r="R87" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S87" t="str">
+        <f>VLOOKUP(C87,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T87" t="str">
+        <f>VLOOKUP(C87,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B88" s="2" t="str">
         <f t="shared" si="11"/>
@@ -5947,7 +7042,7 @@
         <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H88" s="1">
         <v>46023</v>
@@ -5982,10 +7077,18 @@
       <c r="R88" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S88" t="str">
+        <f>VLOOKUP(C88,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T88" t="str">
+        <f>VLOOKUP(C88,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B89" s="2" t="str">
         <f t="shared" si="11"/>
@@ -6001,7 +7104,7 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H89" s="1">
         <v>46023</v>
@@ -6036,10 +7139,18 @@
       <c r="R89" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S89" t="str">
+        <f>VLOOKUP(C89,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T89" t="str">
+        <f>VLOOKUP(C89,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B90" s="2" t="str">
         <f>C90&amp;"_"&amp;J90&amp;"_"&amp;K90&amp;"_"&amp;L90</f>
@@ -6055,7 +7166,7 @@
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H90" s="1">
         <v>46023</v>
@@ -6090,10 +7201,18 @@
       <c r="R90" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S90" t="str">
+        <f>VLOOKUP(C90,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T90" t="str">
+        <f>VLOOKUP(C90,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B91" s="2" t="str">
         <f t="shared" ref="B91:B103" si="12">C91&amp;"_"&amp;J91&amp;"_"&amp;K91&amp;"_"&amp;L91</f>
@@ -6109,7 +7228,7 @@
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H91" s="1">
         <v>46023</v>
@@ -6144,10 +7263,18 @@
       <c r="R91" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S91" t="str">
+        <f>VLOOKUP(C91,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T91" t="str">
+        <f>VLOOKUP(C91,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B92" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6163,7 +7290,7 @@
         <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H92" s="1">
         <v>46023</v>
@@ -6198,10 +7325,18 @@
       <c r="R92" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S92" t="str">
+        <f>VLOOKUP(C92,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T92" t="str">
+        <f>VLOOKUP(C92,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B93" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6217,7 +7352,7 @@
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H93" s="1">
         <v>46023</v>
@@ -6252,10 +7387,18 @@
       <c r="R93" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S93" t="str">
+        <f>VLOOKUP(C93,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T93" t="str">
+        <f>VLOOKUP(C93,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B94" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6271,7 +7414,7 @@
         <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H94" s="1">
         <v>46023</v>
@@ -6306,10 +7449,18 @@
       <c r="R94" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S94" t="str">
+        <f>VLOOKUP(C94,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T94" t="str">
+        <f>VLOOKUP(C94,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B95" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6325,7 +7476,7 @@
         <v>24</v>
       </c>
       <c r="F95" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H95" s="1">
         <v>46023</v>
@@ -6360,10 +7511,18 @@
       <c r="R95" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S95" t="str">
+        <f>VLOOKUP(C95,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T95" t="str">
+        <f>VLOOKUP(C95,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B96" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6379,7 +7538,7 @@
         <v>24</v>
       </c>
       <c r="F96" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H96" s="1">
         <v>46023</v>
@@ -6414,10 +7573,18 @@
       <c r="R96" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S96" t="str">
+        <f>VLOOKUP(C96,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T96" t="str">
+        <f>VLOOKUP(C96,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B97" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6433,7 +7600,7 @@
         <v>24</v>
       </c>
       <c r="F97" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H97" s="1">
         <v>46023</v>
@@ -6468,10 +7635,18 @@
       <c r="R97" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S97" t="str">
+        <f>VLOOKUP(C97,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T97" t="str">
+        <f>VLOOKUP(C97,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B98" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6487,7 +7662,7 @@
         <v>24</v>
       </c>
       <c r="F98" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H98" s="1">
         <v>46023</v>
@@ -6522,10 +7697,18 @@
       <c r="R98" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S98" t="str">
+        <f>VLOOKUP(C98,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T98" t="str">
+        <f>VLOOKUP(C98,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B99" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6541,7 +7724,7 @@
         <v>24</v>
       </c>
       <c r="F99" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H99" s="1">
         <v>46023</v>
@@ -6576,10 +7759,18 @@
       <c r="R99" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S99" t="str">
+        <f>VLOOKUP(C99,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T99" t="str">
+        <f>VLOOKUP(C99,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B100" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6595,7 +7786,7 @@
         <v>24</v>
       </c>
       <c r="F100" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H100" s="1">
         <v>46023</v>
@@ -6630,10 +7821,18 @@
       <c r="R100" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S100" t="str">
+        <f>VLOOKUP(C100,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T100" t="str">
+        <f>VLOOKUP(C100,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B101" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6649,7 +7848,7 @@
         <v>24</v>
       </c>
       <c r="F101" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H101" s="1">
         <v>46023</v>
@@ -6684,10 +7883,18 @@
       <c r="R101" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S101" t="str">
+        <f>VLOOKUP(C101,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T101" t="str">
+        <f>VLOOKUP(C101,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B102" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6703,7 +7910,7 @@
         <v>24</v>
       </c>
       <c r="F102" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H102" s="1">
         <v>46023</v>
@@ -6738,10 +7945,18 @@
       <c r="R102" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S102" t="str">
+        <f>VLOOKUP(C102,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T102" t="str">
+        <f>VLOOKUP(C102,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>percent</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B103" s="2" t="str">
         <f t="shared" si="12"/>
@@ -6757,7 +7972,7 @@
         <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H103" s="1">
         <v>46023</v>
@@ -6792,10 +8007,18 @@
       <c r="R103" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S103" t="str">
+        <f>VLOOKUP(C103,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="T103" t="str">
+        <f>VLOOKUP(C103,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B104" s="2" t="str">
         <f t="shared" ref="B104" si="13">C104&amp;"_"&amp;J104&amp;"_"&amp;K104&amp;"_"&amp;L104</f>
@@ -6811,7 +8034,7 @@
         <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H104" s="1">
         <v>46023</v>
@@ -6845,6 +8068,14 @@
       </c>
       <c r="R104" t="s">
         <v>21</v>
+      </c>
+      <c r="S104" t="str">
+        <f>VLOOKUP(C104,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="T104" t="str">
+        <f>VLOOKUP(C104,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+        <v>degree_C</v>
       </c>
     </row>
   </sheetData>
@@ -6854,4 +8085,1893 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="120" verticalDpi="72" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B6FF77-C883-40C9-8616-F79923CDA0A3}">
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr defaultRowHeight="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" t="s">
+        <v>134</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" t="str">
+        <f>VLOOKUP(A2,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>sd</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="str">
+        <f>VLOOKUP(A3,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>time</v>
+      </c>
+      <c r="N3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>-20</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="str">
+        <f>VLOOKUP(A4,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1200</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>144</v>
+      </c>
+      <c r="K5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="str">
+        <f>VLOOKUP(A5,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>strd</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K6" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="str">
+        <f>VLOOKUP(A6,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stru</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" t="str">
+        <f>VLOOKUP(A7,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rh</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>500</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" t="str">
+        <f>VLOOKUP(A8,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>500</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" t="s">
+        <v>156</v>
+      </c>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" t="str">
+        <f>VLOOKUP(A9,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>500</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" t="s">
+        <v>156</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" t="str">
+        <f>VLOOKUP(A10,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>500</v>
+      </c>
+      <c r="D11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" t="str">
+        <f>VLOOKUP(A11,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" t="str">
+        <f>VLOOKUP(A12,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>tp</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>90</v>
+      </c>
+      <c r="C13">
+        <v>130</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" t="str">
+        <f>VLOOKUP(A13,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>sp</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="O13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>2200</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="str">
+        <f>VLOOKUP(A14,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>fdif</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>2200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15" t="str">
+        <f>VLOOKUP(A15,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>2200</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" t="s">
+        <v>169</v>
+      </c>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" t="s">
+        <v>170</v>
+      </c>
+      <c r="K16" t="s">
+        <v>171</v>
+      </c>
+      <c r="L16" t="s">
+        <v>172</v>
+      </c>
+      <c r="M16" t="str">
+        <f>VLOOKUP(A16,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1200</v>
+      </c>
+      <c r="D17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" t="str">
+        <f>VLOOKUP(A17,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>120</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" t="str">
+        <f>VLOOKUP(A18,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19">
+        <v>-500</v>
+      </c>
+      <c r="C19">
+        <v>1200</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" t="s">
+        <v>178</v>
+      </c>
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="str">
+        <f>VLOOKUP(A19,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>rn</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="O19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>1200</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" t="s">
+        <v>181</v>
+      </c>
+      <c r="K20" t="s">
+        <v>182</v>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" t="str">
+        <f>VLOOKUP(A20,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>300</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" t="s">
+        <v>184</v>
+      </c>
+      <c r="K21" t="s">
+        <v>185</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" t="str">
+        <f>VLOOKUP(A21,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ssru</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>45</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" t="s">
+        <v>186</v>
+      </c>
+      <c r="K22" t="s">
+        <v>187</v>
+      </c>
+      <c r="L22" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" t="str">
+        <f>VLOOKUP(A22,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23">
+        <v>-40</v>
+      </c>
+      <c r="C23">
+        <v>50</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
+        <v>191</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" t="str">
+        <f>VLOOKUP(A23,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="O23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>-20</v>
+      </c>
+      <c r="C24">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" t="s">
+        <v>194</v>
+      </c>
+      <c r="K24" t="s">
+        <v>195</v>
+      </c>
+      <c r="L24" t="s">
+        <v>193</v>
+      </c>
+      <c r="M24" t="str">
+        <f>VLOOKUP(A24,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="O24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>360</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>198</v>
+      </c>
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
+        <v>198</v>
+      </c>
+      <c r="L25" t="s">
+        <v>198</v>
+      </c>
+      <c r="M25" t="str">
+        <f>VLOOKUP(A25,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>wd</v>
+      </c>
+      <c r="O25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" t="str">
+        <f>VLOOKUP(A26,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>ws</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="O26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27">
+        <v>-10</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
+        <v>30</v>
+      </c>
+      <c r="J27" t="s">
+        <v>200</v>
+      </c>
+      <c r="K27" t="s">
+        <v>201</v>
+      </c>
+      <c r="L27" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" t="str">
+        <f>VLOOKUP(A27,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF29616-2603-4811-AA75-C70B902F2583}">
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="43.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E18" t="s">
+        <v>212</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" t="s">
+        <v>216</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" t="s">
+        <v>188</v>
+      </c>
+      <c r="F27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>221</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>175</v>
+      </c>
+      <c r="E29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" t="s">
+        <v>222</v>
+      </c>
+      <c r="F32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" t="s">
+        <v>225</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>175</v>
+      </c>
+      <c r="E33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" t="s">
+        <v>209</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>176</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\tests\testthat\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2686426E-7F9E-4404-AE29-61B6EB8DD53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708A3F8C-FC06-459C-884D-3F89252C3824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
   <sheets>
     <sheet name="dt_meta" sheetId="1" r:id="rId1"/>
-    <sheet name="dt_var_naming" sheetId="2" r:id="rId2"/>
-    <sheet name="naming_lookup" sheetId="3" r:id="rId3"/>
+    <sheet name="naming_lookup" sheetId="3" r:id="rId2"/>
+    <sheet name="dt_var_naming" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="231">
   <si>
     <t>name_dt</t>
   </si>
@@ -1663,7 +1663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B621CE1-A4D4-4502-917D-92507EE2F7EE}">
-  <dimension ref="A1:T104"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -1673,7 +1673,7 @@
     <col min="8" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -1729,13 +1729,19 @@
         <v>14</v>
       </c>
       <c r="S1" t="s">
+        <v>122</v>
+      </c>
+      <c r="T1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U1" t="s">
         <v>130</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>118</v>
       </c>
@@ -1785,15 +1791,24 @@
       <c r="R2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" t="str">
-        <f>VLOOKUP(C2,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="S2" t="e">
+        <f>VLOOKUP($C2,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="T2" t="e">
+        <f>VLOOKUP($C2,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="U2" t="str">
+        <f>VLOOKUP($C2,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>site</v>
+      </c>
+      <c r="V2" t="str">
+        <f>VLOOKUP($C2,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>NA</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -1845,16 +1860,24 @@
       <c r="R3" t="s">
         <v>21</v>
       </c>
-      <c r="S3" t="str">
-        <f>VLOOKUP(C3,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S3">
+        <f>VLOOKUP($C3,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f>VLOOKUP($C3,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U3" t="str">
+        <f>VLOOKUP($C3,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>sd</v>
       </c>
-      <c r="T3" t="str">
-        <f>VLOOKUP(C3,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V3" t="str">
+        <f>VLOOKUP($C3,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>cm</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -1906,16 +1929,24 @@
       <c r="R4" t="s">
         <v>21</v>
       </c>
-      <c r="S4" t="str">
-        <f>VLOOKUP(C4,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S4">
+        <f>VLOOKUP($C4,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f>VLOOKUP($C4,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U4" t="str">
+        <f>VLOOKUP($C4,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>sd</v>
       </c>
-      <c r="T4" t="str">
-        <f>VLOOKUP(C4,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V4" t="str">
+        <f>VLOOKUP($C4,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>cm</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -1967,16 +1998,24 @@
       <c r="R5" t="s">
         <v>16</v>
       </c>
-      <c r="S5" t="str">
-        <f>VLOOKUP(C5,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S5">
+        <f>VLOOKUP($C5,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f>VLOOKUP($C5,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U5" t="str">
+        <f>VLOOKUP($C5,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>time</v>
       </c>
-      <c r="T5" t="str">
-        <f>VLOOKUP(C5,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V5" t="str">
+        <f>VLOOKUP($C5,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>NA</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -2028,16 +2067,24 @@
       <c r="R6" t="s">
         <v>21</v>
       </c>
-      <c r="S6" t="str">
-        <f>VLOOKUP(C6,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S6">
+        <f>VLOOKUP($C6,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="T6">
+        <f>VLOOKUP($C6,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U6" t="str">
+        <f>VLOOKUP($C6,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T6" t="str">
-        <f>VLOOKUP(C6,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V6" t="str">
+        <f>VLOOKUP($C6,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>118</v>
       </c>
@@ -2089,16 +2136,24 @@
       <c r="R7" t="s">
         <v>21</v>
       </c>
-      <c r="S7" t="str">
-        <f>VLOOKUP(C7,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S7">
+        <f>VLOOKUP($C7,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="T7">
+        <f>VLOOKUP($C7,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U7" t="str">
+        <f>VLOOKUP($C7,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T7" t="str">
-        <f>VLOOKUP(C7,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V7" t="str">
+        <f>VLOOKUP($C7,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>118</v>
       </c>
@@ -2150,16 +2205,24 @@
       <c r="R8" t="s">
         <v>21</v>
       </c>
-      <c r="S8" t="str">
-        <f>VLOOKUP(C8,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S8">
+        <f>VLOOKUP($C8,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="T8">
+        <f>VLOOKUP($C8,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U8" t="str">
+        <f>VLOOKUP($C8,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T8" t="str">
-        <f>VLOOKUP(C8,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V8" t="str">
+        <f>VLOOKUP($C8,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>118</v>
       </c>
@@ -2211,16 +2274,24 @@
       <c r="R9" t="s">
         <v>21</v>
       </c>
-      <c r="S9" t="str">
-        <f>VLOOKUP(C9,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S9">
+        <f>VLOOKUP($C9,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <f>VLOOKUP($C9,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U9" t="str">
+        <f>VLOOKUP($C9,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>strd</v>
       </c>
-      <c r="T9" t="str">
-        <f>VLOOKUP(C9,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V9" t="str">
+        <f>VLOOKUP($C9,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -2272,16 +2343,24 @@
       <c r="R10" t="s">
         <v>21</v>
       </c>
-      <c r="S10" t="str">
-        <f>VLOOKUP(C10,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S10">
+        <f>VLOOKUP($C10,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f>VLOOKUP($C10,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U10" t="str">
+        <f>VLOOKUP($C10,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>strd</v>
       </c>
-      <c r="T10" t="str">
-        <f>VLOOKUP(C10,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V10" t="str">
+        <f>VLOOKUP($C10,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -2333,16 +2412,24 @@
       <c r="R11" t="s">
         <v>21</v>
       </c>
-      <c r="S11" t="str">
-        <f>VLOOKUP(C11,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S11">
+        <f>VLOOKUP($C11,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f>VLOOKUP($C11,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="U11" t="str">
+        <f>VLOOKUP($C11,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stru</v>
       </c>
-      <c r="T11" t="str">
-        <f>VLOOKUP(C11,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V11" t="str">
+        <f>VLOOKUP($C11,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -2394,16 +2481,24 @@
       <c r="R12" t="s">
         <v>21</v>
       </c>
-      <c r="S12" t="str">
-        <f>VLOOKUP(C12,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S12">
+        <f>VLOOKUP($C12,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <f>VLOOKUP($C12,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="U12" t="str">
+        <f>VLOOKUP($C12,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stru</v>
       </c>
-      <c r="T12" t="str">
-        <f>VLOOKUP(C12,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V12" t="str">
+        <f>VLOOKUP($C12,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>118</v>
       </c>
@@ -2455,16 +2550,24 @@
       <c r="R13" t="s">
         <v>21</v>
       </c>
-      <c r="S13" t="str">
-        <f>VLOOKUP(C13,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S13">
+        <f>VLOOKUP($C13,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-99999</v>
+      </c>
+      <c r="T13">
+        <f>VLOOKUP($C13,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>99999</v>
+      </c>
+      <c r="U13" t="str">
+        <f>VLOOKUP($C13,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>rh</v>
       </c>
-      <c r="T13">
-        <f>VLOOKUP(C13,naming_lookup!$C$1:$F$40,4,FALSE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="V13">
+        <f>VLOOKUP($C13,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -2516,16 +2619,24 @@
       <c r="R14" t="s">
         <v>21</v>
       </c>
-      <c r="S14" t="str">
-        <f>VLOOKUP(C14,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S14">
+        <f>VLOOKUP($C14,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-99999</v>
+      </c>
+      <c r="T14">
+        <f>VLOOKUP($C14,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>99999</v>
+      </c>
+      <c r="U14" t="str">
+        <f>VLOOKUP($C14,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>rh</v>
       </c>
-      <c r="T14">
-        <f>VLOOKUP(C14,naming_lookup!$C$1:$F$40,4,FALSE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="V14">
+        <f>VLOOKUP($C14,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -2577,16 +2688,24 @@
       <c r="R15" t="s">
         <v>21</v>
       </c>
-      <c r="S15" t="str">
-        <f>VLOOKUP(C15,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S15">
+        <f>VLOOKUP($C15,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f>VLOOKUP($C15,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U15" t="str">
+        <f>VLOOKUP($C15,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T15" t="str">
-        <f>VLOOKUP(C15,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V15" t="str">
+        <f>VLOOKUP($C15,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -2638,16 +2757,24 @@
       <c r="R16" t="s">
         <v>21</v>
       </c>
-      <c r="S16" t="str">
-        <f>VLOOKUP(C16,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S16">
+        <f>VLOOKUP($C16,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <f>VLOOKUP($C16,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U16" t="str">
+        <f>VLOOKUP($C16,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssru</v>
       </c>
-      <c r="T16" t="str">
-        <f>VLOOKUP(C16,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V16" t="str">
+        <f>VLOOKUP($C16,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -2699,16 +2826,24 @@
       <c r="R17" t="s">
         <v>21</v>
       </c>
-      <c r="S17" t="str">
-        <f>VLOOKUP(C17,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S17">
+        <f>VLOOKUP($C17,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <f>VLOOKUP($C17,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U17" t="str">
+        <f>VLOOKUP($C17,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T17" t="str">
-        <f>VLOOKUP(C17,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V17" t="str">
+        <f>VLOOKUP($C17,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -2760,16 +2895,24 @@
       <c r="R18" t="s">
         <v>21</v>
       </c>
-      <c r="S18" t="str">
-        <f>VLOOKUP(C18,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S18">
+        <f>VLOOKUP($C18,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <f>VLOOKUP($C18,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U18" t="str">
+        <f>VLOOKUP($C18,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssru</v>
       </c>
-      <c r="T18" t="str">
-        <f>VLOOKUP(C18,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V18" t="str">
+        <f>VLOOKUP($C18,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -2821,16 +2964,24 @@
       <c r="R19" t="s">
         <v>21</v>
       </c>
-      <c r="S19" t="str">
-        <f>VLOOKUP(C19,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S19">
+        <f>VLOOKUP($C19,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <f>VLOOKUP($C19,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U19" t="str">
+        <f>VLOOKUP($C19,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>tp</v>
       </c>
-      <c r="T19" t="str">
-        <f>VLOOKUP(C19,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V19" t="str">
+        <f>VLOOKUP($C19,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>mm</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -2882,16 +3033,24 @@
       <c r="R20" t="s">
         <v>21</v>
       </c>
-      <c r="S20" t="str">
-        <f>VLOOKUP(C20,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S20">
+        <f>VLOOKUP($C20,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f>VLOOKUP($C20,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U20" t="str">
+        <f>VLOOKUP($C20,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>tp</v>
       </c>
-      <c r="T20" t="str">
-        <f>VLOOKUP(C20,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V20" t="str">
+        <f>VLOOKUP($C20,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>mm</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>118</v>
       </c>
@@ -2943,16 +3102,24 @@
       <c r="R21" t="s">
         <v>21</v>
       </c>
-      <c r="S21" t="str">
-        <f>VLOOKUP(C21,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S21">
+        <f>VLOOKUP($C21,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>90</v>
+      </c>
+      <c r="T21">
+        <f>VLOOKUP($C21,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>130</v>
+      </c>
+      <c r="U21" t="str">
+        <f>VLOOKUP($C21,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>sp</v>
       </c>
-      <c r="T21" t="str">
-        <f>VLOOKUP(C21,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V21" t="str">
+        <f>VLOOKUP($C21,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>kPa</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>118</v>
       </c>
@@ -3004,16 +3171,24 @@
       <c r="R22" t="s">
         <v>21</v>
       </c>
-      <c r="S22" t="str">
-        <f>VLOOKUP(C22,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S22">
+        <f>VLOOKUP($C22,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <f>VLOOKUP($C22,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U22" t="str">
+        <f>VLOOKUP($C22,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>fdif</v>
       </c>
-      <c r="T22" t="str">
-        <f>VLOOKUP(C22,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V22" t="str">
+        <f>VLOOKUP($C22,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -3065,16 +3240,24 @@
       <c r="R23" t="s">
         <v>21</v>
       </c>
-      <c r="S23" t="str">
-        <f>VLOOKUP(C23,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S23">
+        <f>VLOOKUP($C23,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <f>VLOOKUP($C23,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U23" t="str">
+        <f>VLOOKUP($C23,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>fdif</v>
       </c>
-      <c r="T23" t="str">
-        <f>VLOOKUP(C23,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V23" t="str">
+        <f>VLOOKUP($C23,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -3126,16 +3309,24 @@
       <c r="R24" t="s">
         <v>21</v>
       </c>
-      <c r="S24" t="str">
-        <f>VLOOKUP(C24,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S24">
+        <f>VLOOKUP($C24,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <f>VLOOKUP($C24,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U24" t="str">
+        <f>VLOOKUP($C24,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T24" t="str">
-        <f>VLOOKUP(C24,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V24" t="str">
+        <f>VLOOKUP($C24,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -3187,16 +3378,24 @@
       <c r="R25" t="s">
         <v>21</v>
       </c>
-      <c r="S25" t="str">
-        <f>VLOOKUP(C25,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S25">
+        <f>VLOOKUP($C25,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <f>VLOOKUP($C25,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U25" t="str">
+        <f>VLOOKUP($C25,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T25" t="str">
-        <f>VLOOKUP(C25,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V25" t="str">
+        <f>VLOOKUP($C25,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -3248,16 +3447,24 @@
       <c r="R26" t="s">
         <v>21</v>
       </c>
-      <c r="S26" t="str">
-        <f>VLOOKUP(C26,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S26">
+        <f>VLOOKUP($C26,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f>VLOOKUP($C26,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U26" t="str">
+        <f>VLOOKUP($C26,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T26" t="str">
-        <f>VLOOKUP(C26,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V26" t="str">
+        <f>VLOOKUP($C26,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -3309,16 +3516,24 @@
       <c r="R27" t="s">
         <v>21</v>
       </c>
-      <c r="S27" t="str">
-        <f>VLOOKUP(C27,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S27">
+        <f>VLOOKUP($C27,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f>VLOOKUP($C27,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U27" t="str">
+        <f>VLOOKUP($C27,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssru</v>
       </c>
-      <c r="T27" t="str">
-        <f>VLOOKUP(C27,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V27" t="str">
+        <f>VLOOKUP($C27,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -3370,16 +3585,24 @@
       <c r="R28" t="s">
         <v>21</v>
       </c>
-      <c r="S28" t="str">
-        <f>VLOOKUP(C28,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S28">
+        <f>VLOOKUP($C28,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f>VLOOKUP($C28,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U28" t="str">
+        <f>VLOOKUP($C28,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssru</v>
       </c>
-      <c r="T28" t="str">
-        <f>VLOOKUP(C28,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V28" t="str">
+        <f>VLOOKUP($C28,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -3431,16 +3654,24 @@
       <c r="R29" t="s">
         <v>21</v>
       </c>
-      <c r="S29" t="str">
-        <f>VLOOKUP(C29,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S29">
+        <f>VLOOKUP($C29,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <f>VLOOKUP($C29,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U29" t="str">
+        <f>VLOOKUP($C29,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T29" t="str">
-        <f>VLOOKUP(C29,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V29" t="str">
+        <f>VLOOKUP($C29,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>118</v>
       </c>
@@ -3493,16 +3724,24 @@
       <c r="R30" t="s">
         <v>21</v>
       </c>
-      <c r="S30" t="str">
-        <f>VLOOKUP(C30,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S30">
+        <f>VLOOKUP($C30,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="T30">
+        <f>VLOOKUP($C30,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>120</v>
+      </c>
+      <c r="U30" t="str">
+        <f>VLOOKUP($C30,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>rh</v>
       </c>
-      <c r="T30" t="str">
-        <f>VLOOKUP(C30,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V30" t="str">
+        <f>VLOOKUP($C30,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>118</v>
       </c>
@@ -3555,16 +3794,24 @@
       <c r="R31" t="s">
         <v>21</v>
       </c>
-      <c r="S31" t="str">
-        <f>VLOOKUP(C31,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S31">
+        <f>VLOOKUP($C31,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="T31">
+        <f>VLOOKUP($C31,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>120</v>
+      </c>
+      <c r="U31" t="str">
+        <f>VLOOKUP($C31,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>rh</v>
       </c>
-      <c r="T31" t="str">
-        <f>VLOOKUP(C31,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V31" t="str">
+        <f>VLOOKUP($C31,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -3617,16 +3864,24 @@
       <c r="R32" t="s">
         <v>21</v>
       </c>
-      <c r="S32" t="str">
-        <f>VLOOKUP(C32,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S32">
+        <f>VLOOKUP($C32,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="T32">
+        <f>VLOOKUP($C32,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>120</v>
+      </c>
+      <c r="U32" t="str">
+        <f>VLOOKUP($C32,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>rh</v>
       </c>
-      <c r="T32" t="str">
-        <f>VLOOKUP(C32,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V32" t="str">
+        <f>VLOOKUP($C32,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -3679,16 +3934,24 @@
       <c r="R33" t="s">
         <v>21</v>
       </c>
-      <c r="S33" t="str">
-        <f>VLOOKUP(C33,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S33">
+        <f>VLOOKUP($C33,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-500</v>
+      </c>
+      <c r="T33">
+        <f>VLOOKUP($C33,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U33" t="str">
+        <f>VLOOKUP($C33,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>rn</v>
       </c>
-      <c r="T33" t="str">
-        <f>VLOOKUP(C33,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V33" t="str">
+        <f>VLOOKUP($C33,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -3740,16 +4003,24 @@
       <c r="R34" t="s">
         <v>21</v>
       </c>
-      <c r="S34" t="str">
-        <f>VLOOKUP(C34,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S34">
+        <f>VLOOKUP($C34,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <f>VLOOKUP($C34,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U34" t="str">
+        <f>VLOOKUP($C34,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T34" t="str">
-        <f>VLOOKUP(C34,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V34" t="str">
+        <f>VLOOKUP($C34,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>118</v>
       </c>
@@ -3802,16 +4073,24 @@
       <c r="R35" t="s">
         <v>21</v>
       </c>
-      <c r="S35" t="str">
-        <f>VLOOKUP(C35,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S35">
+        <f>VLOOKUP($C35,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <f>VLOOKUP($C35,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U35" t="str">
+        <f>VLOOKUP($C35,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T35" t="str">
-        <f>VLOOKUP(C35,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V35" t="str">
+        <f>VLOOKUP($C35,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>118</v>
       </c>
@@ -3864,16 +4143,24 @@
       <c r="R36" t="s">
         <v>21</v>
       </c>
-      <c r="S36" t="str">
-        <f>VLOOKUP(C36,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S36">
+        <f>VLOOKUP($C36,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <f>VLOOKUP($C36,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U36" t="str">
+        <f>VLOOKUP($C36,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T36" t="str">
-        <f>VLOOKUP(C36,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V36" t="str">
+        <f>VLOOKUP($C36,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -3925,16 +4212,24 @@
       <c r="R37" t="s">
         <v>21</v>
       </c>
-      <c r="S37" t="str">
-        <f>VLOOKUP(C37,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S37">
+        <f>VLOOKUP($C37,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <f>VLOOKUP($C37,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>300</v>
+      </c>
+      <c r="U37" t="str">
+        <f>VLOOKUP($C37,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssru</v>
       </c>
-      <c r="T37" t="str">
-        <f>VLOOKUP(C37,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V37" t="str">
+        <f>VLOOKUP($C37,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>118</v>
       </c>
@@ -3986,16 +4281,24 @@
       <c r="R38" t="s">
         <v>21</v>
       </c>
-      <c r="S38" t="str">
-        <f>VLOOKUP(C38,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S38">
+        <f>VLOOKUP($C38,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <f>VLOOKUP($C38,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>300</v>
+      </c>
+      <c r="U38" t="str">
+        <f>VLOOKUP($C38,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssru</v>
       </c>
-      <c r="T38" t="str">
-        <f>VLOOKUP(C38,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V38" t="str">
+        <f>VLOOKUP($C38,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>118</v>
       </c>
@@ -4047,16 +4350,24 @@
       <c r="R39" t="s">
         <v>21</v>
       </c>
-      <c r="S39" t="str">
-        <f>VLOOKUP(C39,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S39">
+        <f>VLOOKUP($C39,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <f>VLOOKUP($C39,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U39" t="str">
+        <f>VLOOKUP($C39,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T39" t="str">
-        <f>VLOOKUP(C39,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V39" t="str">
+        <f>VLOOKUP($C39,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>118</v>
       </c>
@@ -4109,16 +4420,24 @@
       <c r="R40" t="s">
         <v>21</v>
       </c>
-      <c r="S40" t="str">
-        <f>VLOOKUP(C40,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S40">
+        <f>VLOOKUP($C40,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <f>VLOOKUP($C40,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U40" t="str">
+        <f>VLOOKUP($C40,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T40" t="str">
-        <f>VLOOKUP(C40,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V40" t="str">
+        <f>VLOOKUP($C40,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>118</v>
       </c>
@@ -4171,16 +4490,24 @@
       <c r="R41" t="s">
         <v>21</v>
       </c>
-      <c r="S41" t="str">
-        <f>VLOOKUP(C41,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S41">
+        <f>VLOOKUP($C41,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <f>VLOOKUP($C41,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U41" t="str">
+        <f>VLOOKUP($C41,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T41" t="str">
-        <f>VLOOKUP(C41,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V41" t="str">
+        <f>VLOOKUP($C41,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>118</v>
       </c>
@@ -4233,16 +4560,24 @@
       <c r="R42" t="s">
         <v>21</v>
       </c>
-      <c r="S42" t="str">
-        <f>VLOOKUP(C42,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S42">
+        <f>VLOOKUP($C42,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <f>VLOOKUP($C42,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U42" t="str">
+        <f>VLOOKUP($C42,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T42" t="str">
-        <f>VLOOKUP(C42,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V42" t="str">
+        <f>VLOOKUP($C42,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>118</v>
       </c>
@@ -4295,16 +4630,24 @@
       <c r="R43" t="s">
         <v>21</v>
       </c>
-      <c r="S43" t="str">
-        <f>VLOOKUP(C43,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S43">
+        <f>VLOOKUP($C43,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <f>VLOOKUP($C43,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U43" t="str">
+        <f>VLOOKUP($C43,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T43" t="str">
-        <f>VLOOKUP(C43,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V43" t="str">
+        <f>VLOOKUP($C43,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>118</v>
       </c>
@@ -4357,16 +4700,24 @@
       <c r="R44" t="s">
         <v>21</v>
       </c>
-      <c r="S44" t="str">
-        <f>VLOOKUP(C44,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S44">
+        <f>VLOOKUP($C44,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="T44">
+        <f>VLOOKUP($C44,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U44" t="str">
+        <f>VLOOKUP($C44,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>t2m</v>
       </c>
-      <c r="T44" t="str">
-        <f>VLOOKUP(C44,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V44" t="str">
+        <f>VLOOKUP($C44,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>118</v>
       </c>
@@ -4419,16 +4770,24 @@
       <c r="R45" t="s">
         <v>21</v>
       </c>
-      <c r="S45" t="str">
-        <f>VLOOKUP(C45,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S45">
+        <f>VLOOKUP($C45,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="T45">
+        <f>VLOOKUP($C45,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U45" t="str">
+        <f>VLOOKUP($C45,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>t2m</v>
       </c>
-      <c r="T45" t="str">
-        <f>VLOOKUP(C45,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V45" t="str">
+        <f>VLOOKUP($C45,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -4481,16 +4840,24 @@
       <c r="R46" t="s">
         <v>21</v>
       </c>
-      <c r="S46" t="str">
-        <f>VLOOKUP(C46,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S46">
+        <f>VLOOKUP($C46,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="T46">
+        <f>VLOOKUP($C46,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U46" t="str">
+        <f>VLOOKUP($C46,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>t2m</v>
       </c>
-      <c r="T46" t="str">
-        <f>VLOOKUP(C46,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V46" t="str">
+        <f>VLOOKUP($C46,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -4542,16 +4909,24 @@
       <c r="R47" t="s">
         <v>16</v>
       </c>
-      <c r="S47" t="str">
-        <f>VLOOKUP(C47,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S47">
+        <f>VLOOKUP($C47,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <f>VLOOKUP($C47,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U47" t="str">
+        <f>VLOOKUP($C47,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>time</v>
       </c>
-      <c r="T47" t="str">
-        <f>VLOOKUP(C47,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V47" t="str">
+        <f>VLOOKUP($C47,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>NA</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>118</v>
       </c>
@@ -4604,16 +4979,24 @@
       <c r="R48" t="s">
         <v>21</v>
       </c>
-      <c r="S48" t="str">
-        <f>VLOOKUP(C48,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S48">
+        <f>VLOOKUP($C48,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <f>VLOOKUP($C48,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>360</v>
+      </c>
+      <c r="U48" t="str">
+        <f>VLOOKUP($C48,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>wd</v>
       </c>
-      <c r="T48" t="str">
-        <f>VLOOKUP(C48,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V48" t="str">
+        <f>VLOOKUP($C48,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>118</v>
       </c>
@@ -4666,16 +5049,24 @@
       <c r="R49" t="s">
         <v>21</v>
       </c>
-      <c r="S49" t="str">
-        <f>VLOOKUP(C49,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S49">
+        <f>VLOOKUP($C49,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <f>VLOOKUP($C49,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U49" t="str">
+        <f>VLOOKUP($C49,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ws</v>
       </c>
-      <c r="T49" t="str">
-        <f>VLOOKUP(C49,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V49" t="str">
+        <f>VLOOKUP($C49,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m / s</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>118</v>
       </c>
@@ -4728,16 +5119,24 @@
       <c r="R50" t="s">
         <v>21</v>
       </c>
-      <c r="S50" t="str">
-        <f>VLOOKUP(C50,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S50">
+        <f>VLOOKUP($C50,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <f>VLOOKUP($C50,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>360</v>
+      </c>
+      <c r="U50" t="str">
+        <f>VLOOKUP($C50,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>wd</v>
       </c>
-      <c r="T50" t="str">
-        <f>VLOOKUP(C50,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V50" t="str">
+        <f>VLOOKUP($C50,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>118</v>
       </c>
@@ -4790,16 +5189,24 @@
       <c r="R51" t="s">
         <v>21</v>
       </c>
-      <c r="S51" t="str">
-        <f>VLOOKUP(C51,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S51">
+        <f>VLOOKUP($C51,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <f>VLOOKUP($C51,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U51" t="str">
+        <f>VLOOKUP($C51,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ws</v>
       </c>
-      <c r="T51" t="str">
-        <f>VLOOKUP(C51,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V51" t="str">
+        <f>VLOOKUP($C51,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m / s</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -4851,16 +5258,24 @@
       <c r="R52" t="s">
         <v>21</v>
       </c>
-      <c r="S52" t="str">
-        <f>VLOOKUP(C52,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S52">
+        <f>VLOOKUP($C52,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="T52">
+        <f>VLOOKUP($C52,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="U52" t="str">
+        <f>VLOOKUP($C52,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T52" t="str">
-        <f>VLOOKUP(C52,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V52" t="str">
+        <f>VLOOKUP($C52,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>118</v>
       </c>
@@ -4912,16 +5327,24 @@
       <c r="R53" t="s">
         <v>21</v>
       </c>
-      <c r="S53" t="str">
-        <f>VLOOKUP(C53,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S53">
+        <f>VLOOKUP($C53,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="T53">
+        <f>VLOOKUP($C53,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="U53" t="str">
+        <f>VLOOKUP($C53,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T53" t="str">
-        <f>VLOOKUP(C53,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V53" t="str">
+        <f>VLOOKUP($C53,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -4973,16 +5396,24 @@
       <c r="R54" t="s">
         <v>21</v>
       </c>
-      <c r="S54" t="str">
-        <f>VLOOKUP(C54,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S54">
+        <f>VLOOKUP($C54,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T54">
+        <f>VLOOKUP($C54,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U54" t="str">
+        <f>VLOOKUP($C54,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T54" t="str">
-        <f>VLOOKUP(C54,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V54" t="str">
+        <f>VLOOKUP($C54,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>118</v>
       </c>
@@ -5034,16 +5465,24 @@
       <c r="R55" t="s">
         <v>21</v>
       </c>
-      <c r="S55" t="str">
-        <f>VLOOKUP(C55,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S55">
+        <f>VLOOKUP($C55,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T55">
+        <f>VLOOKUP($C55,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U55" t="str">
+        <f>VLOOKUP($C55,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T55" t="str">
-        <f>VLOOKUP(C55,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V55" t="str">
+        <f>VLOOKUP($C55,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -5095,16 +5534,24 @@
       <c r="R56" t="s">
         <v>21</v>
       </c>
-      <c r="S56" t="str">
-        <f>VLOOKUP(C56,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S56">
+        <f>VLOOKUP($C56,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T56">
+        <f>VLOOKUP($C56,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U56" t="str">
+        <f>VLOOKUP($C56,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T56" t="str">
-        <f>VLOOKUP(C56,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V56" t="str">
+        <f>VLOOKUP($C56,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -5156,16 +5603,24 @@
       <c r="R57" t="s">
         <v>21</v>
       </c>
-      <c r="S57" t="str">
-        <f>VLOOKUP(C57,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S57">
+        <f>VLOOKUP($C57,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T57">
+        <f>VLOOKUP($C57,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U57" t="str">
+        <f>VLOOKUP($C57,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T57" t="str">
-        <f>VLOOKUP(C57,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V57" t="str">
+        <f>VLOOKUP($C57,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>118</v>
       </c>
@@ -5217,16 +5672,24 @@
       <c r="R58" t="s">
         <v>21</v>
       </c>
-      <c r="S58" t="str">
-        <f>VLOOKUP(C58,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S58">
+        <f>VLOOKUP($C58,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T58">
+        <f>VLOOKUP($C58,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U58" t="str">
+        <f>VLOOKUP($C58,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T58" t="str">
-        <f>VLOOKUP(C58,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V58" t="str">
+        <f>VLOOKUP($C58,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -5279,16 +5742,24 @@
       <c r="R59" t="s">
         <v>21</v>
       </c>
-      <c r="S59" t="str">
-        <f>VLOOKUP(C59,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S59">
+        <f>VLOOKUP($C59,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T59">
+        <f>VLOOKUP($C59,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U59" t="str">
+        <f>VLOOKUP($C59,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T59" t="str">
-        <f>VLOOKUP(C59,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V59" t="str">
+        <f>VLOOKUP($C59,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -5341,16 +5812,24 @@
       <c r="R60" t="s">
         <v>21</v>
       </c>
-      <c r="S60" t="str">
-        <f>VLOOKUP(C60,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S60">
+        <f>VLOOKUP($C60,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T60">
+        <f>VLOOKUP($C60,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U60" t="str">
+        <f>VLOOKUP($C60,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T60" t="str">
-        <f>VLOOKUP(C60,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V60" t="str">
+        <f>VLOOKUP($C60,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -5403,16 +5882,24 @@
       <c r="R61" t="s">
         <v>21</v>
       </c>
-      <c r="S61" t="str">
-        <f>VLOOKUP(C61,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S61">
+        <f>VLOOKUP($C61,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T61">
+        <f>VLOOKUP($C61,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U61" t="str">
+        <f>VLOOKUP($C61,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T61" t="str">
-        <f>VLOOKUP(C61,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V61" t="str">
+        <f>VLOOKUP($C61,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -5465,16 +5952,24 @@
       <c r="R62" t="s">
         <v>21</v>
       </c>
-      <c r="S62" t="str">
-        <f>VLOOKUP(C62,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S62">
+        <f>VLOOKUP($C62,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T62">
+        <f>VLOOKUP($C62,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U62" t="str">
+        <f>VLOOKUP($C62,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T62" t="str">
-        <f>VLOOKUP(C62,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V62" t="str">
+        <f>VLOOKUP($C62,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>118</v>
       </c>
@@ -5527,16 +6022,24 @@
       <c r="R63" t="s">
         <v>21</v>
       </c>
-      <c r="S63" t="str">
-        <f>VLOOKUP(C63,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S63">
+        <f>VLOOKUP($C63,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T63">
+        <f>VLOOKUP($C63,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U63" t="str">
+        <f>VLOOKUP($C63,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T63" t="str">
-        <f>VLOOKUP(C63,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V63" t="str">
+        <f>VLOOKUP($C63,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>118</v>
       </c>
@@ -5589,16 +6092,24 @@
       <c r="R64" t="s">
         <v>21</v>
       </c>
-      <c r="S64" t="str">
-        <f>VLOOKUP(C64,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S64">
+        <f>VLOOKUP($C64,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T64">
+        <f>VLOOKUP($C64,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U64" t="str">
+        <f>VLOOKUP($C64,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T64" t="str">
-        <f>VLOOKUP(C64,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V64" t="str">
+        <f>VLOOKUP($C64,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>118</v>
       </c>
@@ -5651,16 +6162,24 @@
       <c r="R65" t="s">
         <v>21</v>
       </c>
-      <c r="S65" t="str">
-        <f>VLOOKUP(C65,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S65">
+        <f>VLOOKUP($C65,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T65">
+        <f>VLOOKUP($C65,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U65" t="str">
+        <f>VLOOKUP($C65,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T65" t="str">
-        <f>VLOOKUP(C65,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V65" t="str">
+        <f>VLOOKUP($C65,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -5713,16 +6232,24 @@
       <c r="R66" t="s">
         <v>21</v>
       </c>
-      <c r="S66" t="str">
-        <f>VLOOKUP(C66,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S66">
+        <f>VLOOKUP($C66,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T66">
+        <f>VLOOKUP($C66,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U66" t="str">
+        <f>VLOOKUP($C66,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T66" t="str">
-        <f>VLOOKUP(C66,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V66" t="str">
+        <f>VLOOKUP($C66,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>118</v>
       </c>
@@ -5775,16 +6302,24 @@
       <c r="R67" t="s">
         <v>21</v>
       </c>
-      <c r="S67" t="str">
-        <f>VLOOKUP(C67,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S67">
+        <f>VLOOKUP($C67,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T67">
+        <f>VLOOKUP($C67,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U67" t="str">
+        <f>VLOOKUP($C67,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T67" t="str">
-        <f>VLOOKUP(C67,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V67" t="str">
+        <f>VLOOKUP($C67,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -5837,16 +6372,24 @@
       <c r="R68" t="s">
         <v>21</v>
       </c>
-      <c r="S68" t="str">
-        <f>VLOOKUP(C68,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S68">
+        <f>VLOOKUP($C68,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T68">
+        <f>VLOOKUP($C68,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U68" t="str">
+        <f>VLOOKUP($C68,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T68" t="str">
-        <f>VLOOKUP(C68,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V68" t="str">
+        <f>VLOOKUP($C68,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -5899,16 +6442,24 @@
       <c r="R69" t="s">
         <v>21</v>
       </c>
-      <c r="S69" t="str">
-        <f>VLOOKUP(C69,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S69">
+        <f>VLOOKUP($C69,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="T69">
+        <f>VLOOKUP($C69,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U69" t="str">
+        <f>VLOOKUP($C69,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T69" t="str">
-        <f>VLOOKUP(C69,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V69" t="str">
+        <f>VLOOKUP($C69,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>118</v>
       </c>
@@ -5961,16 +6512,24 @@
       <c r="R70" t="s">
         <v>21</v>
       </c>
-      <c r="S70" t="str">
-        <f>VLOOKUP(C70,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S70">
+        <f>VLOOKUP($C70,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="T70">
+        <f>VLOOKUP($C70,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U70" t="str">
+        <f>VLOOKUP($C70,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T70" t="str">
-        <f>VLOOKUP(C70,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V70" t="str">
+        <f>VLOOKUP($C70,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>118</v>
       </c>
@@ -6023,16 +6582,24 @@
       <c r="R71" t="s">
         <v>21</v>
       </c>
-      <c r="S71" t="str">
-        <f>VLOOKUP(C71,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S71">
+        <f>VLOOKUP($C71,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="T71">
+        <f>VLOOKUP($C71,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U71" t="str">
+        <f>VLOOKUP($C71,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T71" t="str">
-        <f>VLOOKUP(C71,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V71" t="str">
+        <f>VLOOKUP($C71,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -6085,16 +6652,24 @@
       <c r="R72" t="s">
         <v>21</v>
       </c>
-      <c r="S72" t="str">
-        <f>VLOOKUP(C72,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S72">
+        <f>VLOOKUP($C72,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="T72">
+        <f>VLOOKUP($C72,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U72" t="str">
+        <f>VLOOKUP($C72,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>ssrd</v>
       </c>
-      <c r="T72" t="str">
-        <f>VLOOKUP(C72,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V72" t="str">
+        <f>VLOOKUP($C72,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>118</v>
       </c>
@@ -6147,16 +6722,24 @@
       <c r="R73" t="s">
         <v>21</v>
       </c>
-      <c r="S73" t="str">
-        <f>VLOOKUP(C73,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S73">
+        <f>VLOOKUP($C73,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="T73">
+        <f>VLOOKUP($C73,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="U73" t="str">
+        <f>VLOOKUP($C73,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T73" t="str">
-        <f>VLOOKUP(C73,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V73" t="str">
+        <f>VLOOKUP($C73,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -6209,16 +6792,24 @@
       <c r="R74" t="s">
         <v>21</v>
       </c>
-      <c r="S74" t="str">
-        <f>VLOOKUP(C74,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S74">
+        <f>VLOOKUP($C74,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="T74">
+        <f>VLOOKUP($C74,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="U74" t="str">
+        <f>VLOOKUP($C74,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T74" t="str">
-        <f>VLOOKUP(C74,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V74" t="str">
+        <f>VLOOKUP($C74,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -6271,16 +6862,24 @@
       <c r="R75" t="s">
         <v>21</v>
       </c>
-      <c r="S75" t="str">
-        <f>VLOOKUP(C75,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S75">
+        <f>VLOOKUP($C75,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="T75">
+        <f>VLOOKUP($C75,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="U75" t="str">
+        <f>VLOOKUP($C75,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T75" t="str">
-        <f>VLOOKUP(C75,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V75" t="str">
+        <f>VLOOKUP($C75,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>118</v>
       </c>
@@ -6333,16 +6932,24 @@
       <c r="R76" t="s">
         <v>21</v>
       </c>
-      <c r="S76" t="str">
-        <f>VLOOKUP(C76,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S76">
+        <f>VLOOKUP($C76,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="T76">
+        <f>VLOOKUP($C76,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="U76" t="str">
+        <f>VLOOKUP($C76,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T76" t="str">
-        <f>VLOOKUP(C76,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V76" t="str">
+        <f>VLOOKUP($C76,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -6395,16 +7002,24 @@
       <c r="R77" t="s">
         <v>21</v>
       </c>
-      <c r="S77" t="str">
-        <f>VLOOKUP(C77,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S77">
+        <f>VLOOKUP($C77,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <f>VLOOKUP($C77,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U77" t="str">
+        <f>VLOOKUP($C77,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T77" t="str">
-        <f>VLOOKUP(C77,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V77" t="str">
+        <f>VLOOKUP($C77,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -6457,16 +7072,24 @@
       <c r="R78" t="s">
         <v>21</v>
       </c>
-      <c r="S78" t="str">
-        <f>VLOOKUP(C78,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S78">
+        <f>VLOOKUP($C78,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <f>VLOOKUP($C78,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U78" t="str">
+        <f>VLOOKUP($C78,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T78" t="str">
-        <f>VLOOKUP(C78,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V78" t="str">
+        <f>VLOOKUP($C78,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>118</v>
       </c>
@@ -6519,16 +7142,24 @@
       <c r="R79" t="s">
         <v>21</v>
       </c>
-      <c r="S79" t="str">
-        <f>VLOOKUP(C79,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S79">
+        <f>VLOOKUP($C79,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <f>VLOOKUP($C79,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U79" t="str">
+        <f>VLOOKUP($C79,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T79" t="str">
-        <f>VLOOKUP(C79,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V79" t="str">
+        <f>VLOOKUP($C79,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -6581,16 +7212,24 @@
       <c r="R80" t="s">
         <v>21</v>
       </c>
-      <c r="S80" t="str">
-        <f>VLOOKUP(C80,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S80">
+        <f>VLOOKUP($C80,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <f>VLOOKUP($C80,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U80" t="str">
+        <f>VLOOKUP($C80,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T80" t="str">
-        <f>VLOOKUP(C80,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V80" t="str">
+        <f>VLOOKUP($C80,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>118</v>
       </c>
@@ -6643,16 +7282,24 @@
       <c r="R81" t="s">
         <v>21</v>
       </c>
-      <c r="S81" t="str">
-        <f>VLOOKUP(C81,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S81">
+        <f>VLOOKUP($C81,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <f>VLOOKUP($C81,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U81" t="str">
+        <f>VLOOKUP($C81,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T81" t="str">
-        <f>VLOOKUP(C81,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V81" t="str">
+        <f>VLOOKUP($C81,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>118</v>
       </c>
@@ -6705,16 +7352,24 @@
       <c r="R82" t="s">
         <v>21</v>
       </c>
-      <c r="S82" t="str">
-        <f>VLOOKUP(C82,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S82">
+        <f>VLOOKUP($C82,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <f>VLOOKUP($C82,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U82" t="str">
+        <f>VLOOKUP($C82,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T82" t="str">
-        <f>VLOOKUP(C82,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V82" t="str">
+        <f>VLOOKUP($C82,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -6767,16 +7422,24 @@
       <c r="R83" t="s">
         <v>21</v>
       </c>
-      <c r="S83" t="str">
-        <f>VLOOKUP(C83,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S83">
+        <f>VLOOKUP($C83,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <f>VLOOKUP($C83,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U83" t="str">
+        <f>VLOOKUP($C83,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T83" t="str">
-        <f>VLOOKUP(C83,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V83" t="str">
+        <f>VLOOKUP($C83,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>118</v>
       </c>
@@ -6829,16 +7492,24 @@
       <c r="R84" t="s">
         <v>21</v>
       </c>
-      <c r="S84" t="str">
-        <f>VLOOKUP(C84,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S84">
+        <f>VLOOKUP($C84,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <f>VLOOKUP($C84,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U84" t="str">
+        <f>VLOOKUP($C84,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T84" t="str">
-        <f>VLOOKUP(C84,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V84" t="str">
+        <f>VLOOKUP($C84,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>118</v>
       </c>
@@ -6891,16 +7562,24 @@
       <c r="R85" t="s">
         <v>21</v>
       </c>
-      <c r="S85" t="str">
-        <f>VLOOKUP(C85,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S85">
+        <f>VLOOKUP($C85,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T85">
+        <f>VLOOKUP($C85,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U85" t="str">
+        <f>VLOOKUP($C85,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T85" t="str">
-        <f>VLOOKUP(C85,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V85" t="str">
+        <f>VLOOKUP($C85,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>118</v>
       </c>
@@ -6953,16 +7632,24 @@
       <c r="R86" t="s">
         <v>21</v>
       </c>
-      <c r="S86" t="str">
-        <f>VLOOKUP(C86,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S86">
+        <f>VLOOKUP($C86,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T86">
+        <f>VLOOKUP($C86,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U86" t="str">
+        <f>VLOOKUP($C86,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T86" t="str">
-        <f>VLOOKUP(C86,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V86" t="str">
+        <f>VLOOKUP($C86,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>118</v>
       </c>
@@ -7015,16 +7702,24 @@
       <c r="R87" t="s">
         <v>21</v>
       </c>
-      <c r="S87" t="str">
-        <f>VLOOKUP(C87,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S87">
+        <f>VLOOKUP($C87,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T87">
+        <f>VLOOKUP($C87,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U87" t="str">
+        <f>VLOOKUP($C87,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T87" t="str">
-        <f>VLOOKUP(C87,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V87" t="str">
+        <f>VLOOKUP($C87,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>118</v>
       </c>
@@ -7077,16 +7772,24 @@
       <c r="R88" t="s">
         <v>21</v>
       </c>
-      <c r="S88" t="str">
-        <f>VLOOKUP(C88,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S88">
+        <f>VLOOKUP($C88,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T88">
+        <f>VLOOKUP($C88,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U88" t="str">
+        <f>VLOOKUP($C88,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T88" t="str">
-        <f>VLOOKUP(C88,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V88" t="str">
+        <f>VLOOKUP($C88,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>118</v>
       </c>
@@ -7139,16 +7842,24 @@
       <c r="R89" t="s">
         <v>21</v>
       </c>
-      <c r="S89" t="str">
-        <f>VLOOKUP(C89,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S89">
+        <f>VLOOKUP($C89,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T89">
+        <f>VLOOKUP($C89,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U89" t="str">
+        <f>VLOOKUP($C89,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T89" t="str">
-        <f>VLOOKUP(C89,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V89" t="str">
+        <f>VLOOKUP($C89,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -7201,16 +7912,24 @@
       <c r="R90" t="s">
         <v>21</v>
       </c>
-      <c r="S90" t="str">
-        <f>VLOOKUP(C90,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S90">
+        <f>VLOOKUP($C90,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T90">
+        <f>VLOOKUP($C90,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U90" t="str">
+        <f>VLOOKUP($C90,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T90" t="str">
-        <f>VLOOKUP(C90,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V90" t="str">
+        <f>VLOOKUP($C90,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>118</v>
       </c>
@@ -7263,16 +7982,24 @@
       <c r="R91" t="s">
         <v>21</v>
       </c>
-      <c r="S91" t="str">
-        <f>VLOOKUP(C91,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S91">
+        <f>VLOOKUP($C91,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T91">
+        <f>VLOOKUP($C91,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U91" t="str">
+        <f>VLOOKUP($C91,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T91" t="str">
-        <f>VLOOKUP(C91,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V91" t="str">
+        <f>VLOOKUP($C91,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>118</v>
       </c>
@@ -7325,16 +8052,24 @@
       <c r="R92" t="s">
         <v>21</v>
       </c>
-      <c r="S92" t="str">
-        <f>VLOOKUP(C92,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S92">
+        <f>VLOOKUP($C92,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T92">
+        <f>VLOOKUP($C92,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U92" t="str">
+        <f>VLOOKUP($C92,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T92" t="str">
-        <f>VLOOKUP(C92,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V92" t="str">
+        <f>VLOOKUP($C92,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>118</v>
       </c>
@@ -7387,16 +8122,24 @@
       <c r="R93" t="s">
         <v>21</v>
       </c>
-      <c r="S93" t="str">
-        <f>VLOOKUP(C93,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S93">
+        <f>VLOOKUP($C93,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T93">
+        <f>VLOOKUP($C93,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U93" t="str">
+        <f>VLOOKUP($C93,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T93" t="str">
-        <f>VLOOKUP(C93,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V93" t="str">
+        <f>VLOOKUP($C93,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>118</v>
       </c>
@@ -7449,16 +8192,24 @@
       <c r="R94" t="s">
         <v>21</v>
       </c>
-      <c r="S94" t="str">
-        <f>VLOOKUP(C94,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S94">
+        <f>VLOOKUP($C94,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T94">
+        <f>VLOOKUP($C94,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U94" t="str">
+        <f>VLOOKUP($C94,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>stl1</v>
       </c>
-      <c r="T94" t="str">
-        <f>VLOOKUP(C94,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V94" t="str">
+        <f>VLOOKUP($C94,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>118</v>
       </c>
@@ -7511,16 +8262,24 @@
       <c r="R95" t="s">
         <v>21</v>
       </c>
-      <c r="S95" t="str">
-        <f>VLOOKUP(C95,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S95">
+        <f>VLOOKUP($C95,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <f>VLOOKUP($C95,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U95" t="str">
+        <f>VLOOKUP($C95,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T95" t="str">
-        <f>VLOOKUP(C95,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V95" t="str">
+        <f>VLOOKUP($C95,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>118</v>
       </c>
@@ -7573,16 +8332,24 @@
       <c r="R96" t="s">
         <v>21</v>
       </c>
-      <c r="S96" t="str">
-        <f>VLOOKUP(C96,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S96">
+        <f>VLOOKUP($C96,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T96">
+        <f>VLOOKUP($C96,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U96" t="str">
+        <f>VLOOKUP($C96,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T96" t="str">
-        <f>VLOOKUP(C96,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V96" t="str">
+        <f>VLOOKUP($C96,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>118</v>
       </c>
@@ -7635,16 +8402,24 @@
       <c r="R97" t="s">
         <v>21</v>
       </c>
-      <c r="S97" t="str">
-        <f>VLOOKUP(C97,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S97">
+        <f>VLOOKUP($C97,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T97">
+        <f>VLOOKUP($C97,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U97" t="str">
+        <f>VLOOKUP($C97,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T97" t="str">
-        <f>VLOOKUP(C97,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V97" t="str">
+        <f>VLOOKUP($C97,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>118</v>
       </c>
@@ -7697,16 +8472,24 @@
       <c r="R98" t="s">
         <v>21</v>
       </c>
-      <c r="S98" t="str">
-        <f>VLOOKUP(C98,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S98">
+        <f>VLOOKUP($C98,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T98">
+        <f>VLOOKUP($C98,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U98" t="str">
+        <f>VLOOKUP($C98,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T98" t="str">
-        <f>VLOOKUP(C98,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V98" t="str">
+        <f>VLOOKUP($C98,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>118</v>
       </c>
@@ -7759,16 +8542,24 @@
       <c r="R99" t="s">
         <v>21</v>
       </c>
-      <c r="S99" t="str">
-        <f>VLOOKUP(C99,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S99">
+        <f>VLOOKUP($C99,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T99">
+        <f>VLOOKUP($C99,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U99" t="str">
+        <f>VLOOKUP($C99,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T99" t="str">
-        <f>VLOOKUP(C99,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V99" t="str">
+        <f>VLOOKUP($C99,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>118</v>
       </c>
@@ -7821,16 +8612,24 @@
       <c r="R100" t="s">
         <v>21</v>
       </c>
-      <c r="S100" t="str">
-        <f>VLOOKUP(C100,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S100">
+        <f>VLOOKUP($C100,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T100">
+        <f>VLOOKUP($C100,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U100" t="str">
+        <f>VLOOKUP($C100,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T100" t="str">
-        <f>VLOOKUP(C100,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V100" t="str">
+        <f>VLOOKUP($C100,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>118</v>
       </c>
@@ -7883,16 +8682,24 @@
       <c r="R101" t="s">
         <v>21</v>
       </c>
-      <c r="S101" t="str">
-        <f>VLOOKUP(C101,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S101">
+        <f>VLOOKUP($C101,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T101">
+        <f>VLOOKUP($C101,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U101" t="str">
+        <f>VLOOKUP($C101,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T101" t="str">
-        <f>VLOOKUP(C101,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V101" t="str">
+        <f>VLOOKUP($C101,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>118</v>
       </c>
@@ -7945,16 +8752,24 @@
       <c r="R102" t="s">
         <v>21</v>
       </c>
-      <c r="S102" t="str">
-        <f>VLOOKUP(C102,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S102">
+        <f>VLOOKUP($C102,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <f>VLOOKUP($C102,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U102" t="str">
+        <f>VLOOKUP($C102,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>swvl1</v>
       </c>
-      <c r="T102" t="str">
-        <f>VLOOKUP(C102,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V102" t="str">
+        <f>VLOOKUP($C102,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>119</v>
       </c>
@@ -8007,16 +8822,24 @@
       <c r="R103" t="s">
         <v>21</v>
       </c>
-      <c r="S103" t="str">
-        <f>VLOOKUP(C103,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S103">
+        <f>VLOOKUP($C103,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="T103">
+        <f>VLOOKUP($C103,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U103" t="str">
+        <f>VLOOKUP($C103,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>t2m</v>
       </c>
-      <c r="T103" t="str">
-        <f>VLOOKUP(C103,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V103" t="str">
+        <f>VLOOKUP($C103,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
@@ -8069,12 +8892,20 @@
       <c r="R104" t="s">
         <v>21</v>
       </c>
-      <c r="S104" t="str">
-        <f>VLOOKUP(C104,naming_lookup!$C$1:$E$40,3,FALSE)</f>
+      <c r="S104">
+        <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="T104">
+        <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U104" t="str">
+        <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,5,FALSE)</f>
         <v>t2m</v>
       </c>
-      <c r="T104" t="str">
-        <f>VLOOKUP(C104,naming_lookup!$C$1:$F$40,4,FALSE)</f>
+      <c r="V104" t="str">
+        <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
     </row>
@@ -8088,1070 +8919,1134 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B6FF77-C883-40C9-8616-F79923CDA0A3}">
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF29616-2603-4811-AA75-C70B902F2583}">
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E1" t="s">
         <v>122</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>123</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>95</v>
-      </c>
       <c r="G1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L1" t="s">
-        <v>129</v>
-      </c>
-      <c r="M1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2">
+        <f>VLOOKUP($C2,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="F2">
+        <f>VLOOKUP($C2,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="e">
+        <f>VLOOKUP($C3,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F3" t="e">
+        <f>VLOOKUP($C3,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP($C4,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>VLOOKUP($C4,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP($C5,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>VLOOKUP($C5,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP($C6,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="F6">
+        <f>VLOOKUP($C6,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP($C7,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="F7">
+        <f>VLOOKUP($C7,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <f>VLOOKUP($C8,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="F8">
+        <f>VLOOKUP($C8,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>188</v>
+      </c>
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <f>VLOOKUP($C9,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>90</v>
+      </c>
+      <c r="F9">
+        <f>VLOOKUP($C9,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
         <v>130</v>
       </c>
-      <c r="N1" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="G9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10">
+        <f>VLOOKUP($C10,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f>VLOOKUP($C10,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="G10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11">
+        <f>VLOOKUP($C11,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f>VLOOKUP($C11,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>300</v>
+      </c>
+      <c r="G11" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12">
+        <f>VLOOKUP($C12,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>VLOOKUP($C12,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="G12" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13">
+        <f>VLOOKUP($C13,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>VLOOKUP($C13,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="G13" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14">
+        <f>VLOOKUP($C14,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f>VLOOKUP($C14,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="G14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15">
+        <f>VLOOKUP($C15,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>VLOOKUP($C15,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="G15" t="s">
+        <v>209</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16">
+        <f>VLOOKUP($C16,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f>VLOOKUP($C16,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="G16" t="s">
+        <v>211</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17">
+        <f>VLOOKUP($C17,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f>VLOOKUP($C17,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="G17" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E18">
+        <f>VLOOKUP($C18,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f>VLOOKUP($C18,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>212</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19">
+        <f>VLOOKUP($C19,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f>VLOOKUP($C19,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>360</v>
+      </c>
+      <c r="G19" t="s">
+        <v>214</v>
+      </c>
+      <c r="H19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
         <v>62</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20">
+        <f>VLOOKUP($C20,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f>VLOOKUP($C20,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="G20" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21">
+        <f>VLOOKUP($C21,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-500</v>
+      </c>
+      <c r="F21">
+        <f>VLOOKUP($C21,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="G21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22">
+        <f>VLOOKUP($C22,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="F22">
+        <f>VLOOKUP($C22,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23">
+        <f>VLOOKUP($C23,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="F23">
+        <f>VLOOKUP($C23,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H23" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24">
+        <f>VLOOKUP($C24,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="F24">
+        <f>VLOOKUP($C24,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25">
+        <f>VLOOKUP($C25,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="F25">
+        <f>VLOOKUP($C25,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26">
+        <f>VLOOKUP($C26,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f>VLOOKUP($C26,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="G26" t="s">
+        <v>188</v>
+      </c>
+      <c r="H26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27">
+        <f>VLOOKUP($C27,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f>VLOOKUP($C27,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="G27" t="s">
+        <v>188</v>
+      </c>
+      <c r="H27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28">
+        <f>VLOOKUP($C28,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f>VLOOKUP($C28,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="G28" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>221</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>175</v>
+      </c>
+      <c r="E29">
+        <f>VLOOKUP($C29,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <f>VLOOKUP($C29,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="G29" t="s">
+        <v>188</v>
+      </c>
+      <c r="H29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30">
+        <f>VLOOKUP($C30,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="F30">
+        <f>VLOOKUP($C30,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
         <v>30</v>
       </c>
-      <c r="F2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K2" t="s">
-        <v>134</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="G30" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31">
+        <f>VLOOKUP($C31,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="F31">
+        <f>VLOOKUP($C31,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
         <v>30</v>
       </c>
-      <c r="M2" t="str">
-        <f>VLOOKUP(A2,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>sd</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K3" t="s">
-        <v>138</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" t="str">
-        <f>VLOOKUP(A3,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>time</v>
-      </c>
-      <c r="N3" t="s">
-        <v>138</v>
-      </c>
-      <c r="O3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>-20</v>
-      </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K4" t="s">
-        <v>141</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" t="str">
-        <f>VLOOKUP(A4,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssrd</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
+      <c r="G31" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32">
+        <f>VLOOKUP($C32,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="F32">
+        <f>VLOOKUP($C32,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="G32" t="s">
+        <v>222</v>
+      </c>
+      <c r="H32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" t="s">
+        <v>225</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>175</v>
+      </c>
+      <c r="E33">
+        <f>VLOOKUP($C33,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="F33">
+        <f>VLOOKUP($C33,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>120</v>
+      </c>
+      <c r="G33" t="s">
+        <v>176</v>
+      </c>
+      <c r="H33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34">
+        <f>VLOOKUP($C34,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f>VLOOKUP($C34,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
         <v>1200</v>
       </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G34" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>144</v>
-      </c>
-      <c r="K5" t="s">
-        <v>145</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="str">
-        <f>VLOOKUP(A5,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>strd</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="O5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1000</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>149</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K6" t="s">
-        <v>151</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="str">
-        <f>VLOOKUP(A6,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>stru</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35">
+        <f>VLOOKUP($C35,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <f>VLOOKUP($C35,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>500</v>
+      </c>
+      <c r="G35" t="s">
+        <v>173</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36">
+        <f>VLOOKUP($C36,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <f>VLOOKUP($C36,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>500</v>
+      </c>
+      <c r="G36" t="s">
+        <v>209</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37">
+        <f>VLOOKUP($C37,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <f>VLOOKUP($C37,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>500</v>
+      </c>
+      <c r="G37" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38">
+        <f>VLOOKUP($C38,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <f>VLOOKUP($C38,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>500</v>
+      </c>
+      <c r="G38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <f>VLOOKUP($C39,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-99999</v>
+      </c>
+      <c r="F39">
+        <f>VLOOKUP($C39,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>99999</v>
+      </c>
+      <c r="G39" t="s">
+        <v>176</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" t="s">
-        <v>153</v>
-      </c>
-      <c r="I7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" t="str">
-        <f>VLOOKUP(A7,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>rh</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>500</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" t="str">
-        <f>VLOOKUP(A8,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssrd</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>500</v>
-      </c>
-      <c r="D9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" t="str">
-        <f>VLOOKUP(A9,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssru</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>500</v>
-      </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" t="s">
-        <v>156</v>
-      </c>
-      <c r="I10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" t="str">
-        <f>VLOOKUP(A10,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssrd</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>500</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" t="s">
-        <v>156</v>
-      </c>
-      <c r="I11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" t="str">
-        <f>VLOOKUP(A11,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssru</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M12" t="str">
-        <f>VLOOKUP(A12,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>tp</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="O12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13">
-        <v>90</v>
-      </c>
-      <c r="C13">
-        <v>130</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" t="str">
-        <f>VLOOKUP(A13,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>sp</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="O13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>2200</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F14" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" t="s">
-        <v>165</v>
-      </c>
-      <c r="I14" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K14" t="s">
-        <v>167</v>
-      </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" t="str">
-        <f>VLOOKUP(A14,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>fdif</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>2200</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" t="s">
-        <v>155</v>
-      </c>
-      <c r="F15" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" t="s">
-        <v>168</v>
-      </c>
-      <c r="I15" t="s">
-        <v>47</v>
-      </c>
-      <c r="M15" t="str">
-        <f>VLOOKUP(A15,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssrd</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>2200</v>
-      </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F16" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" t="s">
-        <v>169</v>
-      </c>
-      <c r="I16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J16" t="s">
-        <v>170</v>
-      </c>
-      <c r="K16" t="s">
-        <v>171</v>
-      </c>
-      <c r="L16" t="s">
-        <v>172</v>
-      </c>
-      <c r="M16" t="str">
-        <f>VLOOKUP(A16,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssru</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>121</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>1200</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" t="str">
-        <f>VLOOKUP(A17,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssrd</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="O17" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18">
-        <v>30</v>
-      </c>
-      <c r="C18">
-        <v>120</v>
-      </c>
-      <c r="D18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" t="s">
-        <v>175</v>
-      </c>
-      <c r="F18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" t="str">
-        <f>VLOOKUP(A18,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>rh</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="O18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19">
-        <v>-500</v>
-      </c>
-      <c r="C19">
-        <v>1200</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" t="str">
-        <f>VLOOKUP(A19,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>rn</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="O19" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>1200</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" t="s">
-        <v>180</v>
-      </c>
-      <c r="I20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" t="s">
-        <v>181</v>
-      </c>
-      <c r="K20" t="s">
-        <v>182</v>
-      </c>
-      <c r="L20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" t="str">
-        <f>VLOOKUP(A20,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssrd</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="O20" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>300</v>
-      </c>
-      <c r="D21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" t="s">
-        <v>183</v>
-      </c>
-      <c r="I21" t="s">
-        <v>27</v>
-      </c>
-      <c r="J21" t="s">
-        <v>184</v>
-      </c>
-      <c r="K21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" t="str">
-        <f>VLOOKUP(A21,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ssru</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>45</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" t="s">
-        <v>186</v>
-      </c>
-      <c r="K22" t="s">
-        <v>187</v>
-      </c>
-      <c r="L22" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" t="str">
-        <f>VLOOKUP(A22,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>swvl1</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="O22" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23">
-        <v>-40</v>
-      </c>
-      <c r="C23">
-        <v>50</v>
-      </c>
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" t="s">
-        <v>191</v>
-      </c>
-      <c r="F23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" t="s">
-        <v>73</v>
-      </c>
-      <c r="I23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M23" t="str">
-        <f>VLOOKUP(A23,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>t2m</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="O23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24">
-        <v>-20</v>
-      </c>
-      <c r="C24">
-        <v>50</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>191</v>
-      </c>
-      <c r="F24" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" t="s">
-        <v>194</v>
-      </c>
-      <c r="K24" t="s">
-        <v>195</v>
-      </c>
-      <c r="L24" t="s">
-        <v>193</v>
-      </c>
-      <c r="M24" t="str">
-        <f>VLOOKUP(A24,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>stl1</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="O24" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>360</v>
-      </c>
-      <c r="D25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" t="s">
-        <v>198</v>
-      </c>
-      <c r="F25" t="s">
-        <v>98</v>
-      </c>
-      <c r="G25" t="s">
-        <v>59</v>
-      </c>
-      <c r="H25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" t="s">
-        <v>198</v>
-      </c>
-      <c r="L25" t="s">
-        <v>198</v>
-      </c>
-      <c r="M25" t="str">
-        <f>VLOOKUP(A25,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>wd</v>
-      </c>
-      <c r="O25" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>30</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" t="s">
-        <v>142</v>
-      </c>
-      <c r="F26" t="s">
-        <v>98</v>
-      </c>
-      <c r="G26" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I26" t="s">
-        <v>58</v>
-      </c>
-      <c r="M26" t="str">
-        <f>VLOOKUP(A26,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>ws</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="O26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27">
-        <v>-10</v>
-      </c>
-      <c r="C27">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" t="s">
-        <v>29</v>
-      </c>
-      <c r="I27" t="s">
-        <v>30</v>
-      </c>
-      <c r="J27" t="s">
-        <v>200</v>
-      </c>
-      <c r="K27" t="s">
-        <v>201</v>
-      </c>
-      <c r="L27" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" t="str">
-        <f>VLOOKUP(A27,naming_lookup!$C$1:$E$40,3,FALSE)</f>
-        <v>swvl1</v>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <f>VLOOKUP($C40,dt_var_naming!$A$2:$F$27,5,FALSE)</f>
+        <v>-99999</v>
+      </c>
+      <c r="F40">
+        <f>VLOOKUP($C40,dt_var_naming!$A$2:$F$27,6,FALSE)</f>
+        <v>99999</v>
+      </c>
+      <c r="G40" t="s">
+        <v>176</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9160,815 +10055,1078 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF29616-2603-4811-AA75-C70B902F2583}">
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B6FF77-C883-40C9-8616-F79923CDA0A3}">
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr defaultRowHeight="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>204</v>
+    <row r="1" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
       </c>
       <c r="E1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+      <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" t="s">
+        <v>134</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <f>VLOOKUP(A2,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3">
+        <f>VLOOKUP(A3,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4">
+        <v>-30</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <f>VLOOKUP(A4,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1200</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>144</v>
+      </c>
+      <c r="K5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5">
+        <f>VLOOKUP(A5,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K6" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6">
+        <f>VLOOKUP(A6,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7">
+        <v>-99999</v>
+      </c>
+      <c r="F7">
+        <v>99999</v>
+      </c>
+      <c r="H7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7">
+        <f>VLOOKUP(A7,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>-99999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>500</v>
+      </c>
+      <c r="H8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8">
+        <f>VLOOKUP(A8,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>500</v>
+      </c>
+      <c r="H9" t="s">
+        <v>156</v>
+      </c>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9">
+        <f>VLOOKUP(A9,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>500</v>
+      </c>
+      <c r="H10" t="s">
+        <v>156</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
+        <f>VLOOKUP(A10,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>500</v>
+      </c>
+      <c r="H11" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11">
+        <f>VLOOKUP(A11,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12">
+        <f>VLOOKUP(A12,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>90</v>
+      </c>
+      <c r="F13">
+        <v>130</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13">
+        <f>VLOOKUP(A13,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>90</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="O13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>2200</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14">
+        <f>VLOOKUP(A14,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>2200</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15">
+        <f>VLOOKUP(A15,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>2200</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" t="s">
+        <v>169</v>
+      </c>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" t="s">
+        <v>170</v>
+      </c>
+      <c r="K16" t="s">
+        <v>171</v>
+      </c>
+      <c r="L16" t="s">
+        <v>172</v>
+      </c>
+      <c r="M16">
+        <f>VLOOKUP(A16,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1200</v>
+      </c>
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17">
+        <f>VLOOKUP(A17,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>120</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18">
+        <f>VLOOKUP(A18,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19">
+        <v>-500</v>
+      </c>
+      <c r="F19">
+        <v>1200</v>
+      </c>
+      <c r="H19" t="s">
+        <v>178</v>
+      </c>
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19">
+        <f>VLOOKUP(A19,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>-500</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="O19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1200</v>
+      </c>
+      <c r="G20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" t="s">
+        <v>181</v>
+      </c>
+      <c r="K20" t="s">
+        <v>182</v>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20">
+        <f>VLOOKUP(A20,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>300</v>
+      </c>
+      <c r="G21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" t="s">
+        <v>184</v>
+      </c>
+      <c r="K21" t="s">
+        <v>185</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21">
+        <f>VLOOKUP(A21,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" t="s">
+        <v>186</v>
+      </c>
+      <c r="K22" t="s">
+        <v>187</v>
+      </c>
+      <c r="L22" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22">
+        <f>VLOOKUP(A22,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23">
+        <v>-40</v>
+      </c>
+      <c r="F23">
+        <v>50</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23">
+        <f>VLOOKUP(A23,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="O23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>191</v>
+      </c>
+      <c r="D24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24">
+        <v>-20</v>
+      </c>
+      <c r="F24">
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="H24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" t="s">
+        <v>194</v>
+      </c>
+      <c r="K24" t="s">
+        <v>195</v>
+      </c>
+      <c r="L24" t="s">
+        <v>193</v>
+      </c>
+      <c r="M24">
+        <f>VLOOKUP(A24,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="O24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>198</v>
+      </c>
+      <c r="D25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>360</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
+        <v>198</v>
+      </c>
+      <c r="L25" t="s">
+        <v>198</v>
+      </c>
+      <c r="M25">
+        <f>VLOOKUP(A25,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
         <v>142</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="D26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>30</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26">
+        <f>VLOOKUP(A26,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="O26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27">
+        <v>-10</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="J27" t="s">
+        <v>200</v>
+      </c>
+      <c r="K27" t="s">
+        <v>201</v>
+      </c>
+      <c r="L27" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>209</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E13" t="s">
-        <v>210</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15" t="s">
-        <v>209</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E18" t="s">
-        <v>212</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" t="s">
-        <v>198</v>
-      </c>
-      <c r="E19" t="s">
-        <v>214</v>
-      </c>
-      <c r="F19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" t="s">
-        <v>217</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" t="s">
-        <v>216</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>207</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>191</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>207</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s">
-        <v>191</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
-        <v>191</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>207</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s">
-        <v>191</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>218</v>
-      </c>
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" t="s">
-        <v>188</v>
-      </c>
-      <c r="F26" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>219</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>220</v>
-      </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E28" t="s">
-        <v>188</v>
-      </c>
-      <c r="F28" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>221</v>
-      </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>175</v>
-      </c>
-      <c r="E29" t="s">
-        <v>188</v>
-      </c>
-      <c r="F29" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" t="s">
-        <v>223</v>
-      </c>
-      <c r="C32" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" t="s">
-        <v>191</v>
-      </c>
-      <c r="E32" t="s">
-        <v>222</v>
-      </c>
-      <c r="F32" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>224</v>
-      </c>
-      <c r="B33" t="s">
-        <v>225</v>
-      </c>
-      <c r="C33" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" t="s">
-        <v>175</v>
-      </c>
-      <c r="E33" t="s">
-        <v>176</v>
-      </c>
-      <c r="F33" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E35" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" t="s">
-        <v>157</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" t="s">
-        <v>209</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" t="s">
-        <v>158</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E37" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" t="s">
-        <v>159</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" t="s">
-        <v>209</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>176</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>176</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
+      <c r="M27">
+        <f>VLOOKUP(A27,naming_lookup!$C$1:$G$40,3,FALSE)</f>
+        <v>-10</v>
       </c>
     </row>
   </sheetData>

--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\tests\testthat\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708A3F8C-FC06-459C-884D-3F89252C3824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFF005F-4CCA-4AE3-8886-42E2399916F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
   <sheets>
     <sheet name="dt_meta" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="235">
   <si>
     <t>name_dt</t>
   </si>
@@ -794,12 +794,24 @@
   <si>
     <t>mm</t>
   </si>
+  <si>
+    <t>imputation_method</t>
+  </si>
+  <si>
+    <t>era5</t>
+  </si>
+  <si>
+    <t>zero</t>
+  </si>
+  <si>
+    <t>nightzero</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -930,6 +942,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1663,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B621CE1-A4D4-4502-917D-92507EE2F7EE}">
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:W104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -1673,7 +1691,7 @@
     <col min="8" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -1740,8 +1758,11 @@
       <c r="V1" s="2" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>118</v>
       </c>
@@ -1807,8 +1828,11 @@
         <f>VLOOKUP($C2,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>NA</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -1876,8 +1900,11 @@
         <f>VLOOKUP($C3,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>cm</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W3" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -1945,8 +1972,11 @@
         <f>VLOOKUP($C4,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>cm</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W4" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -2014,8 +2044,11 @@
         <f>VLOOKUP($C5,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>NA</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -2083,8 +2116,11 @@
         <f>VLOOKUP($C6,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W6" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>118</v>
       </c>
@@ -2152,8 +2188,11 @@
         <f>VLOOKUP($C7,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W7" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>118</v>
       </c>
@@ -2221,8 +2260,11 @@
         <f>VLOOKUP($C8,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W8" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>118</v>
       </c>
@@ -2290,8 +2332,11 @@
         <f>VLOOKUP($C9,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W9" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -2359,8 +2404,11 @@
         <f>VLOOKUP($C10,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W10" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -2428,8 +2476,11 @@
         <f>VLOOKUP($C11,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W11" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -2497,8 +2548,11 @@
         <f>VLOOKUP($C12,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W12" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>118</v>
       </c>
@@ -2566,8 +2620,11 @@
         <f>VLOOKUP($C13,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W13" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -2635,8 +2692,11 @@
         <f>VLOOKUP($C14,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W14" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -2704,8 +2764,11 @@
         <f>VLOOKUP($C15,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W15" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -2773,8 +2836,11 @@
         <f>VLOOKUP($C16,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W16" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -2842,8 +2908,11 @@
         <f>VLOOKUP($C17,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W17" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -2911,8 +2980,11 @@
         <f>VLOOKUP($C18,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W18" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -2980,8 +3052,11 @@
         <f>VLOOKUP($C19,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>mm</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W19" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -3049,8 +3124,11 @@
         <f>VLOOKUP($C20,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>mm</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W20" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>118</v>
       </c>
@@ -3118,8 +3196,11 @@
         <f>VLOOKUP($C21,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>kPa</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W21" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>118</v>
       </c>
@@ -3187,8 +3268,11 @@
         <f>VLOOKUP($C22,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W22" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -3256,8 +3340,11 @@
         <f>VLOOKUP($C23,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W23" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -3325,8 +3412,11 @@
         <f>VLOOKUP($C24,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W24" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -3394,8 +3484,11 @@
         <f>VLOOKUP($C25,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W25" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -3463,8 +3556,11 @@
         <f>VLOOKUP($C26,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W26" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -3532,8 +3628,11 @@
         <f>VLOOKUP($C27,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W27" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -3601,8 +3700,11 @@
         <f>VLOOKUP($C28,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>micromol / m^2 / s</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W28" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -3670,8 +3772,11 @@
         <f>VLOOKUP($C29,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W29" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>118</v>
       </c>
@@ -3740,8 +3845,11 @@
         <f>VLOOKUP($C30,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W30" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>118</v>
       </c>
@@ -3810,8 +3918,11 @@
         <f>VLOOKUP($C31,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W31" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -3880,8 +3991,11 @@
         <f>VLOOKUP($C32,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W32" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -3950,8 +4064,11 @@
         <f>VLOOKUP($C33,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W33" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -4019,8 +4136,11 @@
         <f>VLOOKUP($C34,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W34" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>118</v>
       </c>
@@ -4089,8 +4209,11 @@
         <f>VLOOKUP($C35,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W35" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>118</v>
       </c>
@@ -4159,8 +4282,11 @@
         <f>VLOOKUP($C36,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W36" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -4228,8 +4354,11 @@
         <f>VLOOKUP($C37,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W37" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>118</v>
       </c>
@@ -4297,8 +4426,11 @@
         <f>VLOOKUP($C38,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W38" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>118</v>
       </c>
@@ -4366,8 +4498,11 @@
         <f>VLOOKUP($C39,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W39" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>118</v>
       </c>
@@ -4436,8 +4571,11 @@
         <f>VLOOKUP($C40,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W40" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>118</v>
       </c>
@@ -4506,8 +4644,11 @@
         <f>VLOOKUP($C41,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W41" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>118</v>
       </c>
@@ -4576,8 +4717,11 @@
         <f>VLOOKUP($C42,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W42" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>118</v>
       </c>
@@ -4646,8 +4790,11 @@
         <f>VLOOKUP($C43,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W43" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>118</v>
       </c>
@@ -4716,8 +4863,11 @@
         <f>VLOOKUP($C44,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W44" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>118</v>
       </c>
@@ -4786,8 +4936,11 @@
         <f>VLOOKUP($C45,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W45" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -4856,8 +5009,11 @@
         <f>VLOOKUP($C46,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W46" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -4925,8 +5081,11 @@
         <f>VLOOKUP($C47,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>NA</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W47" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>118</v>
       </c>
@@ -4995,8 +5154,11 @@
         <f>VLOOKUP($C48,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W48" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>118</v>
       </c>
@@ -5065,8 +5227,11 @@
         <f>VLOOKUP($C49,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m / s</v>
       </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W49" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>118</v>
       </c>
@@ -5135,8 +5300,11 @@
         <f>VLOOKUP($C50,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W50" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>118</v>
       </c>
@@ -5205,8 +5373,11 @@
         <f>VLOOKUP($C51,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m / s</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W51" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -5274,8 +5445,11 @@
         <f>VLOOKUP($C52,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W52" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>118</v>
       </c>
@@ -5343,8 +5517,11 @@
         <f>VLOOKUP($C53,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W53" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -5412,8 +5589,11 @@
         <f>VLOOKUP($C54,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W54" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>118</v>
       </c>
@@ -5481,8 +5661,11 @@
         <f>VLOOKUP($C55,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W55" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -5550,8 +5733,11 @@
         <f>VLOOKUP($C56,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W56" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -5619,8 +5805,11 @@
         <f>VLOOKUP($C57,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W57" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>118</v>
       </c>
@@ -5688,8 +5877,11 @@
         <f>VLOOKUP($C58,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W58" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -5758,8 +5950,11 @@
         <f>VLOOKUP($C59,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W59" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -5828,8 +6023,11 @@
         <f>VLOOKUP($C60,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W60" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -5898,8 +6096,11 @@
         <f>VLOOKUP($C61,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W61" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -5968,8 +6169,11 @@
         <f>VLOOKUP($C62,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W62" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>118</v>
       </c>
@@ -6038,8 +6242,11 @@
         <f>VLOOKUP($C63,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W63" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>118</v>
       </c>
@@ -6108,8 +6315,11 @@
         <f>VLOOKUP($C64,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W64" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>118</v>
       </c>
@@ -6178,8 +6388,11 @@
         <f>VLOOKUP($C65,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W65" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -6248,8 +6461,11 @@
         <f>VLOOKUP($C66,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W66" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>118</v>
       </c>
@@ -6318,8 +6534,11 @@
         <f>VLOOKUP($C67,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W67" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>118</v>
       </c>
@@ -6388,8 +6607,11 @@
         <f>VLOOKUP($C68,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W68" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -6458,8 +6680,11 @@
         <f>VLOOKUP($C69,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W69" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>118</v>
       </c>
@@ -6528,8 +6753,11 @@
         <f>VLOOKUP($C70,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W70" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>118</v>
       </c>
@@ -6598,8 +6826,11 @@
         <f>VLOOKUP($C71,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W71" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -6668,8 +6899,11 @@
         <f>VLOOKUP($C72,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>W / m^2</v>
       </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W72" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>118</v>
       </c>
@@ -6738,8 +6972,11 @@
         <f>VLOOKUP($C73,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W73" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -6808,8 +7045,11 @@
         <f>VLOOKUP($C74,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W74" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>118</v>
       </c>
@@ -6878,8 +7118,11 @@
         <f>VLOOKUP($C75,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W75" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>118</v>
       </c>
@@ -6948,8 +7191,11 @@
         <f>VLOOKUP($C76,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>m</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W76" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -7018,8 +7264,11 @@
         <f>VLOOKUP($C77,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W77" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -7088,8 +7337,11 @@
         <f>VLOOKUP($C78,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W78" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>118</v>
       </c>
@@ -7158,8 +7410,11 @@
         <f>VLOOKUP($C79,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W79" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -7228,8 +7483,11 @@
         <f>VLOOKUP($C80,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W80" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>118</v>
       </c>
@@ -7298,8 +7556,11 @@
         <f>VLOOKUP($C81,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W81" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>118</v>
       </c>
@@ -7368,8 +7629,11 @@
         <f>VLOOKUP($C82,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W82" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -7438,8 +7702,11 @@
         <f>VLOOKUP($C83,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W83" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>118</v>
       </c>
@@ -7508,8 +7775,11 @@
         <f>VLOOKUP($C84,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W84" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>118</v>
       </c>
@@ -7578,8 +7848,11 @@
         <f>VLOOKUP($C85,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W85" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>118</v>
       </c>
@@ -7648,8 +7921,11 @@
         <f>VLOOKUP($C86,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W86" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>118</v>
       </c>
@@ -7718,8 +7994,11 @@
         <f>VLOOKUP($C87,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W87" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>118</v>
       </c>
@@ -7788,8 +8067,11 @@
         <f>VLOOKUP($C88,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W88" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>118</v>
       </c>
@@ -7858,8 +8140,11 @@
         <f>VLOOKUP($C89,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W89" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -7928,8 +8213,11 @@
         <f>VLOOKUP($C90,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W90" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>118</v>
       </c>
@@ -7998,8 +8286,11 @@
         <f>VLOOKUP($C91,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W91" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>118</v>
       </c>
@@ -8068,8 +8359,11 @@
         <f>VLOOKUP($C92,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W92" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>118</v>
       </c>
@@ -8138,8 +8432,11 @@
         <f>VLOOKUP($C93,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W93" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>118</v>
       </c>
@@ -8208,8 +8505,11 @@
         <f>VLOOKUP($C94,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W94" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>118</v>
       </c>
@@ -8278,8 +8578,11 @@
         <f>VLOOKUP($C95,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W95" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>118</v>
       </c>
@@ -8348,8 +8651,11 @@
         <f>VLOOKUP($C96,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W96" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>118</v>
       </c>
@@ -8418,8 +8724,11 @@
         <f>VLOOKUP($C97,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W97" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>118</v>
       </c>
@@ -8488,8 +8797,11 @@
         <f>VLOOKUP($C98,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W98" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>118</v>
       </c>
@@ -8558,8 +8870,11 @@
         <f>VLOOKUP($C99,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W99" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>118</v>
       </c>
@@ -8628,8 +8943,11 @@
         <f>VLOOKUP($C100,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W100" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>118</v>
       </c>
@@ -8698,8 +9016,11 @@
         <f>VLOOKUP($C101,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W101" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>118</v>
       </c>
@@ -8768,8 +9089,11 @@
         <f>VLOOKUP($C102,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>percent</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W102" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>119</v>
       </c>
@@ -8838,8 +9162,11 @@
         <f>VLOOKUP($C103,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W103" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
@@ -8907,12 +9234,16 @@
       <c r="V104" t="str">
         <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:R53">
     <sortCondition ref="B3:B53"/>
   </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="120" verticalDpi="72" r:id="rId1"/>
 </worksheet>

--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFF005F-4CCA-4AE3-8886-42E2399916F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8B3D4E-CA64-4C16-8CA6-056653E8E9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
   <sheets>
     <sheet name="dt_meta" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="247">
   <si>
     <t>name_dt</t>
   </si>
@@ -805,6 +805,42 @@
   </si>
   <si>
     <t>nightzero</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>AirT</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>Total_solar</t>
+  </si>
+  <si>
+    <t>Net_rad</t>
+  </si>
+  <si>
+    <t>Soil_VWC</t>
+  </si>
+  <si>
+    <t>Soil_T1</t>
+  </si>
+  <si>
+    <t>Soil_T2</t>
+  </si>
+  <si>
+    <t>Shortwave incoming radiation</t>
+  </si>
+  <si>
+    <t>Shortwave outgoing radiation</t>
+  </si>
+  <si>
+    <t>%d/%m/%Y %H:%M</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B621CE1-A4D4-4502-917D-92507EE2F7EE}">
-  <dimension ref="A1:W104"/>
+  <dimension ref="A1:W118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -4078,8 +4114,8 @@
       <c r="C34" t="s">
         <v>36</v>
       </c>
-      <c r="D34" t="s">
-        <v>37</v>
+      <c r="D34" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -4152,7 +4188,7 @@
         <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>37</v>
+        <v>244</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -4225,7 +4261,7 @@
         <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>244</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -4297,7 +4333,7 @@
         <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>245</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -4369,7 +4405,7 @@
         <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>245</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -9170,36 +9206,35 @@
       <c r="A104" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B104" s="2" t="str">
-        <f t="shared" ref="B104" si="13">C104&amp;"_"&amp;J104&amp;"_"&amp;K104&amp;"_"&amp;L104</f>
-        <v>TA_2_1_1</v>
+      <c r="B104" t="s">
+        <v>117</v>
       </c>
       <c r="C104" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="D104" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F104" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="H104" s="1">
-        <v>46023</v>
+        <v>37257</v>
       </c>
       <c r="I104" s="1">
-        <v>46388</v>
-      </c>
-      <c r="J104">
-        <v>2</v>
-      </c>
-      <c r="K104">
-        <v>1</v>
-      </c>
-      <c r="L104">
-        <v>1</v>
+        <v>47484</v>
+      </c>
+      <c r="J104" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104" t="s">
+        <v>16</v>
+      </c>
+      <c r="L104" t="s">
+        <v>16</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -9219,23 +9254,1034 @@
       <c r="R104" t="s">
         <v>21</v>
       </c>
-      <c r="S104">
+      <c r="S104" t="e">
         <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,3,FALSE)</f>
-        <v>-40</v>
-      </c>
-      <c r="T104">
+        <v>#N/A</v>
+      </c>
+      <c r="T104" t="e">
         <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,4,FALSE)</f>
-        <v>50</v>
+        <v>#N/A</v>
       </c>
       <c r="U104" t="str">
         <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,5,FALSE)</f>
-        <v>t2m</v>
+        <v>site</v>
       </c>
       <c r="V104" t="str">
         <f>VLOOKUP($C104,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B105" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" t="s">
+        <v>97</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H105" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I105" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J105" t="s">
+        <v>16</v>
+      </c>
+      <c r="K105" t="s">
+        <v>16</v>
+      </c>
+      <c r="L105" t="s">
+        <v>16</v>
+      </c>
+      <c r="M105" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" t="b">
+        <v>1</v>
+      </c>
+      <c r="O105" t="b">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>100</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>20</v>
+      </c>
+      <c r="R105" t="s">
+        <v>21</v>
+      </c>
+      <c r="S105">
+        <f>VLOOKUP($C105,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <f>VLOOKUP($C105,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U105" t="str">
+        <f>VLOOKUP($C105,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>time</v>
+      </c>
+      <c r="V105" t="str">
+        <f>VLOOKUP($C105,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B106" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106" t="s">
+        <v>53</v>
+      </c>
+      <c r="D106" t="s">
+        <v>54</v>
+      </c>
+      <c r="E106" t="s">
+        <v>230</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H106" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I106" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J106" t="s">
+        <v>16</v>
+      </c>
+      <c r="K106" t="s">
+        <v>16</v>
+      </c>
+      <c r="L106" t="s">
+        <v>16</v>
+      </c>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" t="b">
+        <v>1</v>
+      </c>
+      <c r="O106" t="b">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>100</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>20</v>
+      </c>
+      <c r="R106" t="s">
+        <v>21</v>
+      </c>
+      <c r="S106">
+        <f>VLOOKUP($C106,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T106">
+        <f>VLOOKUP($C106,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U106" t="str">
+        <f>VLOOKUP($C106,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>tp</v>
+      </c>
+      <c r="V106" t="str">
+        <f>VLOOKUP($C106,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>mm</v>
+      </c>
+      <c r="W106" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B107" t="s">
+        <v>152</v>
+      </c>
+      <c r="C107" t="s">
+        <v>152</v>
+      </c>
+      <c r="D107" t="s">
+        <v>87</v>
+      </c>
+      <c r="E107" t="s">
+        <v>88</v>
+      </c>
+      <c r="F107" t="s">
+        <v>99</v>
+      </c>
+      <c r="H107" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I107" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J107" t="s">
+        <v>16</v>
+      </c>
+      <c r="K107" t="s">
+        <v>16</v>
+      </c>
+      <c r="L107" t="s">
+        <v>16</v>
+      </c>
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107" t="b">
+        <v>1</v>
+      </c>
+      <c r="O107" t="b">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>100</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>20</v>
+      </c>
+      <c r="R107" t="s">
+        <v>21</v>
+      </c>
+      <c r="S107">
+        <f>VLOOKUP($C107,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-99999</v>
+      </c>
+      <c r="T107">
+        <f>VLOOKUP($C107,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>99999</v>
+      </c>
+      <c r="U107" t="str">
+        <f>VLOOKUP($C107,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="V107">
+        <f>VLOOKUP($C107,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="W107" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B108" t="s">
+        <v>237</v>
+      </c>
+      <c r="C108" t="s">
+        <v>72</v>
+      </c>
+      <c r="D108" t="s">
+        <v>73</v>
+      </c>
+      <c r="E108" t="s">
+        <v>191</v>
+      </c>
+      <c r="F108" t="s">
+        <v>103</v>
+      </c>
+      <c r="H108" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I108" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J108" t="s">
+        <v>16</v>
+      </c>
+      <c r="K108" t="s">
+        <v>16</v>
+      </c>
+      <c r="L108" t="s">
+        <v>16</v>
+      </c>
+      <c r="M108" t="b">
+        <v>0</v>
+      </c>
+      <c r="N108" t="b">
+        <v>1</v>
+      </c>
+      <c r="O108" t="b">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>100</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>20</v>
+      </c>
+      <c r="R108" t="s">
+        <v>21</v>
+      </c>
+      <c r="S108">
+        <f>VLOOKUP($C108,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="T108">
+        <f>VLOOKUP($C108,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U108" t="str">
+        <f>VLOOKUP($C108,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="V108" t="str">
+        <f>VLOOKUP($C108,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-      <c r="W104" s="2" t="s">
+      <c r="W108" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B109" t="s">
+        <v>74</v>
+      </c>
+      <c r="C109" t="s">
+        <v>74</v>
+      </c>
+      <c r="D109" t="s">
+        <v>75</v>
+      </c>
+      <c r="E109" t="s">
+        <v>175</v>
+      </c>
+      <c r="F109" t="s">
+        <v>101</v>
+      </c>
+      <c r="H109" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I109" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J109" t="s">
+        <v>16</v>
+      </c>
+      <c r="K109" t="s">
+        <v>16</v>
+      </c>
+      <c r="L109" t="s">
+        <v>16</v>
+      </c>
+      <c r="M109" t="b">
+        <v>0</v>
+      </c>
+      <c r="N109" t="b">
+        <v>1</v>
+      </c>
+      <c r="O109" t="b">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>100</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>20</v>
+      </c>
+      <c r="R109" t="s">
+        <v>21</v>
+      </c>
+      <c r="S109">
+        <f>VLOOKUP($C109,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="T109">
+        <f>VLOOKUP($C109,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>120</v>
+      </c>
+      <c r="U109" t="str">
+        <f>VLOOKUP($C109,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="V109" t="str">
+        <f>VLOOKUP($C109,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>percent</v>
+      </c>
+      <c r="W109" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" t="s">
+        <v>238</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D110" t="s">
+        <v>46</v>
+      </c>
+      <c r="E110" t="s">
+        <v>155</v>
+      </c>
+      <c r="F110" t="s">
+        <v>98</v>
+      </c>
+      <c r="H110" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I110" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J110" t="s">
+        <v>16</v>
+      </c>
+      <c r="K110" t="s">
+        <v>16</v>
+      </c>
+      <c r="L110" t="s">
+        <v>16</v>
+      </c>
+      <c r="M110" t="b">
+        <v>0</v>
+      </c>
+      <c r="N110" t="b">
+        <v>1</v>
+      </c>
+      <c r="O110" t="b">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>100</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>20</v>
+      </c>
+      <c r="R110" t="s">
+        <v>21</v>
+      </c>
+      <c r="S110">
+        <f>VLOOKUP($C110,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <f>VLOOKUP($C110,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="U110" t="str">
+        <f>VLOOKUP($C110,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="V110" t="str">
+        <f>VLOOKUP($C110,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B111" t="s">
+        <v>239</v>
+      </c>
+      <c r="C111" t="s">
+        <v>36</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E111" t="s">
+        <v>142</v>
+      </c>
+      <c r="F111" t="s">
+        <v>98</v>
+      </c>
+      <c r="H111" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I111" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J111" t="s">
+        <v>16</v>
+      </c>
+      <c r="K111" t="s">
+        <v>16</v>
+      </c>
+      <c r="L111" t="s">
+        <v>16</v>
+      </c>
+      <c r="M111" t="b">
+        <v>0</v>
+      </c>
+      <c r="N111" t="b">
+        <v>1</v>
+      </c>
+      <c r="O111" t="b">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>100</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>20</v>
+      </c>
+      <c r="R111" t="s">
+        <v>21</v>
+      </c>
+      <c r="S111">
+        <f>VLOOKUP($C111,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T111">
+        <f>VLOOKUP($C111,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U111" t="str">
+        <f>VLOOKUP($C111,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="V111" t="str">
+        <f>VLOOKUP($C111,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" t="s">
+        <v>240</v>
+      </c>
+      <c r="C112" t="s">
+        <v>114</v>
+      </c>
+      <c r="D112" t="s">
+        <v>65</v>
+      </c>
+      <c r="E112" t="s">
+        <v>142</v>
+      </c>
+      <c r="F112" t="s">
+        <v>98</v>
+      </c>
+      <c r="H112" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I112" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J112" t="s">
+        <v>16</v>
+      </c>
+      <c r="K112" t="s">
+        <v>16</v>
+      </c>
+      <c r="L112" t="s">
+        <v>16</v>
+      </c>
+      <c r="M112" t="b">
+        <v>0</v>
+      </c>
+      <c r="N112" t="b">
+        <v>1</v>
+      </c>
+      <c r="O112" t="b">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>100</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>20</v>
+      </c>
+      <c r="R112" t="s">
+        <v>21</v>
+      </c>
+      <c r="S112">
+        <f>VLOOKUP($C112,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-500</v>
+      </c>
+      <c r="T112">
+        <f>VLOOKUP($C112,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="U112" t="str">
+        <f>VLOOKUP($C112,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rn</v>
+      </c>
+      <c r="V112" t="str">
+        <f>VLOOKUP($C112,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+      <c r="W112" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" t="s">
+        <v>56</v>
+      </c>
+      <c r="C113" t="s">
+        <v>56</v>
+      </c>
+      <c r="D113" t="s">
+        <v>57</v>
+      </c>
+      <c r="E113" t="s">
+        <v>229</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H113" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I113" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J113" t="s">
+        <v>16</v>
+      </c>
+      <c r="K113" t="s">
+        <v>16</v>
+      </c>
+      <c r="L113" t="s">
+        <v>16</v>
+      </c>
+      <c r="M113" t="b">
+        <v>0</v>
+      </c>
+      <c r="N113" t="b">
+        <v>1</v>
+      </c>
+      <c r="O113" t="b">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>100</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>20</v>
+      </c>
+      <c r="R113" t="s">
+        <v>21</v>
+      </c>
+      <c r="S113">
+        <f>VLOOKUP($C113,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T113">
+        <f>VLOOKUP($C113,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="U113" t="str">
+        <f>VLOOKUP($C113,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ws</v>
+      </c>
+      <c r="V113" t="str">
+        <f>VLOOKUP($C113,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>m / s</v>
+      </c>
+      <c r="W113" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" t="s">
+        <v>59</v>
+      </c>
+      <c r="C114" t="s">
+        <v>59</v>
+      </c>
+      <c r="D114" t="s">
+        <v>60</v>
+      </c>
+      <c r="E114" t="s">
+        <v>198</v>
+      </c>
+      <c r="F114" t="s">
+        <v>105</v>
+      </c>
+      <c r="H114" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I114" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J114" t="s">
+        <v>16</v>
+      </c>
+      <c r="K114" t="s">
+        <v>16</v>
+      </c>
+      <c r="L114" t="s">
+        <v>16</v>
+      </c>
+      <c r="M114" t="b">
+        <v>0</v>
+      </c>
+      <c r="N114" t="b">
+        <v>1</v>
+      </c>
+      <c r="O114" t="b">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>100</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>20</v>
+      </c>
+      <c r="R114" t="s">
+        <v>21</v>
+      </c>
+      <c r="S114">
+        <f>VLOOKUP($C114,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T114">
+        <f>VLOOKUP($C114,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>360</v>
+      </c>
+      <c r="U114" t="str">
+        <f>VLOOKUP($C114,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>wd</v>
+      </c>
+      <c r="V114" t="str">
+        <f>VLOOKUP($C114,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>degree</v>
+      </c>
+      <c r="W114" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" t="s">
+        <v>241</v>
+      </c>
+      <c r="C115" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115" t="s">
+        <v>175</v>
+      </c>
+      <c r="F115" t="s">
+        <v>102</v>
+      </c>
+      <c r="H115" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I115" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J115" t="s">
+        <v>16</v>
+      </c>
+      <c r="K115" t="s">
+        <v>16</v>
+      </c>
+      <c r="L115" t="s">
+        <v>16</v>
+      </c>
+      <c r="M115" t="b">
+        <v>0</v>
+      </c>
+      <c r="N115" t="b">
+        <v>1</v>
+      </c>
+      <c r="O115" t="b">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>100</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>20</v>
+      </c>
+      <c r="R115" t="s">
+        <v>21</v>
+      </c>
+      <c r="S115">
+        <f>VLOOKUP($C115,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="T115">
+        <f>VLOOKUP($C115,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="U115" t="str">
+        <f>VLOOKUP($C115,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="V115" t="str">
+        <f>VLOOKUP($C115,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>percent</v>
+      </c>
+      <c r="W115" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>18</v>
+      </c>
+      <c r="E116" t="s">
+        <v>191</v>
+      </c>
+      <c r="F116" t="s">
+        <v>103</v>
+      </c>
+      <c r="H116" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I116" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J116" t="s">
+        <v>16</v>
+      </c>
+      <c r="K116" t="s">
+        <v>16</v>
+      </c>
+      <c r="L116" t="s">
+        <v>16</v>
+      </c>
+      <c r="M116" t="b">
+        <v>0</v>
+      </c>
+      <c r="N116" t="b">
+        <v>1</v>
+      </c>
+      <c r="O116" t="b">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>100</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>20</v>
+      </c>
+      <c r="R116" t="s">
+        <v>21</v>
+      </c>
+      <c r="S116">
+        <f>VLOOKUP($C116,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T116">
+        <f>VLOOKUP($C116,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U116" t="str">
+        <f>VLOOKUP($C116,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="V116" t="str">
+        <f>VLOOKUP($C116,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+      <c r="W116" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" t="s">
+        <v>243</v>
+      </c>
+      <c r="C117" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" t="s">
+        <v>18</v>
+      </c>
+      <c r="E117" t="s">
+        <v>191</v>
+      </c>
+      <c r="F117" t="s">
+        <v>103</v>
+      </c>
+      <c r="H117" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I117" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J117" t="s">
+        <v>16</v>
+      </c>
+      <c r="K117" t="s">
+        <v>16</v>
+      </c>
+      <c r="L117" t="s">
+        <v>16</v>
+      </c>
+      <c r="M117" t="b">
+        <v>0</v>
+      </c>
+      <c r="N117" t="b">
+        <v>1</v>
+      </c>
+      <c r="O117" t="b">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>100</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>20</v>
+      </c>
+      <c r="R117" t="s">
+        <v>21</v>
+      </c>
+      <c r="S117">
+        <f>VLOOKUP($C117,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="T117">
+        <f>VLOOKUP($C117,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="U117" t="str">
+        <f>VLOOKUP($C117,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="V117" t="str">
+        <f>VLOOKUP($C117,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+      <c r="W117" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B118" t="s">
+        <v>28</v>
+      </c>
+      <c r="C118" t="s">
+        <v>28</v>
+      </c>
+      <c r="D118" t="s">
+        <v>29</v>
+      </c>
+      <c r="E118" t="s">
+        <v>64</v>
+      </c>
+      <c r="F118" t="s">
+        <v>96</v>
+      </c>
+      <c r="H118" s="1">
+        <v>37257</v>
+      </c>
+      <c r="I118" s="1">
+        <v>47484</v>
+      </c>
+      <c r="J118" t="s">
+        <v>16</v>
+      </c>
+      <c r="K118" t="s">
+        <v>16</v>
+      </c>
+      <c r="L118" t="s">
+        <v>16</v>
+      </c>
+      <c r="M118" t="b">
+        <v>0</v>
+      </c>
+      <c r="N118" t="b">
+        <v>1</v>
+      </c>
+      <c r="O118" t="b">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>100</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>20</v>
+      </c>
+      <c r="R118" t="s">
+        <v>21</v>
+      </c>
+      <c r="S118">
+        <f>VLOOKUP($C118,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="T118">
+        <f>VLOOKUP($C118,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="U118" t="str">
+        <f>VLOOKUP($C118,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="V118" t="str">
+        <f>VLOOKUP($C118,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>m</v>
+      </c>
+      <c r="W118" s="2" t="s">
         <v>232</v>
       </c>
     </row>

--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2265C9-43A6-4054-B5BA-9CFD290FC667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504630FE-0BFE-418B-BD48-B21DADBDF986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5736" yWindow="324" windowWidth="17280" windowHeight="10596" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
@@ -1680,10 +1680,10 @@
   <cols>
     <col min="2" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.77734375" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
     <col min="22" max="22" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="26.77734375" customWidth="1"/>
   </cols>

--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504630FE-0BFE-418B-BD48-B21DADBDF986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A480153-A5CB-4962-96B3-DA1C3040D664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5736" yWindow="324" windowWidth="17280" windowHeight="10596" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
   <sheets>
     <sheet name="dt_meta" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="dt_var_naming" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dt_meta!$A$1:$X$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dt_meta!$A$1:$X$119</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="251">
   <si>
     <t>name_dt</t>
   </si>
@@ -798,7 +798,64 @@
     <t>units_local</t>
   </si>
   <si>
-    <t>TA_2_1_1</t>
+    <t>RH_EB_1_1_1_Avg</t>
+  </si>
+  <si>
+    <t>TA_EB_1_1_1_Avg</t>
+  </si>
+  <si>
+    <t>LWS_EB_7_1_1_Avg</t>
+  </si>
+  <si>
+    <t>PA_EB_1_1_1_Avg</t>
+  </si>
+  <si>
+    <t>P_EB_1_1_1_Tot</t>
+  </si>
+  <si>
+    <t>RN_EB_7_1_1</t>
+  </si>
+  <si>
+    <t>SW_IN_EB_1_1_1</t>
+  </si>
+  <si>
+    <t>PPFD_IN_EB_1_1_1</t>
+  </si>
+  <si>
+    <t>SWC_EB_5_1_1</t>
+  </si>
+  <si>
+    <t>SWC_EB_5_2_1</t>
+  </si>
+  <si>
+    <t>SWC_EB_5_3_1</t>
+  </si>
+  <si>
+    <t>SWC_EB_5_4_1</t>
+  </si>
+  <si>
+    <t>TS_EB_5_1_1</t>
+  </si>
+  <si>
+    <t>TS_EB_5_2_1</t>
+  </si>
+  <si>
+    <t>TS_EB_5_3_1</t>
+  </si>
+  <si>
+    <t>TS_EB_5_4_1</t>
+  </si>
+  <si>
+    <t>G_EB_5_1_1</t>
+  </si>
+  <si>
+    <t>G_EB_5_2_1</t>
+  </si>
+  <si>
+    <t>WTD_EB_5_1_1</t>
+  </si>
+  <si>
+    <t>%Y-%m-%dT%H:%M:%SZ</t>
   </si>
 </sst>
 </file>
@@ -1675,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B621CE1-A4D4-4502-917D-92507EE2F7EE}">
-  <dimension ref="A1:X118"/>
+  <dimension ref="A1:X139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -1786,7 +1843,9 @@
       <c r="H2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
       <c r="J2" t="s">
         <v>11</v>
       </c>
@@ -1862,6 +1921,9 @@
       <c r="H3" t="s">
         <v>90</v>
       </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
       <c r="J3" t="s">
         <v>11</v>
       </c>
@@ -1940,6 +2002,9 @@
       <c r="H4" t="s">
         <v>90</v>
       </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
       <c r="J4">
         <v>4</v>
       </c>
@@ -2092,6 +2157,9 @@
       <c r="H6" t="s">
         <v>92</v>
       </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
       <c r="J6" t="s">
         <v>11</v>
       </c>
@@ -2170,6 +2238,9 @@
       <c r="H7" t="s">
         <v>92</v>
       </c>
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
       <c r="J7">
         <v>4</v>
       </c>
@@ -2248,6 +2319,9 @@
       <c r="H8" t="s">
         <v>92</v>
       </c>
+      <c r="I8" t="s">
+        <v>11</v>
+      </c>
       <c r="J8">
         <v>4</v>
       </c>
@@ -2326,6 +2400,9 @@
       <c r="H9" t="s">
         <v>93</v>
       </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
       <c r="J9" t="s">
         <v>11</v>
       </c>
@@ -2404,6 +2481,9 @@
       <c r="H10" t="s">
         <v>93</v>
       </c>
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
       <c r="J10">
         <v>5</v>
       </c>
@@ -2482,6 +2562,9 @@
       <c r="H11" t="s">
         <v>92</v>
       </c>
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
       <c r="J11" t="s">
         <v>11</v>
       </c>
@@ -2560,6 +2643,9 @@
       <c r="H12" t="s">
         <v>92</v>
       </c>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
       <c r="J12">
         <v>5</v>
       </c>
@@ -2638,6 +2724,9 @@
       <c r="H13" t="s">
         <v>93</v>
       </c>
+      <c r="I13" t="s">
+        <v>11</v>
+      </c>
       <c r="J13">
         <v>4</v>
       </c>
@@ -2716,6 +2805,9 @@
       <c r="H14" t="s">
         <v>93</v>
       </c>
+      <c r="I14" t="s">
+        <v>11</v>
+      </c>
       <c r="J14">
         <v>4</v>
       </c>
@@ -2794,6 +2886,9 @@
       <c r="H15" t="s">
         <v>92</v>
       </c>
+      <c r="I15" t="s">
+        <v>11</v>
+      </c>
       <c r="J15">
         <v>5</v>
       </c>
@@ -2872,6 +2967,9 @@
       <c r="H16" t="s">
         <v>92</v>
       </c>
+      <c r="I16" t="s">
+        <v>11</v>
+      </c>
       <c r="J16">
         <v>5</v>
       </c>
@@ -2950,6 +3048,9 @@
       <c r="H17" t="s">
         <v>92</v>
       </c>
+      <c r="I17" t="s">
+        <v>11</v>
+      </c>
       <c r="J17">
         <v>5</v>
       </c>
@@ -3028,6 +3129,9 @@
       <c r="H18" t="s">
         <v>92</v>
       </c>
+      <c r="I18" t="s">
+        <v>11</v>
+      </c>
       <c r="J18">
         <v>5</v>
       </c>
@@ -3106,6 +3210,9 @@
       <c r="H19" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="I19" t="s">
+        <v>11</v>
+      </c>
       <c r="J19">
         <v>12</v>
       </c>
@@ -3184,6 +3291,9 @@
       <c r="H20" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="I20" t="s">
+        <v>11</v>
+      </c>
       <c r="J20">
         <v>13</v>
       </c>
@@ -3262,6 +3372,9 @@
       <c r="H21" t="s">
         <v>94</v>
       </c>
+      <c r="I21" t="s">
+        <v>11</v>
+      </c>
       <c r="J21">
         <v>4</v>
       </c>
@@ -3340,6 +3453,9 @@
       <c r="H22" t="s">
         <v>92</v>
       </c>
+      <c r="I22" t="s">
+        <v>11</v>
+      </c>
       <c r="J22" t="s">
         <v>11</v>
       </c>
@@ -3418,6 +3534,9 @@
       <c r="H23" t="s">
         <v>92</v>
       </c>
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
       <c r="J23">
         <v>4</v>
       </c>
@@ -3496,6 +3615,9 @@
       <c r="H24" t="s">
         <v>92</v>
       </c>
+      <c r="I24" t="s">
+        <v>11</v>
+      </c>
       <c r="J24">
         <v>4</v>
       </c>
@@ -3574,6 +3696,9 @@
       <c r="H25" t="s">
         <v>92</v>
       </c>
+      <c r="I25" t="s">
+        <v>11</v>
+      </c>
       <c r="J25">
         <v>5</v>
       </c>
@@ -3652,6 +3777,9 @@
       <c r="H26" t="s">
         <v>92</v>
       </c>
+      <c r="I26" t="s">
+        <v>11</v>
+      </c>
       <c r="J26">
         <v>5</v>
       </c>
@@ -3730,6 +3858,9 @@
       <c r="H27" t="s">
         <v>92</v>
       </c>
+      <c r="I27" t="s">
+        <v>11</v>
+      </c>
       <c r="J27" t="s">
         <v>11</v>
       </c>
@@ -3808,6 +3939,9 @@
       <c r="H28" t="s">
         <v>92</v>
       </c>
+      <c r="I28" t="s">
+        <v>11</v>
+      </c>
       <c r="J28">
         <v>5</v>
       </c>
@@ -3886,6 +4020,9 @@
       <c r="H29" t="s">
         <v>92</v>
       </c>
+      <c r="I29" t="s">
+        <v>11</v>
+      </c>
       <c r="J29">
         <v>4</v>
       </c>
@@ -3964,6 +4101,9 @@
       <c r="H30" t="s">
         <v>95</v>
       </c>
+      <c r="I30" t="s">
+        <v>11</v>
+      </c>
       <c r="J30">
         <v>2</v>
       </c>
@@ -4042,6 +4182,9 @@
       <c r="H31" t="s">
         <v>95</v>
       </c>
+      <c r="I31" t="s">
+        <v>11</v>
+      </c>
       <c r="J31">
         <v>4</v>
       </c>
@@ -4120,6 +4263,9 @@
       <c r="H32" t="s">
         <v>95</v>
       </c>
+      <c r="I32" t="s">
+        <v>11</v>
+      </c>
       <c r="J32">
         <v>7</v>
       </c>
@@ -4198,6 +4344,9 @@
       <c r="H33" t="s">
         <v>92</v>
       </c>
+      <c r="I33" t="s">
+        <v>11</v>
+      </c>
       <c r="J33">
         <v>5</v>
       </c>
@@ -4276,6 +4425,9 @@
       <c r="H34" t="s">
         <v>92</v>
       </c>
+      <c r="I34" t="s">
+        <v>11</v>
+      </c>
       <c r="J34" t="s">
         <v>11</v>
       </c>
@@ -4354,6 +4506,9 @@
       <c r="H35" t="s">
         <v>92</v>
       </c>
+      <c r="I35" t="s">
+        <v>11</v>
+      </c>
       <c r="J35">
         <v>5</v>
       </c>
@@ -4432,6 +4587,9 @@
       <c r="H36" t="s">
         <v>92</v>
       </c>
+      <c r="I36" t="s">
+        <v>11</v>
+      </c>
       <c r="J36">
         <v>7</v>
       </c>
@@ -4510,6 +4668,9 @@
       <c r="H37" t="s">
         <v>92</v>
       </c>
+      <c r="I37" t="s">
+        <v>11</v>
+      </c>
       <c r="J37" t="s">
         <v>11</v>
       </c>
@@ -4588,6 +4749,9 @@
       <c r="H38" t="s">
         <v>92</v>
       </c>
+      <c r="I38" t="s">
+        <v>11</v>
+      </c>
       <c r="J38">
         <v>5</v>
       </c>
@@ -4666,6 +4830,9 @@
       <c r="H39" t="s">
         <v>96</v>
       </c>
+      <c r="I39" t="s">
+        <v>11</v>
+      </c>
       <c r="J39" t="s">
         <v>11</v>
       </c>
@@ -4744,6 +4911,9 @@
       <c r="H40" t="s">
         <v>96</v>
       </c>
+      <c r="I40" t="s">
+        <v>11</v>
+      </c>
       <c r="J40">
         <v>4</v>
       </c>
@@ -4822,6 +4992,9 @@
       <c r="H41" t="s">
         <v>96</v>
       </c>
+      <c r="I41" t="s">
+        <v>11</v>
+      </c>
       <c r="J41">
         <v>4</v>
       </c>
@@ -4900,6 +5073,9 @@
       <c r="H42" t="s">
         <v>96</v>
       </c>
+      <c r="I42" t="s">
+        <v>11</v>
+      </c>
       <c r="J42">
         <v>4</v>
       </c>
@@ -4978,6 +5154,9 @@
       <c r="H43" t="s">
         <v>96</v>
       </c>
+      <c r="I43" t="s">
+        <v>11</v>
+      </c>
       <c r="J43">
         <v>4</v>
       </c>
@@ -5056,6 +5235,9 @@
       <c r="H44" t="s">
         <v>97</v>
       </c>
+      <c r="I44" t="s">
+        <v>11</v>
+      </c>
       <c r="J44">
         <v>2</v>
       </c>
@@ -5134,6 +5316,9 @@
       <c r="H45" t="s">
         <v>97</v>
       </c>
+      <c r="I45" t="s">
+        <v>11</v>
+      </c>
       <c r="J45">
         <v>4</v>
       </c>
@@ -5212,6 +5397,9 @@
       <c r="H46" t="s">
         <v>97</v>
       </c>
+      <c r="I46" t="s">
+        <v>11</v>
+      </c>
       <c r="J46">
         <v>7</v>
       </c>
@@ -5364,6 +5552,9 @@
       <c r="H48" t="s">
         <v>99</v>
       </c>
+      <c r="I48" t="s">
+        <v>11</v>
+      </c>
       <c r="J48">
         <v>6</v>
       </c>
@@ -5442,6 +5633,9 @@
       <c r="H49" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="I49" t="s">
+        <v>11</v>
+      </c>
       <c r="J49">
         <v>6</v>
       </c>
@@ -5520,6 +5714,9 @@
       <c r="H50" t="s">
         <v>99</v>
       </c>
+      <c r="I50" t="s">
+        <v>11</v>
+      </c>
       <c r="J50">
         <v>7</v>
       </c>
@@ -5598,6 +5795,9 @@
       <c r="H51" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="I51" t="s">
+        <v>11</v>
+      </c>
       <c r="J51">
         <v>7</v>
       </c>
@@ -5676,6 +5876,9 @@
       <c r="H52" t="s">
         <v>90</v>
       </c>
+      <c r="I52" t="s">
+        <v>11</v>
+      </c>
       <c r="J52" t="s">
         <v>11</v>
       </c>
@@ -5754,6 +5957,9 @@
       <c r="H53" t="s">
         <v>90</v>
       </c>
+      <c r="I53" t="s">
+        <v>11</v>
+      </c>
       <c r="J53">
         <v>4</v>
       </c>
@@ -5832,6 +6038,9 @@
       <c r="H54" t="s">
         <v>97</v>
       </c>
+      <c r="I54" t="s">
+        <v>11</v>
+      </c>
       <c r="J54" t="s">
         <v>11</v>
       </c>
@@ -5910,6 +6119,9 @@
       <c r="H55" t="s">
         <v>97</v>
       </c>
+      <c r="I55" t="s">
+        <v>11</v>
+      </c>
       <c r="J55">
         <v>4</v>
       </c>
@@ -5988,6 +6200,9 @@
       <c r="H56" t="s">
         <v>97</v>
       </c>
+      <c r="I56" t="s">
+        <v>11</v>
+      </c>
       <c r="J56">
         <v>4</v>
       </c>
@@ -6066,6 +6281,9 @@
       <c r="H57" t="s">
         <v>97</v>
       </c>
+      <c r="I57" t="s">
+        <v>11</v>
+      </c>
       <c r="J57">
         <v>4</v>
       </c>
@@ -6144,6 +6362,9 @@
       <c r="H58" t="s">
         <v>97</v>
       </c>
+      <c r="I58" t="s">
+        <v>11</v>
+      </c>
       <c r="J58">
         <v>4</v>
       </c>
@@ -6222,6 +6443,9 @@
       <c r="H59" t="s">
         <v>97</v>
       </c>
+      <c r="I59" t="s">
+        <v>11</v>
+      </c>
       <c r="J59">
         <v>8</v>
       </c>
@@ -6300,6 +6524,9 @@
       <c r="H60" t="s">
         <v>97</v>
       </c>
+      <c r="I60" t="s">
+        <v>11</v>
+      </c>
       <c r="J60">
         <v>8</v>
       </c>
@@ -6378,6 +6605,9 @@
       <c r="H61" t="s">
         <v>97</v>
       </c>
+      <c r="I61" t="s">
+        <v>11</v>
+      </c>
       <c r="J61">
         <v>8</v>
       </c>
@@ -6456,6 +6686,9 @@
       <c r="H62" t="s">
         <v>97</v>
       </c>
+      <c r="I62" t="s">
+        <v>11</v>
+      </c>
       <c r="J62">
         <v>8</v>
       </c>
@@ -6534,6 +6767,9 @@
       <c r="H63" t="s">
         <v>97</v>
       </c>
+      <c r="I63" t="s">
+        <v>11</v>
+      </c>
       <c r="J63">
         <v>8</v>
       </c>
@@ -6612,6 +6848,9 @@
       <c r="H64" t="s">
         <v>97</v>
       </c>
+      <c r="I64" t="s">
+        <v>11</v>
+      </c>
       <c r="J64">
         <v>9</v>
       </c>
@@ -6690,6 +6929,9 @@
       <c r="H65" t="s">
         <v>97</v>
       </c>
+      <c r="I65" t="s">
+        <v>11</v>
+      </c>
       <c r="J65">
         <v>9</v>
       </c>
@@ -6768,6 +7010,9 @@
       <c r="H66" t="s">
         <v>97</v>
       </c>
+      <c r="I66" t="s">
+        <v>11</v>
+      </c>
       <c r="J66">
         <v>9</v>
       </c>
@@ -6846,6 +7091,9 @@
       <c r="H67" t="s">
         <v>97</v>
       </c>
+      <c r="I67" t="s">
+        <v>11</v>
+      </c>
       <c r="J67">
         <v>9</v>
       </c>
@@ -6924,6 +7172,9 @@
       <c r="H68" t="s">
         <v>97</v>
       </c>
+      <c r="I68" t="s">
+        <v>11</v>
+      </c>
       <c r="J68">
         <v>9</v>
       </c>
@@ -7002,6 +7253,9 @@
       <c r="H69" t="s">
         <v>92</v>
       </c>
+      <c r="I69" t="s">
+        <v>11</v>
+      </c>
       <c r="J69">
         <v>8</v>
       </c>
@@ -7080,6 +7334,9 @@
       <c r="H70" t="s">
         <v>92</v>
       </c>
+      <c r="I70" t="s">
+        <v>11</v>
+      </c>
       <c r="J70">
         <v>9</v>
       </c>
@@ -7158,6 +7415,9 @@
       <c r="H71" t="s">
         <v>92</v>
       </c>
+      <c r="I71" t="s">
+        <v>11</v>
+      </c>
       <c r="J71">
         <v>10</v>
       </c>
@@ -7236,6 +7496,9 @@
       <c r="H72" t="s">
         <v>92</v>
       </c>
+      <c r="I72" t="s">
+        <v>11</v>
+      </c>
       <c r="J72">
         <v>11</v>
       </c>
@@ -7314,6 +7577,9 @@
       <c r="H73" t="s">
         <v>90</v>
       </c>
+      <c r="I73" t="s">
+        <v>11</v>
+      </c>
       <c r="J73">
         <v>8</v>
       </c>
@@ -7392,6 +7658,9 @@
       <c r="H74" t="s">
         <v>90</v>
       </c>
+      <c r="I74" t="s">
+        <v>11</v>
+      </c>
       <c r="J74">
         <v>9</v>
       </c>
@@ -7470,6 +7739,9 @@
       <c r="H75" t="s">
         <v>90</v>
       </c>
+      <c r="I75" t="s">
+        <v>11</v>
+      </c>
       <c r="J75">
         <v>10</v>
       </c>
@@ -7548,6 +7820,9 @@
       <c r="H76" t="s">
         <v>90</v>
       </c>
+      <c r="I76" t="s">
+        <v>11</v>
+      </c>
       <c r="J76">
         <v>11</v>
       </c>
@@ -7626,6 +7901,9 @@
       <c r="H77" t="s">
         <v>96</v>
       </c>
+      <c r="I77" t="s">
+        <v>11</v>
+      </c>
       <c r="J77">
         <v>8</v>
       </c>
@@ -7704,6 +7982,9 @@
       <c r="H78" t="s">
         <v>96</v>
       </c>
+      <c r="I78" t="s">
+        <v>11</v>
+      </c>
       <c r="J78">
         <v>8</v>
       </c>
@@ -7782,6 +8063,9 @@
       <c r="H79" t="s">
         <v>96</v>
       </c>
+      <c r="I79" t="s">
+        <v>11</v>
+      </c>
       <c r="J79">
         <v>8</v>
       </c>
@@ -7860,6 +8144,9 @@
       <c r="H80" t="s">
         <v>96</v>
       </c>
+      <c r="I80" t="s">
+        <v>11</v>
+      </c>
       <c r="J80">
         <v>8</v>
       </c>
@@ -7938,6 +8225,9 @@
       <c r="H81" t="s">
         <v>96</v>
       </c>
+      <c r="I81" t="s">
+        <v>11</v>
+      </c>
       <c r="J81">
         <v>9</v>
       </c>
@@ -8016,6 +8306,9 @@
       <c r="H82" t="s">
         <v>96</v>
       </c>
+      <c r="I82" t="s">
+        <v>11</v>
+      </c>
       <c r="J82">
         <v>9</v>
       </c>
@@ -8094,6 +8387,9 @@
       <c r="H83" t="s">
         <v>96</v>
       </c>
+      <c r="I83" t="s">
+        <v>11</v>
+      </c>
       <c r="J83">
         <v>9</v>
       </c>
@@ -8172,6 +8468,9 @@
       <c r="H84" t="s">
         <v>96</v>
       </c>
+      <c r="I84" t="s">
+        <v>11</v>
+      </c>
       <c r="J84">
         <v>9</v>
       </c>
@@ -8250,6 +8549,9 @@
       <c r="H85" t="s">
         <v>97</v>
       </c>
+      <c r="I85" t="s">
+        <v>11</v>
+      </c>
       <c r="J85">
         <v>10</v>
       </c>
@@ -8328,6 +8630,9 @@
       <c r="H86" t="s">
         <v>97</v>
       </c>
+      <c r="I86" t="s">
+        <v>11</v>
+      </c>
       <c r="J86">
         <v>10</v>
       </c>
@@ -8406,6 +8711,9 @@
       <c r="H87" t="s">
         <v>97</v>
       </c>
+      <c r="I87" t="s">
+        <v>11</v>
+      </c>
       <c r="J87">
         <v>10</v>
       </c>
@@ -8484,6 +8792,9 @@
       <c r="H88" t="s">
         <v>97</v>
       </c>
+      <c r="I88" t="s">
+        <v>11</v>
+      </c>
       <c r="J88">
         <v>10</v>
       </c>
@@ -8562,6 +8873,9 @@
       <c r="H89" t="s">
         <v>97</v>
       </c>
+      <c r="I89" t="s">
+        <v>11</v>
+      </c>
       <c r="J89">
         <v>10</v>
       </c>
@@ -8640,6 +8954,9 @@
       <c r="H90" t="s">
         <v>97</v>
       </c>
+      <c r="I90" t="s">
+        <v>11</v>
+      </c>
       <c r="J90">
         <v>11</v>
       </c>
@@ -8718,6 +9035,9 @@
       <c r="H91" t="s">
         <v>97</v>
       </c>
+      <c r="I91" t="s">
+        <v>11</v>
+      </c>
       <c r="J91">
         <v>11</v>
       </c>
@@ -8796,6 +9116,9 @@
       <c r="H92" t="s">
         <v>97</v>
       </c>
+      <c r="I92" t="s">
+        <v>11</v>
+      </c>
       <c r="J92">
         <v>11</v>
       </c>
@@ -8874,6 +9197,9 @@
       <c r="H93" t="s">
         <v>97</v>
       </c>
+      <c r="I93" t="s">
+        <v>11</v>
+      </c>
       <c r="J93">
         <v>11</v>
       </c>
@@ -8952,6 +9278,9 @@
       <c r="H94" t="s">
         <v>97</v>
       </c>
+      <c r="I94" t="s">
+        <v>11</v>
+      </c>
       <c r="J94">
         <v>11</v>
       </c>
@@ -9030,6 +9359,9 @@
       <c r="H95" t="s">
         <v>96</v>
       </c>
+      <c r="I95" t="s">
+        <v>11</v>
+      </c>
       <c r="J95">
         <v>10</v>
       </c>
@@ -9108,6 +9440,9 @@
       <c r="H96" t="s">
         <v>96</v>
       </c>
+      <c r="I96" t="s">
+        <v>11</v>
+      </c>
       <c r="J96">
         <v>10</v>
       </c>
@@ -9186,6 +9521,9 @@
       <c r="H97" t="s">
         <v>96</v>
       </c>
+      <c r="I97" t="s">
+        <v>11</v>
+      </c>
       <c r="J97">
         <v>10</v>
       </c>
@@ -9264,6 +9602,9 @@
       <c r="H98" t="s">
         <v>96</v>
       </c>
+      <c r="I98" t="s">
+        <v>11</v>
+      </c>
       <c r="J98">
         <v>10</v>
       </c>
@@ -9342,6 +9683,9 @@
       <c r="H99" t="s">
         <v>96</v>
       </c>
+      <c r="I99" t="s">
+        <v>11</v>
+      </c>
       <c r="J99">
         <v>11</v>
       </c>
@@ -9420,6 +9764,9 @@
       <c r="H100" t="s">
         <v>96</v>
       </c>
+      <c r="I100" t="s">
+        <v>11</v>
+      </c>
       <c r="J100">
         <v>11</v>
       </c>
@@ -9498,6 +9845,9 @@
       <c r="H101" t="s">
         <v>96</v>
       </c>
+      <c r="I101" t="s">
+        <v>11</v>
+      </c>
       <c r="J101">
         <v>11</v>
       </c>
@@ -9576,6 +9926,9 @@
       <c r="H102" t="s">
         <v>96</v>
       </c>
+      <c r="I102" t="s">
+        <v>11</v>
+      </c>
       <c r="J102">
         <v>11</v>
       </c>
@@ -9652,6 +10005,9 @@
       <c r="H103" t="s">
         <v>103</v>
       </c>
+      <c r="I103" t="s">
+        <v>11</v>
+      </c>
       <c r="J103" t="s">
         <v>11</v>
       </c>
@@ -9807,6 +10163,9 @@
       <c r="H105" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="I105" t="s">
+        <v>11</v>
+      </c>
       <c r="J105">
         <v>1</v>
       </c>
@@ -9883,6 +10242,9 @@
       <c r="H106" t="s">
         <v>93</v>
       </c>
+      <c r="I106" t="s">
+        <v>11</v>
+      </c>
       <c r="J106">
         <v>1</v>
       </c>
@@ -9959,6 +10321,9 @@
       <c r="H107" t="s">
         <v>97</v>
       </c>
+      <c r="I107" t="s">
+        <v>11</v>
+      </c>
       <c r="J107">
         <v>1</v>
       </c>
@@ -10035,6 +10400,9 @@
       <c r="H108" t="s">
         <v>95</v>
       </c>
+      <c r="I108" t="s">
+        <v>11</v>
+      </c>
       <c r="J108">
         <v>1</v>
       </c>
@@ -10111,6 +10479,9 @@
       <c r="H109" t="s">
         <v>92</v>
       </c>
+      <c r="I109" t="s">
+        <v>11</v>
+      </c>
       <c r="J109">
         <v>1</v>
       </c>
@@ -10187,6 +10558,9 @@
       <c r="H110" t="s">
         <v>92</v>
       </c>
+      <c r="I110" t="s">
+        <v>11</v>
+      </c>
       <c r="J110">
         <v>1</v>
       </c>
@@ -10263,6 +10637,9 @@
       <c r="H111" t="s">
         <v>92</v>
       </c>
+      <c r="I111" t="s">
+        <v>11</v>
+      </c>
       <c r="J111">
         <v>1</v>
       </c>
@@ -10339,6 +10716,9 @@
       <c r="H112" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="I112" t="s">
+        <v>11</v>
+      </c>
       <c r="J112">
         <v>1</v>
       </c>
@@ -10415,6 +10795,9 @@
       <c r="H113" t="s">
         <v>99</v>
       </c>
+      <c r="I113" t="s">
+        <v>11</v>
+      </c>
       <c r="J113">
         <v>1</v>
       </c>
@@ -10491,6 +10874,9 @@
       <c r="H114" t="s">
         <v>96</v>
       </c>
+      <c r="I114" t="s">
+        <v>11</v>
+      </c>
       <c r="J114">
         <v>1</v>
       </c>
@@ -10567,6 +10953,9 @@
       <c r="H115" t="s">
         <v>97</v>
       </c>
+      <c r="I115" t="s">
+        <v>11</v>
+      </c>
       <c r="J115">
         <v>1</v>
       </c>
@@ -10643,6 +11032,9 @@
       <c r="H116" t="s">
         <v>97</v>
       </c>
+      <c r="I116" t="s">
+        <v>11</v>
+      </c>
       <c r="J116">
         <v>1</v>
       </c>
@@ -10719,6 +11111,9 @@
       <c r="H117" t="s">
         <v>90</v>
       </c>
+      <c r="I117" t="s">
+        <v>11</v>
+      </c>
       <c r="J117">
         <v>1</v>
       </c>
@@ -10775,77 +11170,1664 @@
         <v>105</v>
       </c>
       <c r="B118" s="1">
-        <v>34700</v>
+        <v>45139.541666666664</v>
       </c>
       <c r="C118" s="1">
-        <v>47484</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E118" s="2" t="str">
-        <f>V118&amp;"_"&amp;J118&amp;"_"&amp;K118&amp;"_"&amp;L118</f>
-        <v>TA_2_1_1</v>
+        <v>45292</v>
+      </c>
+      <c r="D118" t="s">
+        <v>103</v>
+      </c>
+      <c r="E118" t="s">
+        <v>103</v>
       </c>
       <c r="F118" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="G118" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H118" t="s">
-        <v>97</v>
-      </c>
-      <c r="J118">
-        <v>2</v>
-      </c>
-      <c r="K118">
-        <v>1</v>
-      </c>
-      <c r="L118">
-        <v>1</v>
+        <v>103</v>
+      </c>
+      <c r="I118" t="s">
+        <v>11</v>
+      </c>
+      <c r="J118" t="s">
+        <v>11</v>
+      </c>
+      <c r="K118" t="s">
+        <v>11</v>
+      </c>
+      <c r="L118" t="s">
+        <v>11</v>
       </c>
       <c r="M118" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N118" t="s">
-        <v>16</v>
-      </c>
-      <c r="O118">
+        <v>11</v>
+      </c>
+      <c r="O118" t="e">
         <f>VLOOKUP($V118,naming_lookup!$C$1:$H$40,3,FALSE)</f>
-        <v>-40</v>
-      </c>
-      <c r="P118">
+        <v>#N/A</v>
+      </c>
+      <c r="P118" t="e">
         <f>VLOOKUP($V118,naming_lookup!$C$1:$H$40,4,FALSE)</f>
-        <v>50</v>
-      </c>
-      <c r="Q118">
-        <v>100</v>
-      </c>
-      <c r="R118" s="2" t="s">
-        <v>210</v>
+        <v>#N/A</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>11</v>
+      </c>
+      <c r="R118" t="s">
+        <v>11</v>
       </c>
       <c r="S118" t="str">
         <f>VLOOKUP($V118,naming_lookup!$C$1:$H$40,5,FALSE)</f>
-        <v>t2m</v>
+        <v>site</v>
       </c>
       <c r="T118" t="str">
         <f>VLOOKUP($V118,naming_lookup!$C$1:$H$40,5,FALSE)</f>
-        <v>t2m</v>
+        <v>site</v>
       </c>
       <c r="U118" t="str">
         <f>VLOOKUP($V118,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="V118" t="s">
+        <v>103</v>
+      </c>
+      <c r="W118" t="s">
+        <v>103</v>
+      </c>
+      <c r="X118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B119" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C119" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G119" t="s">
+        <v>11</v>
+      </c>
+      <c r="H119" t="s">
+        <v>91</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J119" t="s">
+        <v>11</v>
+      </c>
+      <c r="K119" t="s">
+        <v>11</v>
+      </c>
+      <c r="L119" t="s">
+        <v>11</v>
+      </c>
+      <c r="M119" t="s">
+        <v>15</v>
+      </c>
+      <c r="N119" t="s">
+        <v>16</v>
+      </c>
+      <c r="O119" t="e">
+        <f>VLOOKUP($V119,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="P119" t="e">
+        <f>VLOOKUP($V119,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>11</v>
+      </c>
+      <c r="R119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S119" t="str">
+        <f>VLOOKUP($V119,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>time</v>
+      </c>
+      <c r="T119" t="str">
+        <f>VLOOKUP($V119,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>time</v>
+      </c>
+      <c r="U119" t="str">
+        <f>VLOOKUP($V119,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>NA</v>
+      </c>
+      <c r="V119" t="s">
+        <v>85</v>
+      </c>
+      <c r="W119" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B120" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C120" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D120" t="s">
+        <v>231</v>
+      </c>
+      <c r="E120" t="s">
+        <v>231</v>
+      </c>
+      <c r="F120" t="s">
+        <v>70</v>
+      </c>
+      <c r="G120" t="s">
+        <v>158</v>
+      </c>
+      <c r="H120" t="s">
+        <v>95</v>
+      </c>
+      <c r="I120" t="s">
+        <v>11</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120" t="s">
+        <v>15</v>
+      </c>
+      <c r="N120" t="s">
+        <v>16</v>
+      </c>
+      <c r="O120">
+        <f>VLOOKUP($V120,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="P120">
+        <f>VLOOKUP($V120,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>120</v>
+      </c>
+      <c r="Q120">
+        <v>100</v>
+      </c>
+      <c r="R120" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S120" t="str">
+        <f>VLOOKUP($V120,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="T120" t="str">
+        <f>VLOOKUP($V120,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="U120" t="str">
+        <f>VLOOKUP($V120,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>percent</v>
+      </c>
+      <c r="V120" t="s">
+        <v>69</v>
+      </c>
+      <c r="W120" t="s">
+        <v>70</v>
+      </c>
+      <c r="X120" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B121" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C121" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D121" t="s">
+        <v>232</v>
+      </c>
+      <c r="E121" t="s">
+        <v>232</v>
+      </c>
+      <c r="F121" t="s">
+        <v>68</v>
+      </c>
+      <c r="G121" t="s">
+        <v>174</v>
+      </c>
+      <c r="H121" t="s">
+        <v>97</v>
+      </c>
+      <c r="I121" t="s">
+        <v>11</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121" t="s">
+        <v>15</v>
+      </c>
+      <c r="N121" t="s">
+        <v>16</v>
+      </c>
+      <c r="O121">
+        <f>VLOOKUP($V121,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-40</v>
+      </c>
+      <c r="P121">
+        <f>VLOOKUP($V121,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="Q121">
+        <v>100</v>
+      </c>
+      <c r="R121" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S121" t="str">
+        <f>VLOOKUP($V121,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="T121" t="str">
+        <f>VLOOKUP($V121,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>t2m</v>
+      </c>
+      <c r="U121" t="str">
+        <f>VLOOKUP($V121,naming_lookup!$C$1:$H$40,6,FALSE)</f>
         <v>degree_C</v>
       </c>
-      <c r="V118" t="s">
+      <c r="V121" t="s">
         <v>67</v>
       </c>
-      <c r="W118" t="s">
+      <c r="W121" t="s">
         <v>68</v>
       </c>
-      <c r="X118" t="s">
-        <v>14</v>
-      </c>
+      <c r="X121" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B122" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C122" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D122" t="s">
+        <v>233</v>
+      </c>
+      <c r="E122" t="s">
+        <v>233</v>
+      </c>
+      <c r="F122" t="s">
+        <v>82</v>
+      </c>
+      <c r="G122" t="s">
+        <v>83</v>
+      </c>
+      <c r="H122" t="s">
+        <v>93</v>
+      </c>
+      <c r="I122" t="s">
+        <v>11</v>
+      </c>
+      <c r="J122">
+        <v>7</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122" t="s">
+        <v>15</v>
+      </c>
+      <c r="N122" t="s">
+        <v>16</v>
+      </c>
+      <c r="O122">
+        <f>VLOOKUP($V122,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-99999</v>
+      </c>
+      <c r="P122">
+        <f>VLOOKUP($V122,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>99999</v>
+      </c>
+      <c r="Q122">
+        <v>100</v>
+      </c>
+      <c r="R122" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S122" t="str">
+        <f>VLOOKUP($V122,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="T122" t="str">
+        <f>VLOOKUP($V122,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rh</v>
+      </c>
+      <c r="U122">
+        <f>VLOOKUP($V122,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="V122" t="s">
+        <v>135</v>
+      </c>
+      <c r="W122" t="s">
+        <v>82</v>
+      </c>
+      <c r="X122" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B123" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C123" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D123" t="s">
+        <v>234</v>
+      </c>
+      <c r="E123" t="s">
+        <v>234</v>
+      </c>
+      <c r="F123" t="s">
+        <v>29</v>
+      </c>
+      <c r="G123" t="s">
+        <v>30</v>
+      </c>
+      <c r="H123" t="s">
+        <v>94</v>
+      </c>
+      <c r="I123" t="s">
+        <v>11</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123" t="s">
+        <v>15</v>
+      </c>
+      <c r="N123" t="s">
+        <v>16</v>
+      </c>
+      <c r="O123">
+        <f>VLOOKUP($V123,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>90</v>
+      </c>
+      <c r="P123">
+        <f>VLOOKUP($V123,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>130</v>
+      </c>
+      <c r="Q123">
+        <v>100</v>
+      </c>
+      <c r="R123" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S123" t="str">
+        <f>VLOOKUP($V123,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>sp</v>
+      </c>
+      <c r="T123" t="str">
+        <f>VLOOKUP($V123,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>sp</v>
+      </c>
+      <c r="U123" t="str">
+        <f>VLOOKUP($V123,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>kPa</v>
+      </c>
+      <c r="V123" t="s">
+        <v>28</v>
+      </c>
+      <c r="W123" t="s">
+        <v>29</v>
+      </c>
+      <c r="X123" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B124" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C124" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D124" t="s">
+        <v>235</v>
+      </c>
+      <c r="E124" t="s">
+        <v>235</v>
+      </c>
+      <c r="F124" t="s">
+        <v>49</v>
+      </c>
+      <c r="G124" t="s">
+        <v>208</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I124" t="s">
+        <v>11</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124" t="s">
+        <v>15</v>
+      </c>
+      <c r="N124" t="s">
+        <v>16</v>
+      </c>
+      <c r="O124">
+        <f>VLOOKUP($V124,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <f>VLOOKUP($V124,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="Q124">
+        <v>100</v>
+      </c>
+      <c r="R124" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S124" t="str">
+        <f>VLOOKUP($V124,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>tp</v>
+      </c>
+      <c r="T124" t="str">
+        <f>VLOOKUP($V124,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>tp</v>
+      </c>
+      <c r="U124" t="str">
+        <f>VLOOKUP($V124,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>mm</v>
+      </c>
+      <c r="V124" t="s">
+        <v>48</v>
+      </c>
+      <c r="W124" t="s">
+        <v>49</v>
+      </c>
+      <c r="X124" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B125" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C125" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D125" t="s">
+        <v>236</v>
+      </c>
+      <c r="E125" t="s">
+        <v>236</v>
+      </c>
+      <c r="F125" t="s">
+        <v>60</v>
+      </c>
+      <c r="G125" t="s">
+        <v>125</v>
+      </c>
+      <c r="H125" t="s">
+        <v>92</v>
+      </c>
+      <c r="I125" t="s">
+        <v>11</v>
+      </c>
+      <c r="J125">
+        <v>7</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125" t="s">
+        <v>15</v>
+      </c>
+      <c r="N125" t="s">
+        <v>16</v>
+      </c>
+      <c r="O125">
+        <f>VLOOKUP($V125,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-500</v>
+      </c>
+      <c r="P125">
+        <f>VLOOKUP($V125,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="Q125">
+        <v>100</v>
+      </c>
+      <c r="R125" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S125" t="str">
+        <f>VLOOKUP($V125,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rn</v>
+      </c>
+      <c r="T125" t="str">
+        <f>VLOOKUP($V125,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>rn</v>
+      </c>
+      <c r="U125" t="str">
+        <f>VLOOKUP($V125,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+      <c r="V125" t="s">
+        <v>100</v>
+      </c>
+      <c r="W125" t="s">
+        <v>60</v>
+      </c>
+      <c r="X125" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B126" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C126" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D126" t="s">
+        <v>237</v>
+      </c>
+      <c r="E126" t="s">
+        <v>237</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G126" t="s">
+        <v>125</v>
+      </c>
+      <c r="H126" t="s">
+        <v>92</v>
+      </c>
+      <c r="I126" t="s">
+        <v>11</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126" t="s">
+        <v>15</v>
+      </c>
+      <c r="N126" t="s">
+        <v>16</v>
+      </c>
+      <c r="O126">
+        <f>VLOOKUP($V126,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <f>VLOOKUP($V126,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="Q126">
+        <v>100</v>
+      </c>
+      <c r="R126" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S126" t="str">
+        <f>VLOOKUP($V126,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T126" t="str">
+        <f>VLOOKUP($V126,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="U126" t="str">
+        <f>VLOOKUP($V126,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+      <c r="V126" t="s">
+        <v>31</v>
+      </c>
+      <c r="W126" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="X126" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B127" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C127" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D127" t="s">
+        <v>238</v>
+      </c>
+      <c r="E127" t="s">
+        <v>238</v>
+      </c>
+      <c r="F127" t="s">
+        <v>41</v>
+      </c>
+      <c r="G127" t="s">
+        <v>138</v>
+      </c>
+      <c r="H127" t="s">
+        <v>92</v>
+      </c>
+      <c r="I127" t="s">
+        <v>11</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127" t="s">
+        <v>15</v>
+      </c>
+      <c r="N127" t="s">
+        <v>16</v>
+      </c>
+      <c r="O127">
+        <f>VLOOKUP($V127,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <f>VLOOKUP($V127,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>2200</v>
+      </c>
+      <c r="Q127">
+        <v>100</v>
+      </c>
+      <c r="R127" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S127" t="str">
+        <f>VLOOKUP($V127,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T127" t="str">
+        <f>VLOOKUP($V127,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="U127" t="str">
+        <f>VLOOKUP($V127,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>micromol / m^2 / s</v>
+      </c>
+      <c r="V127" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W127" t="s">
+        <v>41</v>
+      </c>
+      <c r="X127" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B128" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C128" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D128" t="s">
+        <v>239</v>
+      </c>
+      <c r="E128" t="s">
+        <v>239</v>
+      </c>
+      <c r="F128" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" t="s">
+        <v>158</v>
+      </c>
+      <c r="H128" t="s">
+        <v>96</v>
+      </c>
+      <c r="I128" t="s">
+        <v>11</v>
+      </c>
+      <c r="J128">
+        <v>5</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128" t="s">
+        <v>15</v>
+      </c>
+      <c r="N128" t="s">
+        <v>16</v>
+      </c>
+      <c r="O128">
+        <f>VLOOKUP($V128,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <f>VLOOKUP($V128,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="Q128">
+        <v>100</v>
+      </c>
+      <c r="R128" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S128" t="str">
+        <f>VLOOKUP($V128,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T128" t="str">
+        <f>VLOOKUP($V128,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="U128" t="str">
+        <f>VLOOKUP($V128,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>percent</v>
+      </c>
+      <c r="V128" t="s">
+        <v>17</v>
+      </c>
+      <c r="W128" t="s">
+        <v>18</v>
+      </c>
+      <c r="X128" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B129" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C129" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D129" t="s">
+        <v>240</v>
+      </c>
+      <c r="E129" t="s">
+        <v>240</v>
+      </c>
+      <c r="F129" t="s">
+        <v>18</v>
+      </c>
+      <c r="G129" t="s">
+        <v>158</v>
+      </c>
+      <c r="H129" t="s">
+        <v>96</v>
+      </c>
+      <c r="I129" t="s">
+        <v>11</v>
+      </c>
+      <c r="J129">
+        <v>5</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129" t="s">
+        <v>15</v>
+      </c>
+      <c r="N129" t="s">
+        <v>16</v>
+      </c>
+      <c r="O129">
+        <f>VLOOKUP($V129,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <f>VLOOKUP($V129,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="Q129">
+        <v>100</v>
+      </c>
+      <c r="R129" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S129" t="str">
+        <f>VLOOKUP($V129,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T129" t="str">
+        <f>VLOOKUP($V129,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="U129" t="str">
+        <f>VLOOKUP($V129,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>percent</v>
+      </c>
+      <c r="V129" t="s">
+        <v>17</v>
+      </c>
+      <c r="W129" t="s">
+        <v>18</v>
+      </c>
+      <c r="X129" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B130" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C130" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D130" t="s">
+        <v>241</v>
+      </c>
+      <c r="E130" t="s">
+        <v>241</v>
+      </c>
+      <c r="F130" t="s">
+        <v>18</v>
+      </c>
+      <c r="G130" t="s">
+        <v>158</v>
+      </c>
+      <c r="H130" t="s">
+        <v>96</v>
+      </c>
+      <c r="I130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J130">
+        <v>5</v>
+      </c>
+      <c r="K130">
+        <v>3</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130" t="s">
+        <v>15</v>
+      </c>
+      <c r="N130" t="s">
+        <v>16</v>
+      </c>
+      <c r="O130">
+        <f>VLOOKUP($V130,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <f>VLOOKUP($V130,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="Q130">
+        <v>100</v>
+      </c>
+      <c r="R130" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S130" t="str">
+        <f>VLOOKUP($V130,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T130" t="str">
+        <f>VLOOKUP($V130,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="U130" t="str">
+        <f>VLOOKUP($V130,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>percent</v>
+      </c>
+      <c r="V130" t="s">
+        <v>17</v>
+      </c>
+      <c r="W130" t="s">
+        <v>18</v>
+      </c>
+      <c r="X130" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B131" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C131" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D131" t="s">
+        <v>242</v>
+      </c>
+      <c r="E131" t="s">
+        <v>242</v>
+      </c>
+      <c r="F131" t="s">
+        <v>18</v>
+      </c>
+      <c r="G131" t="s">
+        <v>158</v>
+      </c>
+      <c r="H131" t="s">
+        <v>96</v>
+      </c>
+      <c r="I131" t="s">
+        <v>11</v>
+      </c>
+      <c r="J131">
+        <v>5</v>
+      </c>
+      <c r="K131">
+        <v>4</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131" t="s">
+        <v>15</v>
+      </c>
+      <c r="N131" t="s">
+        <v>16</v>
+      </c>
+      <c r="O131">
+        <f>VLOOKUP($V131,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <f>VLOOKUP($V131,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="Q131">
+        <v>100</v>
+      </c>
+      <c r="R131" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S131" t="str">
+        <f>VLOOKUP($V131,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T131" t="str">
+        <f>VLOOKUP($V131,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="U131" t="str">
+        <f>VLOOKUP($V131,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>percent</v>
+      </c>
+      <c r="V131" t="s">
+        <v>17</v>
+      </c>
+      <c r="W131" t="s">
+        <v>18</v>
+      </c>
+      <c r="X131" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B132" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C132" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D132" t="s">
+        <v>243</v>
+      </c>
+      <c r="E132" t="s">
+        <v>243</v>
+      </c>
+      <c r="F132" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" t="s">
+        <v>174</v>
+      </c>
+      <c r="H132" t="s">
+        <v>97</v>
+      </c>
+      <c r="I132" t="s">
+        <v>11</v>
+      </c>
+      <c r="J132">
+        <v>5</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132" t="s">
+        <v>15</v>
+      </c>
+      <c r="N132" t="s">
+        <v>16</v>
+      </c>
+      <c r="O132">
+        <f>VLOOKUP($V132,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="P132">
+        <f>VLOOKUP($V132,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="Q132">
+        <v>100</v>
+      </c>
+      <c r="R132" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S132" t="str">
+        <f>VLOOKUP($V132,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T132" t="str">
+        <f>VLOOKUP($V132,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="U132" t="str">
+        <f>VLOOKUP($V132,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+      <c r="V132" t="s">
+        <v>12</v>
+      </c>
+      <c r="W132" t="s">
+        <v>13</v>
+      </c>
+      <c r="X132" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B133" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C133" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D133" t="s">
+        <v>244</v>
+      </c>
+      <c r="E133" t="s">
+        <v>244</v>
+      </c>
+      <c r="F133" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" t="s">
+        <v>174</v>
+      </c>
+      <c r="H133" t="s">
+        <v>97</v>
+      </c>
+      <c r="I133" t="s">
+        <v>11</v>
+      </c>
+      <c r="J133">
+        <v>5</v>
+      </c>
+      <c r="K133">
+        <v>2</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133" t="s">
+        <v>15</v>
+      </c>
+      <c r="N133" t="s">
+        <v>16</v>
+      </c>
+      <c r="O133">
+        <f>VLOOKUP($V133,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="P133">
+        <f>VLOOKUP($V133,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="Q133">
+        <v>100</v>
+      </c>
+      <c r="R133" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S133" t="str">
+        <f>VLOOKUP($V133,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T133" t="str">
+        <f>VLOOKUP($V133,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="U133" t="str">
+        <f>VLOOKUP($V133,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+      <c r="V133" t="s">
+        <v>12</v>
+      </c>
+      <c r="W133" t="s">
+        <v>13</v>
+      </c>
+      <c r="X133" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B134" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C134" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D134" t="s">
+        <v>245</v>
+      </c>
+      <c r="E134" t="s">
+        <v>245</v>
+      </c>
+      <c r="F134" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" t="s">
+        <v>174</v>
+      </c>
+      <c r="H134" t="s">
+        <v>97</v>
+      </c>
+      <c r="I134" t="s">
+        <v>11</v>
+      </c>
+      <c r="J134">
+        <v>5</v>
+      </c>
+      <c r="K134">
+        <v>3</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134" t="s">
+        <v>15</v>
+      </c>
+      <c r="N134" t="s">
+        <v>16</v>
+      </c>
+      <c r="O134">
+        <f>VLOOKUP($V134,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="P134">
+        <f>VLOOKUP($V134,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="Q134">
+        <v>100</v>
+      </c>
+      <c r="R134" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S134" t="str">
+        <f>VLOOKUP($V134,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T134" t="str">
+        <f>VLOOKUP($V134,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="U134" t="str">
+        <f>VLOOKUP($V134,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+      <c r="V134" t="s">
+        <v>12</v>
+      </c>
+      <c r="W134" t="s">
+        <v>13</v>
+      </c>
+      <c r="X134" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B135" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C135" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D135" t="s">
+        <v>246</v>
+      </c>
+      <c r="E135" t="s">
+        <v>246</v>
+      </c>
+      <c r="F135" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" t="s">
+        <v>174</v>
+      </c>
+      <c r="H135" t="s">
+        <v>97</v>
+      </c>
+      <c r="I135" t="s">
+        <v>11</v>
+      </c>
+      <c r="J135">
+        <v>5</v>
+      </c>
+      <c r="K135">
+        <v>4</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135" t="s">
+        <v>15</v>
+      </c>
+      <c r="N135" t="s">
+        <v>16</v>
+      </c>
+      <c r="O135">
+        <f>VLOOKUP($V135,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-20</v>
+      </c>
+      <c r="P135">
+        <f>VLOOKUP($V135,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="Q135">
+        <v>100</v>
+      </c>
+      <c r="R135" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S135" t="str">
+        <f>VLOOKUP($V135,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="T135" t="str">
+        <f>VLOOKUP($V135,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>stl1</v>
+      </c>
+      <c r="U135" t="str">
+        <f>VLOOKUP($V135,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>degree_C</v>
+      </c>
+      <c r="V135" t="s">
+        <v>12</v>
+      </c>
+      <c r="W135" t="s">
+        <v>13</v>
+      </c>
+      <c r="X135" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B136" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C136" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D136" t="s">
+        <v>247</v>
+      </c>
+      <c r="E136" t="s">
+        <v>247</v>
+      </c>
+      <c r="F136" t="s">
+        <v>21</v>
+      </c>
+      <c r="G136" t="s">
+        <v>22</v>
+      </c>
+      <c r="H136" t="s">
+        <v>92</v>
+      </c>
+      <c r="I136" t="s">
+        <v>11</v>
+      </c>
+      <c r="J136">
+        <v>5</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="M136" t="s">
+        <v>15</v>
+      </c>
+      <c r="N136" t="s">
+        <v>16</v>
+      </c>
+      <c r="O136">
+        <f>VLOOKUP($V136,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="P136">
+        <f>VLOOKUP($V136,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="Q136">
+        <v>100</v>
+      </c>
+      <c r="R136" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S136" t="str">
+        <f>VLOOKUP($V136,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T136" t="str">
+        <f>VLOOKUP($V136,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="U136" t="str">
+        <f>VLOOKUP($V136,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+      <c r="V136" t="s">
+        <v>20</v>
+      </c>
+      <c r="W136" t="s">
+        <v>21</v>
+      </c>
+      <c r="X136" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B137" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C137" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D137" t="s">
+        <v>248</v>
+      </c>
+      <c r="E137" t="s">
+        <v>248</v>
+      </c>
+      <c r="F137" t="s">
+        <v>21</v>
+      </c>
+      <c r="G137" t="s">
+        <v>22</v>
+      </c>
+      <c r="H137" t="s">
+        <v>92</v>
+      </c>
+      <c r="I137" t="s">
+        <v>11</v>
+      </c>
+      <c r="J137">
+        <v>5</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137" t="s">
+        <v>15</v>
+      </c>
+      <c r="N137" t="s">
+        <v>16</v>
+      </c>
+      <c r="O137">
+        <f>VLOOKUP($V137,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-30</v>
+      </c>
+      <c r="P137">
+        <f>VLOOKUP($V137,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="Q137">
+        <v>100</v>
+      </c>
+      <c r="R137" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S137" t="str">
+        <f>VLOOKUP($V137,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="T137" t="str">
+        <f>VLOOKUP($V137,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>ssrd</v>
+      </c>
+      <c r="U137" t="str">
+        <f>VLOOKUP($V137,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>W / m^2</v>
+      </c>
+      <c r="V137" t="s">
+        <v>20</v>
+      </c>
+      <c r="W137" t="s">
+        <v>21</v>
+      </c>
+      <c r="X137" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B138" s="1">
+        <v>45139.541666666664</v>
+      </c>
+      <c r="C138" s="1">
+        <v>45292</v>
+      </c>
+      <c r="D138" t="s">
+        <v>249</v>
+      </c>
+      <c r="E138" t="s">
+        <v>249</v>
+      </c>
+      <c r="F138" t="s">
+        <v>24</v>
+      </c>
+      <c r="G138" t="s">
+        <v>59</v>
+      </c>
+      <c r="H138" t="s">
+        <v>90</v>
+      </c>
+      <c r="I138" t="s">
+        <v>11</v>
+      </c>
+      <c r="J138">
+        <v>5</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>1</v>
+      </c>
+      <c r="M138" t="s">
+        <v>15</v>
+      </c>
+      <c r="N138" t="s">
+        <v>16</v>
+      </c>
+      <c r="O138">
+        <f>VLOOKUP($V138,naming_lookup!$C$1:$H$40,3,FALSE)</f>
+        <v>-10</v>
+      </c>
+      <c r="P138">
+        <f>VLOOKUP($V138,naming_lookup!$C$1:$H$40,4,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="Q138">
+        <v>100</v>
+      </c>
+      <c r="R138" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S138" t="str">
+        <f>VLOOKUP($V138,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="T138" t="str">
+        <f>VLOOKUP($V138,naming_lookup!$C$1:$H$40,5,FALSE)</f>
+        <v>swvl1</v>
+      </c>
+      <c r="U138" t="str">
+        <f>VLOOKUP($V138,naming_lookup!$C$1:$H$40,6,FALSE)</f>
+        <v>m</v>
+      </c>
+      <c r="V138" t="s">
+        <v>23</v>
+      </c>
+      <c r="W138" t="s">
+        <v>24</v>
+      </c>
+      <c r="X138" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A139" s="2"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E3:N53">

--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plevy\Documents\metamet\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cehacuk-my.sharepoint.com/personal/clacap_ceh_ac_uk/Documents/metamet/tests/testthat/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A480153-A5CB-4962-96B3-DA1C3040D664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3A480153-A5CB-4962-96B3-DA1C3040D664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA9B4E97-8CB5-4EF9-BF9B-68D61D592B8D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
   <sheets>
     <sheet name="dt_meta" sheetId="1" r:id="rId1"/>
@@ -1733,19 +1733,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B621CE1-A4D4-4502-917D-92507EE2F7EE}">
   <dimension ref="A1:X139"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
-    <col min="22" max="22" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.77734375" customWidth="1"/>
+    <col min="2" max="3" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.81640625" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="8.90625" customWidth="1"/>
+    <col min="17" max="17" width="10.1796875" customWidth="1"/>
+    <col min="22" max="22" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>103</v>
       </c>
@@ -1819,7 +1820,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -1894,7 +1895,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -2056,7 +2057,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -2130,7 +2131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -2292,7 +2293,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -2454,7 +2455,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>104</v>
       </c>
@@ -2535,7 +2536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>104</v>
       </c>
@@ -2616,7 +2617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>104</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>104</v>
       </c>
@@ -2778,7 +2779,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -2859,7 +2860,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>104</v>
       </c>
@@ -2940,7 +2941,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>104</v>
       </c>
@@ -3021,7 +3022,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -3102,7 +3103,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>104</v>
       </c>
@@ -3183,7 +3184,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -3264,7 +3265,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -3426,7 +3427,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>104</v>
       </c>
@@ -3507,7 +3508,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -3588,7 +3589,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>104</v>
       </c>
@@ -3669,7 +3670,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>104</v>
       </c>
@@ -3750,7 +3751,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -3831,7 +3832,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -3912,7 +3913,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>104</v>
       </c>
@@ -3993,7 +3994,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>104</v>
       </c>
@@ -4074,7 +4075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>104</v>
       </c>
@@ -4155,7 +4156,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -4317,7 +4318,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>104</v>
       </c>
@@ -4479,7 +4480,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -4560,7 +4561,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>104</v>
       </c>
@@ -4641,7 +4642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>104</v>
       </c>
@@ -4722,7 +4723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>104</v>
       </c>
@@ -4803,7 +4804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>104</v>
       </c>
@@ -4884,7 +4885,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>104</v>
       </c>
@@ -4965,7 +4966,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -5046,7 +5047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>104</v>
       </c>
@@ -5127,7 +5128,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>104</v>
       </c>
@@ -5208,7 +5209,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>104</v>
       </c>
@@ -5289,7 +5290,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -5370,7 +5371,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>104</v>
       </c>
@@ -5451,7 +5452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -5525,7 +5526,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -5606,7 +5607,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -5687,7 +5688,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -5768,7 +5769,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -5849,7 +5850,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -5930,7 +5931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -6011,7 +6012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -6092,7 +6093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -6173,7 +6174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>104</v>
       </c>
@@ -6254,7 +6255,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -6335,7 +6336,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>104</v>
       </c>
@@ -6416,7 +6417,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>104</v>
       </c>
@@ -6497,7 +6498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>104</v>
       </c>
@@ -6578,7 +6579,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>104</v>
       </c>
@@ -6659,7 +6660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>104</v>
       </c>
@@ -6740,7 +6741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>104</v>
       </c>
@@ -6821,7 +6822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>104</v>
       </c>
@@ -6902,7 +6903,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>104</v>
       </c>
@@ -6983,7 +6984,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>104</v>
       </c>
@@ -7064,7 +7065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>104</v>
       </c>
@@ -7145,7 +7146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>104</v>
       </c>
@@ -7226,7 +7227,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>104</v>
       </c>
@@ -7307,7 +7308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>104</v>
       </c>
@@ -7388,7 +7389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>104</v>
       </c>
@@ -7469,7 +7470,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>104</v>
       </c>
@@ -7550,7 +7551,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>104</v>
       </c>
@@ -7631,7 +7632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>104</v>
       </c>
@@ -7712,7 +7713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>104</v>
       </c>
@@ -7793,7 +7794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -7874,7 +7875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>104</v>
       </c>
@@ -8036,7 +8037,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>104</v>
       </c>
@@ -8117,7 +8118,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>104</v>
       </c>
@@ -8198,7 +8199,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>104</v>
       </c>
@@ -8279,7 +8280,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>104</v>
       </c>
@@ -8360,7 +8361,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>104</v>
       </c>
@@ -8441,7 +8442,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>104</v>
       </c>
@@ -8522,7 +8523,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>104</v>
       </c>
@@ -8603,7 +8604,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>104</v>
       </c>
@@ -8684,7 +8685,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>104</v>
       </c>
@@ -8765,7 +8766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>104</v>
       </c>
@@ -8846,7 +8847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>104</v>
       </c>
@@ -8927,7 +8928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -9008,7 +9009,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>104</v>
       </c>
@@ -9089,7 +9090,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -9170,7 +9171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -9251,7 +9252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -9332,7 +9333,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -9413,7 +9414,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -9494,7 +9495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -9575,7 +9576,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>104</v>
       </c>
@@ -9656,7 +9657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>104</v>
       </c>
@@ -9737,7 +9738,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -9818,7 +9819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>104</v>
       </c>
@@ -9899,7 +9900,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -9980,7 +9981,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>106</v>
       </c>
@@ -10059,7 +10060,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>106</v>
       </c>
@@ -10138,7 +10139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>106</v>
       </c>
@@ -10217,7 +10218,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>106</v>
       </c>
@@ -10296,7 +10297,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>106</v>
       </c>
@@ -10375,7 +10376,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>106</v>
       </c>
@@ -10454,7 +10455,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>106</v>
       </c>
@@ -10533,7 +10534,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>106</v>
       </c>
@@ -10612,7 +10613,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>106</v>
       </c>
@@ -10691,7 +10692,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>106</v>
       </c>
@@ -10770,7 +10771,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>106</v>
       </c>
@@ -10849,7 +10850,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>106</v>
       </c>
@@ -10928,7 +10929,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>106</v>
       </c>
@@ -11007,7 +11008,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>106</v>
       </c>
@@ -11086,7 +11087,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>106</v>
       </c>
@@ -11165,7 +11166,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>105</v>
       </c>
@@ -11244,7 +11245,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>105</v>
       </c>
@@ -11323,7 +11324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>105</v>
       </c>
@@ -11402,7 +11403,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>105</v>
       </c>
@@ -11481,7 +11482,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>105</v>
       </c>
@@ -11560,7 +11561,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>105</v>
       </c>
@@ -11639,7 +11640,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>105</v>
       </c>
@@ -11718,7 +11719,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>105</v>
       </c>
@@ -11797,7 +11798,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>105</v>
       </c>
@@ -11876,7 +11877,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>105</v>
       </c>
@@ -11955,7 +11956,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>105</v>
       </c>
@@ -12034,7 +12035,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>105</v>
       </c>
@@ -12113,7 +12114,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>105</v>
       </c>
@@ -12192,7 +12193,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>105</v>
       </c>
@@ -12271,7 +12272,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>105</v>
       </c>
@@ -12350,7 +12351,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>105</v>
       </c>
@@ -12429,7 +12430,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>105</v>
       </c>
@@ -12508,7 +12509,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>105</v>
       </c>
@@ -12587,7 +12588,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>105</v>
       </c>
@@ -12666,7 +12667,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>105</v>
       </c>
@@ -12745,7 +12746,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>105</v>
       </c>
@@ -12824,7 +12825,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A139" s="2"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -12842,17 +12843,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF29616-2603-4811-AA75-C70B902F2583}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.36328125" customWidth="1"/>
+    <col min="2" max="2" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>185</v>
       </c>
@@ -12878,7 +12879,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>186</v>
       </c>
@@ -12906,7 +12907,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -12934,7 +12935,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>205</v>
       </c>
@@ -12962,7 +12963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -12990,7 +12991,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -13018,7 +13019,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -13046,7 +13047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -13074,7 +13075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>187</v>
       </c>
@@ -13102,7 +13103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -13130,7 +13131,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -13158,7 +13159,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -13186,7 +13187,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -13214,7 +13215,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -13242,7 +13243,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
@@ -13270,7 +13271,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
@@ -13298,7 +13299,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -13326,7 +13327,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>52</v>
       </c>
@@ -13354,7 +13355,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>55</v>
       </c>
@@ -13382,7 +13383,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -13410,7 +13411,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -13438,7 +13439,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>186</v>
       </c>
@@ -13466,7 +13467,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>186</v>
       </c>
@@ -13494,7 +13495,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>186</v>
       </c>
@@ -13522,7 +13523,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>186</v>
       </c>
@@ -13550,7 +13551,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -13578,7 +13579,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -13606,7 +13607,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -13634,7 +13635,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -13662,7 +13663,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -13690,7 +13691,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -13718,7 +13719,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -13746,7 +13747,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>203</v>
       </c>
@@ -13774,7 +13775,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -13802,7 +13803,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>74</v>
       </c>
@@ -13830,7 +13831,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>76</v>
       </c>
@@ -13858,7 +13859,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>78</v>
       </c>
@@ -13886,7 +13887,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>80</v>
       </c>
@@ -13914,7 +13915,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>82</v>
       </c>
@@ -13942,7 +13943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>82</v>
       </c>
@@ -13978,15 +13979,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B6FF77-C883-40C9-8616-F79923CDA0A3}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>225</v>
       </c>
@@ -14033,7 +14034,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -14081,7 +14082,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -14120,7 +14121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -14162,7 +14163,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -14210,7 +14211,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -14252,7 +14253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>135</v>
       </c>
@@ -14282,7 +14283,7 @@
         <v>-99999</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -14312,7 +14313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -14342,7 +14343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>141</v>
       </c>
@@ -14372,7 +14373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>142</v>
       </c>
@@ -14402,7 +14403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -14441,7 +14442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -14480,7 +14481,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -14522,7 +14523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -14555,7 +14556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -14597,7 +14598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>107</v>
       </c>
@@ -14630,7 +14631,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -14669,7 +14670,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -14705,7 +14706,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -14753,7 +14754,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -14795,7 +14796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -14843,7 +14844,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -14882,7 +14883,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -14930,7 +14931,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -14969,7 +14970,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -15008,7 +15009,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>23</v>
       </c>

--- a/tests/testthat/data-raw/dt_meta.xlsx
+++ b/tests/testthat/data-raw/dt_meta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cehacuk-my.sharepoint.com/personal/clacap_ceh_ac_uk/Documents/metamet/tests/testthat/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3A480153-A5CB-4962-96B3-DA1C3040D664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA9B4E97-8CB5-4EF9-BF9B-68D61D592B8D}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{3A480153-A5CB-4962-96B3-DA1C3040D664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8C983C1-D57F-426A-9C3E-AF6B956C139F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
+    <workbookView xWindow="1270" yWindow="1610" windowWidth="14400" windowHeight="8170" xr2:uid="{A45171B9-DFAC-4AFC-87E9-9DEEF5646C72}"/>
   </bookViews>
   <sheets>
     <sheet name="dt_meta" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="dt_var_naming" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dt_meta!$A$1:$X$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dt_meta!$A$1:$X$138</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
